--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C67EFD-791E-4E44-AEB2-291B7E5A7442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797BFF78-90CF-4DD5-BC00-7E60280D7948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="4" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="3" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -775,18 +775,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 大甲</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>09:00</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 清水</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>12:00</t>
   </si>
   <si>
@@ -930,10 +922,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>駐駕大甲Nissan 裕唐汽車服務廠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>26</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -962,10 +950,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 回宮</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>15:05</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2450,6 +2434,18 @@
   <si>
     <t>四張福德宮</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲</t>
+  </si>
+  <si>
+    <t>清水</t>
+  </si>
+  <si>
+    <t>駐駕大甲Nissan裕唐汽車服務廠</t>
+  </si>
+  <si>
+    <t>回宮</t>
   </si>
 </sst>
 </file>
@@ -3056,7 +3052,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3070,6 +3066,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3478,27 +3480,27 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -3507,27 +3509,27 @@
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -3538,22 +3540,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -3564,22 +3566,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -3590,22 +3592,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -3616,19 +3618,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>160</v>
@@ -3642,22 +3644,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -3668,22 +3670,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -3694,22 +3696,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
@@ -3720,22 +3722,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -3746,22 +3748,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
@@ -3772,22 +3774,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>13</v>
@@ -3795,22 +3797,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
@@ -3818,22 +3820,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -3841,19 +3843,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>126</v>
@@ -3867,22 +3869,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>166</v>
@@ -3893,22 +3895,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>166</v>
@@ -3919,22 +3921,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>166</v>
@@ -3945,22 +3947,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>166</v>
@@ -3971,22 +3973,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>166</v>
@@ -3997,10 +3999,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>187</v>
@@ -4012,7 +4014,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>166</v>
@@ -4023,10 +4025,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>187</v>
@@ -4038,7 +4040,7 @@
         <v>87</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>166</v>
@@ -4049,10 +4051,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>187</v>
@@ -4061,10 +4063,10 @@
         <v>187</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>166</v>
@@ -4075,10 +4077,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>187</v>
@@ -4087,10 +4089,10 @@
         <v>187</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>166</v>
@@ -4101,10 +4103,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>187</v>
@@ -4113,10 +4115,10 @@
         <v>187</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>166</v>
@@ -4127,10 +4129,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>187</v>
@@ -4139,10 +4141,10 @@
         <v>187</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>166</v>
@@ -4153,10 +4155,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>187</v>
@@ -4165,10 +4167,10 @@
         <v>187</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>166</v>
@@ -4179,22 +4181,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>166</v>
@@ -4205,22 +4207,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>166</v>
@@ -4231,22 +4233,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>166</v>
@@ -4257,22 +4259,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>166</v>
@@ -4283,22 +4285,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>166</v>
@@ -4306,22 +4308,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>166</v>
@@ -4332,22 +4334,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>166</v>
@@ -4358,22 +4360,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>166</v>
@@ -4384,22 +4386,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>166</v>
@@ -4410,22 +4412,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>166</v>
@@ -4436,22 +4438,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>166</v>
@@ -4462,22 +4464,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>166</v>
@@ -4488,22 +4490,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>166</v>
@@ -4514,22 +4516,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>166</v>
@@ -4540,22 +4542,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>166</v>
@@ -4566,22 +4568,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>166</v>
@@ -4592,22 +4594,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>166</v>
@@ -4618,22 +4620,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>166</v>
@@ -4644,22 +4646,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>166</v>
@@ -4670,22 +4672,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>166</v>
@@ -4696,22 +4698,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>166</v>
@@ -4722,22 +4724,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>166</v>
@@ -4748,22 +4750,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>166</v>
@@ -4774,22 +4776,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>166</v>
@@ -4800,22 +4802,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>166</v>
@@ -4826,22 +4828,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>166</v>
@@ -4852,22 +4854,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>166</v>
@@ -4878,22 +4880,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>166</v>
@@ -4904,22 +4906,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>166</v>
@@ -4930,22 +4932,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>166</v>
@@ -4956,22 +4958,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>166</v>
@@ -4982,22 +4984,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>166</v>
@@ -5008,22 +5010,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>166</v>
@@ -5034,10 +5036,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>187</v>
@@ -5049,7 +5051,7 @@
         <v>88</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>166</v>
@@ -5060,10 +5062,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>187</v>
@@ -5072,10 +5074,10 @@
         <v>9</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>166</v>
@@ -5086,10 +5088,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>187</v>
@@ -5098,10 +5100,10 @@
         <v>9</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>166</v>
@@ -5112,10 +5114,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>187</v>
@@ -5124,7 +5126,7 @@
         <v>9</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>12</v>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E66" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -5180,27 +5182,27 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -5209,27 +5211,27 @@
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -5240,22 +5242,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -5266,22 +5268,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -5292,22 +5294,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -5318,22 +5320,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -5344,22 +5346,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -5370,22 +5372,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -5396,22 +5398,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
@@ -5422,22 +5424,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -5448,22 +5450,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
@@ -5474,13 +5476,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>179</v>
@@ -5489,7 +5491,7 @@
         <v>87</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>13</v>
@@ -5500,22 +5502,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
@@ -5526,22 +5528,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -5552,22 +5554,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
@@ -5578,22 +5580,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>13</v>
@@ -5604,22 +5606,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
@@ -5630,22 +5632,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>13</v>
@@ -5656,22 +5658,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>13</v>
@@ -5682,22 +5684,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>13</v>
@@ -5708,19 +5710,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>50</v>
@@ -5734,13 +5736,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>179</v>
@@ -5749,7 +5751,7 @@
         <v>103</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>13</v>
@@ -5760,22 +5762,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>13</v>
@@ -5786,22 +5788,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>13</v>
@@ -5812,22 +5814,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>13</v>
@@ -5838,13 +5840,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>188</v>
@@ -5853,7 +5855,7 @@
         <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>13</v>
@@ -5864,22 +5866,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>13</v>
@@ -5890,22 +5892,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>13</v>
@@ -5916,22 +5918,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>13</v>
@@ -5942,22 +5944,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>13</v>
@@ -5968,22 +5970,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>13</v>
@@ -5994,22 +5996,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>13</v>
@@ -6020,22 +6022,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>13</v>
@@ -6046,22 +6048,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>13</v>
@@ -6072,22 +6074,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>13</v>
@@ -6098,22 +6100,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>13</v>
@@ -6124,22 +6126,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>13</v>
@@ -6150,22 +6152,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>13</v>
@@ -6176,22 +6178,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>13</v>
@@ -6202,22 +6204,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>13</v>
@@ -6228,22 +6230,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>13</v>
@@ -6254,22 +6256,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>13</v>
@@ -6280,22 +6282,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>13</v>
@@ -6306,22 +6308,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>13</v>
@@ -6332,22 +6334,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>13</v>
@@ -6358,22 +6360,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>13</v>
@@ -6384,22 +6386,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>13</v>
@@ -6410,22 +6412,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>13</v>
@@ -6436,22 +6438,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>13</v>
@@ -6462,22 +6464,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>13</v>
@@ -6488,22 +6490,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>13</v>
@@ -6514,22 +6516,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>13</v>
@@ -6540,22 +6542,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>13</v>
@@ -6566,22 +6568,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>13</v>
@@ -6592,22 +6594,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>13</v>
@@ -6618,22 +6620,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>13</v>
@@ -6644,22 +6646,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>13</v>
@@ -6670,22 +6672,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>13</v>
@@ -6696,22 +6698,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>13</v>
@@ -6722,22 +6724,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>13</v>
@@ -6748,22 +6750,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>13</v>
@@ -6774,22 +6776,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>13</v>
@@ -6800,16 +6802,16 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>94</v>
@@ -6826,22 +6828,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>13</v>
@@ -6852,22 +6854,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>13</v>
@@ -6878,22 +6880,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>13</v>
@@ -6904,22 +6906,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>13</v>
@@ -6930,22 +6932,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>13</v>
@@ -6953,22 +6955,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>13</v>
@@ -6976,19 +6978,19 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>126</v>
@@ -7002,22 +7004,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>166</v>
@@ -7028,22 +7030,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>166</v>
@@ -7054,22 +7056,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>166</v>
@@ -7080,19 +7082,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>167</v>
@@ -7106,16 +7108,16 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>17</v>
@@ -7132,22 +7134,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>166</v>
@@ -7158,22 +7160,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>166</v>
@@ -7184,22 +7186,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>166</v>
@@ -7210,22 +7212,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>166</v>
@@ -7236,22 +7238,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>166</v>
@@ -7262,22 +7264,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>166</v>
@@ -7288,22 +7290,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>166</v>
@@ -7314,22 +7316,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>166</v>
@@ -7340,22 +7342,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>166</v>
@@ -7366,22 +7368,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>166</v>
@@ -7392,22 +7394,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>166</v>
@@ -7418,22 +7420,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>166</v>
@@ -7444,22 +7446,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>166</v>
@@ -7470,22 +7472,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>166</v>
@@ -7496,22 +7498,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>166</v>
@@ -7522,22 +7524,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>177</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>166</v>
@@ -7548,16 +7550,16 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>79</v>
@@ -7611,27 +7613,27 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -7640,27 +7642,27 @@
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -7671,19 +7673,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>19</v>
@@ -7697,13 +7699,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
@@ -7712,7 +7714,7 @@
         <v>172</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -7723,22 +7725,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -7749,22 +7751,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -7775,22 +7777,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -7801,22 +7803,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -7827,22 +7829,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
@@ -7853,13 +7855,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>72</v>
@@ -7868,7 +7870,7 @@
         <v>87</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -7879,13 +7881,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>72</v>
@@ -7894,7 +7896,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
@@ -7905,22 +7907,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>13</v>
@@ -7931,22 +7933,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
@@ -7957,19 +7959,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
@@ -7983,22 +7985,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
@@ -8009,19 +8011,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>30</v>
@@ -8035,13 +8037,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>72</v>
@@ -8050,7 +8052,7 @@
         <v>97</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
@@ -8061,22 +8063,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>13</v>
@@ -8087,13 +8089,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>72</v>
@@ -8113,22 +8115,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>13</v>
@@ -8139,19 +8141,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>50</v>
@@ -8165,22 +8167,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>13</v>
@@ -8191,22 +8193,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>13</v>
@@ -8217,19 +8219,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>53</v>
@@ -8243,22 +8245,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>13</v>
@@ -8269,22 +8271,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>13</v>
@@ -8295,22 +8297,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>13</v>
@@ -8321,13 +8323,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>92</v>
@@ -8336,7 +8338,7 @@
         <v>87</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>13</v>
@@ -8347,22 +8349,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>13</v>
@@ -8373,22 +8375,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>13</v>
@@ -8399,22 +8401,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>13</v>
@@ -8425,22 +8427,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>13</v>
@@ -8451,13 +8453,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>92</v>
@@ -8466,7 +8468,7 @@
         <v>145</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>13</v>
@@ -8477,22 +8479,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>13</v>
@@ -8503,22 +8505,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>13</v>
@@ -8529,13 +8531,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>137</v>
@@ -8544,7 +8546,7 @@
         <v>87</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>13</v>
@@ -8555,22 +8557,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>13</v>
@@ -8581,13 +8583,13 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>137</v>
@@ -8596,7 +8598,7 @@
         <v>62</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>13</v>
@@ -8607,22 +8609,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>13</v>
@@ -8630,22 +8632,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>13</v>
@@ -8656,22 +8658,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>13</v>
@@ -8679,22 +8681,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>13</v>
@@ -8702,13 +8704,13 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>137</v>
@@ -8717,7 +8719,7 @@
         <v>140</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>13</v>
@@ -8728,22 +8730,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>13</v>
@@ -8754,22 +8756,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>13</v>
@@ -8780,22 +8782,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>13</v>
@@ -8803,22 +8805,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>13</v>
@@ -8829,22 +8831,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>13</v>
@@ -8855,22 +8857,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>13</v>
@@ -8878,22 +8880,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>13</v>
@@ -8901,22 +8903,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>13</v>
@@ -8927,22 +8929,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>13</v>
@@ -8950,13 +8952,13 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>138</v>
@@ -8965,7 +8967,7 @@
         <v>87</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>13</v>
@@ -8976,22 +8978,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>13</v>
@@ -9002,22 +9004,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>13</v>
@@ -9028,22 +9030,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>13</v>
@@ -9054,22 +9056,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>13</v>
@@ -9080,22 +9082,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>13</v>
@@ -9106,19 +9108,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>14</v>
@@ -9129,22 +9131,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>13</v>
@@ -9155,22 +9157,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>13</v>
@@ -9181,22 +9183,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>13</v>
@@ -9207,22 +9209,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>13</v>
@@ -9233,22 +9235,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>13</v>
@@ -9259,22 +9261,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>13</v>
@@ -9285,22 +9287,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>13</v>
@@ -9308,13 +9310,13 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>139</v>
@@ -9323,7 +9325,7 @@
         <v>33</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>13</v>
@@ -9334,22 +9336,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>13</v>
@@ -9360,22 +9362,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>13</v>
@@ -9386,22 +9388,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>13</v>
@@ -9412,22 +9414,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>13</v>
@@ -9438,13 +9440,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>139</v>
@@ -9453,7 +9455,7 @@
         <v>75</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>13</v>
@@ -9464,22 +9466,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>13</v>
@@ -9487,22 +9489,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>13</v>
@@ -9510,22 +9512,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>13</v>
@@ -9533,22 +9535,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>13</v>
@@ -9556,22 +9558,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>13</v>
@@ -9579,22 +9581,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>13</v>
@@ -9602,13 +9604,13 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>139</v>
@@ -9628,22 +9630,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>166</v>
@@ -9654,22 +9656,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>166</v>
@@ -9680,22 +9682,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>166</v>
@@ -9706,22 +9708,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>166</v>
@@ -9732,22 +9734,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>166</v>
@@ -9758,22 +9760,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>166</v>
@@ -9784,22 +9786,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>166</v>
@@ -9810,22 +9812,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>166</v>
@@ -9836,19 +9838,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>167</v>
@@ -9862,13 +9864,13 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>179</v>
@@ -9888,22 +9890,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>166</v>
@@ -9914,22 +9916,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>166</v>
@@ -9940,22 +9942,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>166</v>
@@ -9966,22 +9968,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>166</v>
@@ -9992,19 +9994,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>20</v>
@@ -10018,22 +10020,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>166</v>
@@ -10044,22 +10046,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>166</v>
@@ -10070,22 +10072,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>166</v>
@@ -10096,22 +10098,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>166</v>
@@ -10122,22 +10124,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>166</v>
@@ -10148,13 +10150,13 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>188</v>
@@ -10163,7 +10165,7 @@
         <v>177</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>166</v>
@@ -10174,19 +10176,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>12</v>
@@ -10220,30 +10222,30 @@
     <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.65" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="15.65" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>550</v>
+      <c r="G1" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10269,7 +10271,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10286,10 +10288,10 @@
         <v>188</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>190</v>
+        <v>654</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -10312,10 +10314,10 @@
         <v>188</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>192</v>
+        <v>655</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -10338,10 +10340,10 @@
         <v>188</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -10364,7 +10366,7 @@
         <v>188</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>167</v>
@@ -10390,10 +10392,10 @@
         <v>188</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -10413,13 +10415,13 @@
         <v>187</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -10439,13 +10441,13 @@
         <v>187</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -10465,13 +10467,13 @@
         <v>187</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
@@ -10491,13 +10493,13 @@
         <v>187</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -10517,13 +10519,13 @@
         <v>187</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
@@ -10543,13 +10545,13 @@
         <v>187</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>13</v>
@@ -10569,13 +10571,13 @@
         <v>187</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
@@ -10595,10 +10597,10 @@
         <v>187</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>126</v>
@@ -10621,10 +10623,10 @@
         <v>187</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>126</v>
@@ -10647,13 +10649,13 @@
         <v>187</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>166</v>
@@ -10673,7 +10675,7 @@
         <v>187</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>65</v>
@@ -10699,7 +10701,7 @@
         <v>187</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>34</v>
@@ -10725,13 +10727,13 @@
         <v>187</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>166</v>
@@ -10751,13 +10753,13 @@
         <v>187</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>166</v>
@@ -10777,13 +10779,13 @@
         <v>187</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>166</v>
@@ -10803,13 +10805,13 @@
         <v>187</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>166</v>
@@ -10829,13 +10831,13 @@
         <v>187</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>166</v>
@@ -10855,13 +10857,13 @@
         <v>187</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>166</v>
@@ -10881,13 +10883,13 @@
         <v>187</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>229</v>
+        <v>656</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>166</v>
@@ -10907,13 +10909,13 @@
         <v>187</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>229</v>
+        <v>656</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>166</v>
@@ -10933,13 +10935,13 @@
         <v>187</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>166</v>
@@ -10959,13 +10961,13 @@
         <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>166</v>
@@ -10985,13 +10987,13 @@
         <v>187</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>166</v>
@@ -11011,13 +11013,13 @@
         <v>187</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>178</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>166</v>
@@ -11037,13 +11039,13 @@
         <v>187</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>166</v>
@@ -11063,13 +11065,13 @@
         <v>187</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>237</v>
+        <v>657</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>166</v>
@@ -11154,30 +11156,30 @@
     <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>549</v>
-      </c>
-      <c r="H1" t="s">
-        <v>550</v>
+      <c r="G1" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11203,7 +11205,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11405,7 +11407,7 @@
         <v>41</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797BFF78-90CF-4DD5-BC00-7E60280D7948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D639A052-CC02-4F6D-ABDA-B7C5F3B6818F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="3" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="5" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="2023" sheetId="4" r:id="rId3"/>
     <sheet name="2022" sheetId="3" r:id="rId4"/>
     <sheet name="2021" sheetId="2" r:id="rId5"/>
+    <sheet name="2020" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="685">
   <si>
     <t>年份</t>
   </si>
@@ -2446,6 +2447,114 @@
   </si>
   <si>
     <t>回宮</t>
+  </si>
+  <si>
+    <t>2020</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>庚子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:00</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:50</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲Toyota</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>04:00</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>員林宏泰汽車商行</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">駐駕 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化市彰化聯誼會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:25</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>03:00</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林虎尾農工</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:30</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>元長市區民宅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>19:16</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>二崙慈聖宮埤腳媽</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>番婆鎮安宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化市中華西路民宅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中清水紫雲巖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:30</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄通南守望相助隊旁帳蓬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苗栗通霄慈后宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:20</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:53</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:16</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:53</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3052,7 +3161,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3066,12 +3175,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10222,29 +10325,29 @@
     <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="15.65" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.65" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>546</v>
       </c>
     </row>
@@ -11156,29 +11259,29 @@
     <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" t="s">
         <v>545</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" t="s">
         <v>546</v>
       </c>
     </row>
@@ -13178,6 +13281,793 @@
         <v>183</v>
       </c>
     </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E4B1C3-666C-4C27-86E8-39D6DDB5C8F1}">
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultRowHeight="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F50" s="3"/>
+    </row>
+    <row r="51" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F53" s="3"/>
+    </row>
+    <row r="54" spans="6:6" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D639A052-CC02-4F6D-ABDA-B7C5F3B6818F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9052C6FC-00DE-4D0C-BF9A-9386EFC11812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="5" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="7" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="2022" sheetId="3" r:id="rId4"/>
     <sheet name="2021" sheetId="2" r:id="rId5"/>
     <sheet name="2020" sheetId="6" r:id="rId6"/>
+    <sheet name="2019" sheetId="8" r:id="rId7"/>
+    <sheet name="2018" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="876">
   <si>
     <t>年份</t>
   </si>
@@ -2554,6 +2556,594 @@
   </si>
   <si>
     <t>14:53</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 16:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 18:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 03:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 20:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 18:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 19:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 14:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 14:25</t>
+  </si>
+  <si>
+    <t>2019</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>己亥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中華佛教文物流通中心</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑫車汽車廣場</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林褒忠分駐所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>野川堂秘境鍋物-虎尾店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>埤頭合興宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲日南民宅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>起駕</t>
+  </si>
+  <si>
+    <t>2018</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>戊戌</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>23：40</t>
+  </si>
+  <si>
+    <t>05：50</t>
+  </si>
+  <si>
+    <t>06：13</t>
+  </si>
+  <si>
+    <t>08：54</t>
+  </si>
+  <si>
+    <t>09：05</t>
+  </si>
+  <si>
+    <t>11：47</t>
+  </si>
+  <si>
+    <t>12：58</t>
+  </si>
+  <si>
+    <t>15：48</t>
+  </si>
+  <si>
+    <t>20：25</t>
+  </si>
+  <si>
+    <t>21：28</t>
+  </si>
+  <si>
+    <t>23：49</t>
+  </si>
+  <si>
+    <t>00：02</t>
+  </si>
+  <si>
+    <t>04：50</t>
+  </si>
+  <si>
+    <t>05：15</t>
+  </si>
+  <si>
+    <t>07：26</t>
+  </si>
+  <si>
+    <t>09：10</t>
+  </si>
+  <si>
+    <t>10：18</t>
+  </si>
+  <si>
+    <t>10：58</t>
+  </si>
+  <si>
+    <t>11：57</t>
+  </si>
+  <si>
+    <t>12：01</t>
+  </si>
+  <si>
+    <t>12：06</t>
+  </si>
+  <si>
+    <t>12：07</t>
+  </si>
+  <si>
+    <t>15：00</t>
+  </si>
+  <si>
+    <t>07：25</t>
+  </si>
+  <si>
+    <t>08：50</t>
+  </si>
+  <si>
+    <t>09：04</t>
+  </si>
+  <si>
+    <t>10：25</t>
+  </si>
+  <si>
+    <t>10：35</t>
+  </si>
+  <si>
+    <t>11：35</t>
+  </si>
+  <si>
+    <t>13：55</t>
+  </si>
+  <si>
+    <t>14：49</t>
+  </si>
+  <si>
+    <t>18：31</t>
+  </si>
+  <si>
+    <t>05：00</t>
+  </si>
+  <si>
+    <t>06：21</t>
+  </si>
+  <si>
+    <t>06：41</t>
+  </si>
+  <si>
+    <t>07：49</t>
+  </si>
+  <si>
+    <t>08：18</t>
+  </si>
+  <si>
+    <t>09：23</t>
+  </si>
+  <si>
+    <t>09：49</t>
+  </si>
+  <si>
+    <t>10：21</t>
+  </si>
+  <si>
+    <t>10：40</t>
+  </si>
+  <si>
+    <t>11：50</t>
+  </si>
+  <si>
+    <t>14：32</t>
+  </si>
+  <si>
+    <t>18：30</t>
+  </si>
+  <si>
+    <t>05：44</t>
+  </si>
+  <si>
+    <t>06：52</t>
+  </si>
+  <si>
+    <t>09：17</t>
+  </si>
+  <si>
+    <t>10：26</t>
+  </si>
+  <si>
+    <t>10：39</t>
+  </si>
+  <si>
+    <t>12：17</t>
+  </si>
+  <si>
+    <t>14：58</t>
+  </si>
+  <si>
+    <t>15：23</t>
+  </si>
+  <si>
+    <t>15：36</t>
+  </si>
+  <si>
+    <t>17：59</t>
+  </si>
+  <si>
+    <t>05：59</t>
+  </si>
+  <si>
+    <t>07：46</t>
+  </si>
+  <si>
+    <t>08：56</t>
+  </si>
+  <si>
+    <t>09：08</t>
+  </si>
+  <si>
+    <t>10：11</t>
+  </si>
+  <si>
+    <t>10：37</t>
+  </si>
+  <si>
+    <t>11：30</t>
+  </si>
+  <si>
+    <t>11：38</t>
+  </si>
+  <si>
+    <t>11：51</t>
+  </si>
+  <si>
+    <t>14：29</t>
+  </si>
+  <si>
+    <t>14：52</t>
+  </si>
+  <si>
+    <t>15：06</t>
+  </si>
+  <si>
+    <t>15：20</t>
+  </si>
+  <si>
+    <t>15：35</t>
+  </si>
+  <si>
+    <t>16：27</t>
+  </si>
+  <si>
+    <t>16：45</t>
+  </si>
+  <si>
+    <t>19：29</t>
+  </si>
+  <si>
+    <t>06：05</t>
+  </si>
+  <si>
+    <t>06：17</t>
+  </si>
+  <si>
+    <t>07：10</t>
+  </si>
+  <si>
+    <t>07：24</t>
+  </si>
+  <si>
+    <t>07：50</t>
+  </si>
+  <si>
+    <t>08：01</t>
+  </si>
+  <si>
+    <t>08：17</t>
+  </si>
+  <si>
+    <t>08：28</t>
+  </si>
+  <si>
+    <t>10：10</t>
+  </si>
+  <si>
+    <t>10：56</t>
+  </si>
+  <si>
+    <t>11：16</t>
+  </si>
+  <si>
+    <t>13：58</t>
+  </si>
+  <si>
+    <t>14：31</t>
+  </si>
+  <si>
+    <t>14：41</t>
+  </si>
+  <si>
+    <t>06：59</t>
+  </si>
+  <si>
+    <t>08：26</t>
+  </si>
+  <si>
+    <t>08：33</t>
+  </si>
+  <si>
+    <t>09：48</t>
+  </si>
+  <si>
+    <t>10：28</t>
+  </si>
+  <si>
+    <t>10：43</t>
+  </si>
+  <si>
+    <t>13：29</t>
+  </si>
+  <si>
+    <t>14：20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白沙屯拱天宮           </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>停駕龜殼村路口、台61西濱快速公路交叉處</t>
+  </si>
+  <si>
+    <t>在台61西濱高架橋下路旁停駕</t>
+  </si>
+  <si>
+    <t>停駕伸港福安宮午休</t>
+  </si>
+  <si>
+    <t>伸港福安宮起駕</t>
+  </si>
+  <si>
+    <t>大慶公司停駕</t>
+  </si>
+  <si>
+    <t>台61西濱快速公路、152縣道（橋墩P156）路口停駕</t>
+  </si>
+  <si>
+    <t>停駕東北村龍鳳宮,休息10分鐘</t>
+  </si>
+  <si>
+    <t>停駕東勢賜安宮,休息10分鐘</t>
+  </si>
+  <si>
+    <t>中山路24之1號停駕,休息6分鐘</t>
+  </si>
+  <si>
+    <t>停駕於真武殿牌樓後設置的臨時棚架,休息18分鐘</t>
+  </si>
+  <si>
+    <t>北港朝天宮千順將軍入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮三十六執士入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮頭旗入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮媽祖大轎入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮拜天公</t>
+  </si>
+  <si>
+    <t>「逗陣迓媽祖」團隊設立之臨時帳棚停駕</t>
+  </si>
+  <si>
+    <t>客厝國小停駕午休</t>
+  </si>
+  <si>
+    <t>客厝國小起駕</t>
+  </si>
+  <si>
+    <t>鹿寮朝鳳宮簡易行館停駕</t>
+  </si>
+  <si>
+    <t>揚子中學活動中心駐駕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">揚子中學活動中心起駕 </t>
+  </si>
+  <si>
+    <t>廉使里永興宮停駕</t>
+  </si>
+  <si>
+    <t>吳厝朝興宮停駕</t>
+  </si>
+  <si>
+    <t>魚寮鎮南宮停駕</t>
+  </si>
+  <si>
+    <t>西螺建興辦事處停駕</t>
+  </si>
+  <si>
+    <t>西螺福興宮停駕</t>
+  </si>
+  <si>
+    <t>駐駕北斗奠安宮</t>
+  </si>
+  <si>
+    <t>北斗奠安宮起駕</t>
+  </si>
+  <si>
+    <t>停駕北斗自助餐（中山路二段林家白沙屯媽祖）</t>
+  </si>
+  <si>
+    <t>停駕永靖碧天宮忠義堂</t>
+  </si>
+  <si>
+    <t>停駕楓康超市員林店門口</t>
+  </si>
+  <si>
+    <t>大村國中川堂禮義廉恥匾下停駕</t>
+  </si>
+  <si>
+    <t>停駕花壇鄉公所午休</t>
+  </si>
+  <si>
+    <t>停駕白沙屯媽祖花壇聯誼會創始會館（易晁工業／中山路二段493號）</t>
+  </si>
+  <si>
+    <t>駐駕彰化市現代汽車（南陽汽車）</t>
+  </si>
+  <si>
+    <t>彰化市現代汽車（南陽汽車）起駕</t>
+  </si>
+  <si>
+    <t>停駕吉雄汽車百貨（沙田路一段148之8號）</t>
+  </si>
+  <si>
+    <t>大肚公有零售市場（沙田路二段707號）停駕</t>
+  </si>
+  <si>
+    <t>停駕建成鋼鐵（沙田路四段104號）</t>
+  </si>
+  <si>
+    <t>停駕山腳社區空地</t>
+  </si>
+  <si>
+    <t>停駕沙鹿光田綜合醫院</t>
+  </si>
+  <si>
+    <t>停駕土地銀行沙鹿分行</t>
+  </si>
+  <si>
+    <t>停駕鹿寮台新服飾行（本年度香燈腳服裝製作公司）</t>
+  </si>
+  <si>
+    <t>停駕「市場聯誼會」（臺中各市場組織而成的聯誼會）</t>
+  </si>
+  <si>
+    <t>停駕清水紫雲巖</t>
+  </si>
+  <si>
+    <t>駐駕大甲洪發芋頭總店（大甲經國路農安街交叉口）</t>
+  </si>
+  <si>
+    <t>大甲洪發芋頭總店起駕</t>
+  </si>
+  <si>
+    <t>停駕賜海汽車商行</t>
+  </si>
+  <si>
+    <t>至青一路民宅停駕</t>
+  </si>
+  <si>
+    <t>停駕立泰水泥（苗栗縣苑裡鎮新復里50號）</t>
+  </si>
+  <si>
+    <t>停駕於順心意點心會帳棚</t>
+  </si>
+  <si>
+    <t>停駕苑裡慈和宮（中山路305號）</t>
+  </si>
+  <si>
+    <t>通霄慶雲寺臨時帳棚（五南37號附近）停駕</t>
+  </si>
+  <si>
+    <t>停駕通南里臨時帳棚</t>
+  </si>
+  <si>
+    <t>通霄火車站前圓環停駕</t>
+  </si>
+  <si>
+    <t>進通霄國中賜福</t>
+  </si>
+  <si>
+    <t>離開通霄國中</t>
+  </si>
+  <si>
+    <t>駐駕通灣慈后宮</t>
+  </si>
+  <si>
+    <t>通灣慈后宮起駕</t>
+  </si>
+  <si>
+    <t>秋茂園請出兩尊媽祖換轎</t>
+  </si>
+  <si>
+    <t>八人大轎起駕</t>
+  </si>
+  <si>
+    <t>內島里1鄰9號前空地停轎駕（休息至10：30）</t>
+  </si>
+  <si>
+    <t>停駕於通霄白沙屯郵局旁（通霄鎮白東里142號）</t>
+  </si>
+  <si>
+    <t>白沙屯拱天宮回宮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">停駕王功福海宮晚餐 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新街北辰派出所停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港媽祖醫院停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港朝天宮起駕</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2561,7 +3151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2731,6 +3321,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -3161,7 +3758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3175,6 +3772,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -14073,4 +14679,3051 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B457FF62-E3A4-47CC-8DF9-D106DD661FD9}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F6E3BB-BB0B-4022-9C9D-00F71C4EF075}">
+  <dimension ref="A1:I105"/>
+  <sheetFormatPr defaultRowHeight="20.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="82" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="6"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" t="s">
+        <v>546</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="7" t="str">
+        <f>MID(F3, 10, LEN(F3))</f>
+        <v>61西濱快速公路交叉處</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9052C6FC-00DE-4D0C-BF9A-9386EFC11812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB8DCA6-2A74-4493-945C-14CB79CEF298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="7" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
@@ -22,6 +22,9 @@
     <sheet name="2019" sheetId="8" r:id="rId7"/>
     <sheet name="2018" sheetId="10" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2018'!$A$1:$G$105</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="876">
   <si>
     <t>年份</t>
   </si>
@@ -2939,211 +2942,215 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>在台61西濱高架橋下路旁停駕</t>
+  </si>
+  <si>
+    <t>停駕伸港福安宮午休</t>
+  </si>
+  <si>
+    <t>伸港福安宮起駕</t>
+  </si>
+  <si>
+    <t>大慶公司停駕</t>
+  </si>
+  <si>
+    <t>台61西濱快速公路、152縣道（橋墩P156）路口停駕</t>
+  </si>
+  <si>
+    <t>停駕東北村龍鳳宮,休息10分鐘</t>
+  </si>
+  <si>
+    <t>停駕東勢賜安宮,休息10分鐘</t>
+  </si>
+  <si>
+    <t>中山路24之1號停駕,休息6分鐘</t>
+  </si>
+  <si>
+    <t>停駕於真武殿牌樓後設置的臨時棚架,休息18分鐘</t>
+  </si>
+  <si>
+    <t>北港朝天宮千順將軍入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮三十六執士入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮頭旗入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮媽祖大轎入廟</t>
+  </si>
+  <si>
+    <t>北港朝天宮拜天公</t>
+  </si>
+  <si>
+    <t>客厝國小停駕午休</t>
+  </si>
+  <si>
+    <t>客厝國小起駕</t>
+  </si>
+  <si>
+    <t>鹿寮朝鳳宮簡易行館停駕</t>
+  </si>
+  <si>
+    <t>揚子中學活動中心駐駕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">揚子中學活動中心起駕 </t>
+  </si>
+  <si>
+    <t>廉使里永興宮停駕</t>
+  </si>
+  <si>
+    <t>吳厝朝興宮停駕</t>
+  </si>
+  <si>
+    <t>魚寮鎮南宮停駕</t>
+  </si>
+  <si>
+    <t>西螺建興辦事處停駕</t>
+  </si>
+  <si>
+    <t>西螺福興宮停駕</t>
+  </si>
+  <si>
+    <t>駐駕北斗奠安宮</t>
+  </si>
+  <si>
+    <t>北斗奠安宮起駕</t>
+  </si>
+  <si>
+    <t>停駕北斗自助餐（中山路二段林家白沙屯媽祖）</t>
+  </si>
+  <si>
+    <t>停駕永靖碧天宮忠義堂</t>
+  </si>
+  <si>
+    <t>停駕楓康超市員林店門口</t>
+  </si>
+  <si>
+    <t>大村國中川堂禮義廉恥匾下停駕</t>
+  </si>
+  <si>
+    <t>停駕花壇鄉公所午休</t>
+  </si>
+  <si>
+    <t>停駕白沙屯媽祖花壇聯誼會創始會館（易晁工業／中山路二段493號）</t>
+  </si>
+  <si>
+    <t>彰化市現代汽車（南陽汽車）起駕</t>
+  </si>
+  <si>
+    <t>停駕吉雄汽車百貨（沙田路一段148之8號）</t>
+  </si>
+  <si>
+    <t>大肚公有零售市場（沙田路二段707號）停駕</t>
+  </si>
+  <si>
+    <t>停駕建成鋼鐵（沙田路四段104號）</t>
+  </si>
+  <si>
+    <t>停駕山腳社區空地</t>
+  </si>
+  <si>
+    <t>停駕沙鹿光田綜合醫院</t>
+  </si>
+  <si>
+    <t>停駕土地銀行沙鹿分行</t>
+  </si>
+  <si>
+    <t>停駕鹿寮台新服飾行（本年度香燈腳服裝製作公司）</t>
+  </si>
+  <si>
+    <t>停駕「市場聯誼會」（臺中各市場組織而成的聯誼會）</t>
+  </si>
+  <si>
+    <t>停駕清水紫雲巖</t>
+  </si>
+  <si>
+    <t>大甲洪發芋頭總店起駕</t>
+  </si>
+  <si>
+    <t>停駕賜海汽車商行</t>
+  </si>
+  <si>
+    <t>至青一路民宅停駕</t>
+  </si>
+  <si>
+    <t>停駕立泰水泥（苗栗縣苑裡鎮新復里50號）</t>
+  </si>
+  <si>
+    <t>停駕於順心意點心會帳棚</t>
+  </si>
+  <si>
+    <t>停駕苑裡慈和宮（中山路305號）</t>
+  </si>
+  <si>
+    <t>通霄慶雲寺臨時帳棚（五南37號附近）停駕</t>
+  </si>
+  <si>
+    <t>停駕通南里臨時帳棚</t>
+  </si>
+  <si>
+    <t>通霄火車站前圓環停駕</t>
+  </si>
+  <si>
+    <t>進通霄國中賜福</t>
+  </si>
+  <si>
+    <t>離開通霄國中</t>
+  </si>
+  <si>
+    <t>駐駕通灣慈后宮</t>
+  </si>
+  <si>
+    <t>通灣慈后宮起駕</t>
+  </si>
+  <si>
+    <t>秋茂園請出兩尊媽祖換轎</t>
+  </si>
+  <si>
+    <t>八人大轎起駕</t>
+  </si>
+  <si>
+    <t>內島里1鄰9號前空地停轎駕（休息至10：30）</t>
+  </si>
+  <si>
+    <t>停駕於通霄白沙屯郵局旁（通霄鎮白東里142號）</t>
+  </si>
+  <si>
+    <t>白沙屯拱天宮回宮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">停駕王功福海宮晚餐 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新街北辰派出所停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港媽祖醫院停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港朝天宮起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>駐駕彰化市現代汽車(南陽汽車)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>駐駕大甲洪發芋頭總店(大甲經國路農安街交叉口)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>逗陣迓媽祖團隊設立之臨時帳棚停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>停駕龜殼村路口、台61西濱快速公路交叉處</t>
-  </si>
-  <si>
-    <t>在台61西濱高架橋下路旁停駕</t>
-  </si>
-  <si>
-    <t>停駕伸港福安宮午休</t>
-  </si>
-  <si>
-    <t>伸港福安宮起駕</t>
-  </si>
-  <si>
-    <t>大慶公司停駕</t>
-  </si>
-  <si>
-    <t>台61西濱快速公路、152縣道（橋墩P156）路口停駕</t>
-  </si>
-  <si>
-    <t>停駕東北村龍鳳宮,休息10分鐘</t>
-  </si>
-  <si>
-    <t>停駕東勢賜安宮,休息10分鐘</t>
-  </si>
-  <si>
-    <t>中山路24之1號停駕,休息6分鐘</t>
-  </si>
-  <si>
-    <t>停駕於真武殿牌樓後設置的臨時棚架,休息18分鐘</t>
-  </si>
-  <si>
-    <t>北港朝天宮千順將軍入廟</t>
-  </si>
-  <si>
-    <t>北港朝天宮三十六執士入廟</t>
-  </si>
-  <si>
-    <t>北港朝天宮頭旗入廟</t>
-  </si>
-  <si>
-    <t>北港朝天宮媽祖大轎入廟</t>
-  </si>
-  <si>
-    <t>北港朝天宮拜天公</t>
-  </si>
-  <si>
-    <t>「逗陣迓媽祖」團隊設立之臨時帳棚停駕</t>
-  </si>
-  <si>
-    <t>客厝國小停駕午休</t>
-  </si>
-  <si>
-    <t>客厝國小起駕</t>
-  </si>
-  <si>
-    <t>鹿寮朝鳳宮簡易行館停駕</t>
-  </si>
-  <si>
-    <t>揚子中學活動中心駐駕</t>
-  </si>
-  <si>
-    <t xml:space="preserve">揚子中學活動中心起駕 </t>
-  </si>
-  <si>
-    <t>廉使里永興宮停駕</t>
-  </si>
-  <si>
-    <t>吳厝朝興宮停駕</t>
-  </si>
-  <si>
-    <t>魚寮鎮南宮停駕</t>
-  </si>
-  <si>
-    <t>西螺建興辦事處停駕</t>
-  </si>
-  <si>
-    <t>西螺福興宮停駕</t>
-  </si>
-  <si>
-    <t>駐駕北斗奠安宮</t>
-  </si>
-  <si>
-    <t>北斗奠安宮起駕</t>
-  </si>
-  <si>
-    <t>停駕北斗自助餐（中山路二段林家白沙屯媽祖）</t>
-  </si>
-  <si>
-    <t>停駕永靖碧天宮忠義堂</t>
-  </si>
-  <si>
-    <t>停駕楓康超市員林店門口</t>
-  </si>
-  <si>
-    <t>大村國中川堂禮義廉恥匾下停駕</t>
-  </si>
-  <si>
-    <t>停駕花壇鄉公所午休</t>
-  </si>
-  <si>
-    <t>停駕白沙屯媽祖花壇聯誼會創始會館（易晁工業／中山路二段493號）</t>
-  </si>
-  <si>
-    <t>駐駕彰化市現代汽車（南陽汽車）</t>
-  </si>
-  <si>
-    <t>彰化市現代汽車（南陽汽車）起駕</t>
-  </si>
-  <si>
-    <t>停駕吉雄汽車百貨（沙田路一段148之8號）</t>
-  </si>
-  <si>
-    <t>大肚公有零售市場（沙田路二段707號）停駕</t>
-  </si>
-  <si>
-    <t>停駕建成鋼鐵（沙田路四段104號）</t>
-  </si>
-  <si>
-    <t>停駕山腳社區空地</t>
-  </si>
-  <si>
-    <t>停駕沙鹿光田綜合醫院</t>
-  </si>
-  <si>
-    <t>停駕土地銀行沙鹿分行</t>
-  </si>
-  <si>
-    <t>停駕鹿寮台新服飾行（本年度香燈腳服裝製作公司）</t>
-  </si>
-  <si>
-    <t>停駕「市場聯誼會」（臺中各市場組織而成的聯誼會）</t>
-  </si>
-  <si>
-    <t>停駕清水紫雲巖</t>
-  </si>
-  <si>
-    <t>駐駕大甲洪發芋頭總店（大甲經國路農安街交叉口）</t>
-  </si>
-  <si>
-    <t>大甲洪發芋頭總店起駕</t>
-  </si>
-  <si>
-    <t>停駕賜海汽車商行</t>
-  </si>
-  <si>
-    <t>至青一路民宅停駕</t>
-  </si>
-  <si>
-    <t>停駕立泰水泥（苗栗縣苑裡鎮新復里50號）</t>
-  </si>
-  <si>
-    <t>停駕於順心意點心會帳棚</t>
-  </si>
-  <si>
-    <t>停駕苑裡慈和宮（中山路305號）</t>
-  </si>
-  <si>
-    <t>通霄慶雲寺臨時帳棚（五南37號附近）停駕</t>
-  </si>
-  <si>
-    <t>停駕通南里臨時帳棚</t>
-  </si>
-  <si>
-    <t>通霄火車站前圓環停駕</t>
-  </si>
-  <si>
-    <t>進通霄國中賜福</t>
-  </si>
-  <si>
-    <t>離開通霄國中</t>
-  </si>
-  <si>
-    <t>駐駕通灣慈后宮</t>
-  </si>
-  <si>
-    <t>通灣慈后宮起駕</t>
-  </si>
-  <si>
-    <t>秋茂園請出兩尊媽祖換轎</t>
-  </si>
-  <si>
-    <t>八人大轎起駕</t>
-  </si>
-  <si>
-    <t>內島里1鄰9號前空地停轎駕（休息至10：30）</t>
-  </si>
-  <si>
-    <t>停駕於通霄白沙屯郵局旁（通霄鎮白東里142號）</t>
-  </si>
-  <si>
-    <t>白沙屯拱天宮回宮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">停駕王功福海宮晚餐 </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>新街北辰派出所停駕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>北港媽祖醫院停駕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>北港朝天宮起駕</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3758,7 +3765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3774,13 +3781,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15281,36 +15282,34 @@
     <col min="5" max="5" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="82" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="6"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15337,7 +15336,7 @@
       <c r="H2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I2" s="6"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15356,12 +15355,15 @@
         <v>715</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>808</v>
+        <v>875</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="7" t="str">
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5" t="str">
         <f>MID(F3, 10, LEN(F3))</f>
         <v>61西濱快速公路交叉處</v>
       </c>
@@ -15388,7 +15390,7 @@
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -15407,12 +15409,15 @@
         <v>717</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -15436,7 +15441,7 @@
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -15455,12 +15460,15 @@
         <v>719</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="H7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -15479,12 +15487,12 @@
         <v>720</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -15503,12 +15511,15 @@
         <v>721</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="H9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -15527,12 +15538,15 @@
         <v>722</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="6"/>
+      <c r="H10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -15556,7 +15570,7 @@
       <c r="G11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -15575,12 +15589,15 @@
         <v>724</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="6"/>
+      <c r="H12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -15622,10 +15639,13 @@
         <v>726</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15645,10 +15665,13 @@
         <v>727</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15668,13 +15691,16 @@
         <v>728</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>712</v>
       </c>
@@ -15691,13 +15717,16 @@
         <v>729</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>712</v>
       </c>
@@ -15714,13 +15743,16 @@
         <v>730</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>712</v>
       </c>
@@ -15743,7 +15775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>712</v>
       </c>
@@ -15760,13 +15792,13 @@
         <v>732</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>712</v>
       </c>
@@ -15783,13 +15815,13 @@
         <v>733</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>712</v>
       </c>
@@ -15806,13 +15838,13 @@
         <v>734</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>712</v>
       </c>
@@ -15829,13 +15861,13 @@
         <v>735</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>712</v>
       </c>
@@ -15852,13 +15884,13 @@
         <v>736</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>712</v>
       </c>
@@ -15875,13 +15907,13 @@
         <v>737</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>712</v>
       </c>
@@ -15898,13 +15930,16 @@
         <v>738</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>712</v>
       </c>
@@ -15927,7 +15962,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>712</v>
       </c>
@@ -15944,13 +15979,16 @@
         <v>740</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>823</v>
+        <v>874</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>712</v>
       </c>
@@ -15967,13 +16005,13 @@
         <v>741</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>711</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>712</v>
       </c>
@@ -15990,13 +16028,16 @@
         <v>742</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>712</v>
       </c>
@@ -16013,13 +16054,13 @@
         <v>743</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>712</v>
       </c>
@@ -16036,13 +16077,16 @@
         <v>744</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>712</v>
       </c>
@@ -16065,7 +16109,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>712</v>
       </c>
@@ -16082,13 +16126,16 @@
         <v>745</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>712</v>
       </c>
@@ -16105,13 +16152,13 @@
         <v>746</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>712</v>
       </c>
@@ -16128,13 +16175,16 @@
         <v>747</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>712</v>
       </c>
@@ -16157,7 +16207,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>712</v>
       </c>
@@ -16174,13 +16224,16 @@
         <v>749</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>712</v>
       </c>
@@ -16203,7 +16256,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>712</v>
       </c>
@@ -16220,13 +16273,16 @@
         <v>751</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>712</v>
       </c>
@@ -16249,7 +16305,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>712</v>
       </c>
@@ -16266,13 +16322,16 @@
         <v>753</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>712</v>
       </c>
@@ -16295,7 +16354,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>712</v>
       </c>
@@ -16312,13 +16371,16 @@
         <v>755</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>712</v>
       </c>
@@ -16341,7 +16403,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>712</v>
       </c>
@@ -16358,13 +16420,16 @@
         <v>757</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>712</v>
       </c>
@@ -16381,13 +16446,13 @@
         <v>746</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>712</v>
       </c>
@@ -16404,13 +16469,16 @@
         <v>758</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>712</v>
       </c>
@@ -16427,13 +16495,16 @@
         <v>759</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>712</v>
       </c>
@@ -16450,13 +16521,16 @@
         <v>760</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>712</v>
       </c>
@@ -16473,13 +16547,16 @@
         <v>761</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>712</v>
       </c>
@@ -16502,7 +16579,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>712</v>
       </c>
@@ -16519,13 +16596,16 @@
         <v>763</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>712</v>
       </c>
@@ -16548,7 +16628,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>712</v>
       </c>
@@ -16565,13 +16645,16 @@
         <v>765</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>712</v>
       </c>
@@ -16594,7 +16677,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>712</v>
       </c>
@@ -16611,13 +16694,16 @@
         <v>767</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>712</v>
       </c>
@@ -16634,13 +16720,13 @@
         <v>746</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>712</v>
       </c>
@@ -16657,13 +16743,16 @@
         <v>768</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>712</v>
       </c>
@@ -16686,7 +16775,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>712</v>
       </c>
@@ -16703,13 +16792,16 @@
         <v>769</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>712</v>
       </c>
@@ -16732,7 +16824,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>712</v>
       </c>
@@ -16749,13 +16841,16 @@
         <v>770</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>712</v>
       </c>
@@ -16778,7 +16873,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>712</v>
       </c>
@@ -16795,13 +16890,16 @@
         <v>772</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>712</v>
       </c>
@@ -16824,7 +16922,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>712</v>
       </c>
@@ -16841,13 +16939,16 @@
         <v>774</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H67" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>712</v>
       </c>
@@ -16870,7 +16971,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>712</v>
       </c>
@@ -16887,13 +16988,16 @@
         <v>776</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>712</v>
       </c>
@@ -16916,7 +17020,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>712</v>
       </c>
@@ -16933,13 +17037,16 @@
         <v>778</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>712</v>
       </c>
@@ -16962,7 +17069,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>712</v>
       </c>
@@ -16979,13 +17086,16 @@
         <v>780</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>712</v>
       </c>
@@ -17008,7 +17118,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>712</v>
       </c>
@@ -17025,13 +17135,16 @@
         <v>782</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>712</v>
       </c>
@@ -17054,7 +17167,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>712</v>
       </c>
@@ -17071,13 +17184,16 @@
         <v>784</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H77" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>712</v>
       </c>
@@ -17094,13 +17210,13 @@
         <v>34</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>712</v>
       </c>
@@ -17117,13 +17233,16 @@
         <v>785</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>712</v>
       </c>
@@ -17146,7 +17265,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>712</v>
       </c>
@@ -17163,13 +17282,16 @@
         <v>787</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H81" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>712</v>
       </c>
@@ -17192,7 +17314,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>712</v>
       </c>
@@ -17209,13 +17331,16 @@
         <v>789</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>712</v>
       </c>
@@ -17238,7 +17363,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>712</v>
       </c>
@@ -17255,13 +17380,16 @@
         <v>791</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>712</v>
       </c>
@@ -17284,7 +17412,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>712</v>
       </c>
@@ -17301,13 +17429,16 @@
         <v>752</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H87" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>712</v>
       </c>
@@ -17330,7 +17461,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>712</v>
       </c>
@@ -17347,13 +17478,16 @@
         <v>794</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>712</v>
       </c>
@@ -17376,7 +17510,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>712</v>
       </c>
@@ -17393,13 +17527,16 @@
         <v>719</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H91" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>712</v>
       </c>
@@ -17422,7 +17559,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>712</v>
       </c>
@@ -17439,13 +17576,16 @@
         <v>797</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>712</v>
       </c>
@@ -17468,7 +17608,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>712</v>
       </c>
@@ -17485,13 +17625,13 @@
         <v>744</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>712</v>
       </c>
@@ -17508,13 +17648,13 @@
         <v>764</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>712</v>
       </c>
@@ -17531,13 +17671,16 @@
         <v>766</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>712</v>
       </c>
@@ -17554,13 +17697,13 @@
         <v>799</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>712</v>
       </c>
@@ -17577,13 +17720,13 @@
         <v>800</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>712</v>
       </c>
@@ -17600,13 +17743,13 @@
         <v>801</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>712</v>
       </c>
@@ -17623,13 +17766,13 @@
         <v>802</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>712</v>
       </c>
@@ -17652,7 +17795,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>712</v>
       </c>
@@ -17669,13 +17812,16 @@
         <v>804</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H103" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>712</v>
       </c>
@@ -17698,7 +17844,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>712</v>
       </c>
@@ -17715,10 +17861,13 @@
         <v>806</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>166</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB8DCA6-2A74-4493-945C-14CB79CEF298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE27CF0-0823-48E7-A10D-3246AAE32C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="7" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="866">
   <si>
     <t>年份</t>
   </si>
@@ -2659,285 +2659,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>23：40</t>
-  </si>
-  <si>
-    <t>05：50</t>
-  </si>
-  <si>
-    <t>06：13</t>
-  </si>
-  <si>
-    <t>08：54</t>
-  </si>
-  <si>
-    <t>09：05</t>
-  </si>
-  <si>
-    <t>11：47</t>
-  </si>
-  <si>
-    <t>12：58</t>
-  </si>
-  <si>
-    <t>15：48</t>
-  </si>
-  <si>
-    <t>20：25</t>
-  </si>
-  <si>
-    <t>21：28</t>
-  </si>
-  <si>
-    <t>23：49</t>
-  </si>
-  <si>
-    <t>00：02</t>
-  </si>
-  <si>
-    <t>04：50</t>
-  </si>
-  <si>
-    <t>05：15</t>
-  </si>
-  <si>
-    <t>07：26</t>
-  </si>
-  <si>
-    <t>09：10</t>
-  </si>
-  <si>
-    <t>10：18</t>
-  </si>
-  <si>
-    <t>10：58</t>
-  </si>
-  <si>
-    <t>11：57</t>
-  </si>
-  <si>
-    <t>12：01</t>
-  </si>
-  <si>
-    <t>12：06</t>
-  </si>
-  <si>
-    <t>12：07</t>
-  </si>
-  <si>
-    <t>15：00</t>
-  </si>
-  <si>
-    <t>07：25</t>
-  </si>
-  <si>
-    <t>08：50</t>
-  </si>
-  <si>
-    <t>09：04</t>
-  </si>
-  <si>
-    <t>10：25</t>
-  </si>
-  <si>
-    <t>10：35</t>
-  </si>
-  <si>
-    <t>11：35</t>
-  </si>
-  <si>
-    <t>13：55</t>
-  </si>
-  <si>
-    <t>14：49</t>
-  </si>
-  <si>
-    <t>18：31</t>
-  </si>
-  <si>
-    <t>05：00</t>
-  </si>
-  <si>
-    <t>06：21</t>
-  </si>
-  <si>
-    <t>06：41</t>
-  </si>
-  <si>
-    <t>07：49</t>
-  </si>
-  <si>
-    <t>08：18</t>
-  </si>
-  <si>
-    <t>09：23</t>
-  </si>
-  <si>
-    <t>09：49</t>
-  </si>
-  <si>
-    <t>10：21</t>
-  </si>
-  <si>
-    <t>10：40</t>
-  </si>
-  <si>
-    <t>11：50</t>
-  </si>
-  <si>
-    <t>14：32</t>
-  </si>
-  <si>
-    <t>18：30</t>
-  </si>
-  <si>
-    <t>05：44</t>
-  </si>
-  <si>
-    <t>06：52</t>
-  </si>
-  <si>
-    <t>09：17</t>
-  </si>
-  <si>
-    <t>10：26</t>
-  </si>
-  <si>
-    <t>10：39</t>
-  </si>
-  <si>
-    <t>12：17</t>
-  </si>
-  <si>
-    <t>14：58</t>
-  </si>
-  <si>
-    <t>15：23</t>
-  </si>
-  <si>
-    <t>15：36</t>
-  </si>
-  <si>
-    <t>17：59</t>
-  </si>
-  <si>
-    <t>05：59</t>
-  </si>
-  <si>
-    <t>07：46</t>
-  </si>
-  <si>
-    <t>08：56</t>
-  </si>
-  <si>
-    <t>09：08</t>
-  </si>
-  <si>
-    <t>10：11</t>
-  </si>
-  <si>
-    <t>10：37</t>
-  </si>
-  <si>
-    <t>11：30</t>
-  </si>
-  <si>
-    <t>11：38</t>
-  </si>
-  <si>
-    <t>11：51</t>
-  </si>
-  <si>
-    <t>14：29</t>
-  </si>
-  <si>
-    <t>14：52</t>
-  </si>
-  <si>
-    <t>15：06</t>
-  </si>
-  <si>
-    <t>15：20</t>
-  </si>
-  <si>
-    <t>15：35</t>
-  </si>
-  <si>
-    <t>16：27</t>
-  </si>
-  <si>
-    <t>16：45</t>
-  </si>
-  <si>
-    <t>19：29</t>
-  </si>
-  <si>
-    <t>06：05</t>
-  </si>
-  <si>
-    <t>06：17</t>
-  </si>
-  <si>
-    <t>07：10</t>
-  </si>
-  <si>
-    <t>07：24</t>
-  </si>
-  <si>
-    <t>07：50</t>
-  </si>
-  <si>
-    <t>08：01</t>
-  </si>
-  <si>
-    <t>08：17</t>
-  </si>
-  <si>
-    <t>08：28</t>
-  </si>
-  <si>
-    <t>10：10</t>
-  </si>
-  <si>
-    <t>10：56</t>
-  </si>
-  <si>
-    <t>11：16</t>
-  </si>
-  <si>
-    <t>13：58</t>
-  </si>
-  <si>
-    <t>14：31</t>
-  </si>
-  <si>
-    <t>14：41</t>
-  </si>
-  <si>
-    <t>06：59</t>
-  </si>
-  <si>
-    <t>08：26</t>
-  </si>
-  <si>
-    <t>08：33</t>
-  </si>
-  <si>
-    <t>09：48</t>
-  </si>
-  <si>
-    <t>10：28</t>
-  </si>
-  <si>
-    <t>10：43</t>
-  </si>
-  <si>
-    <t>13：29</t>
-  </si>
-  <si>
-    <t>14：20</t>
-  </si>
-  <si>
     <t xml:space="preserve">白沙屯拱天宮           </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -3074,83 +2795,416 @@
     <t>停駕賜海汽車商行</t>
   </si>
   <si>
+    <t>停駕立泰水泥（苗栗縣苑裡鎮新復里50號）</t>
+  </si>
+  <si>
+    <t>停駕於順心意點心會帳棚</t>
+  </si>
+  <si>
+    <t>停駕苑裡慈和宮（中山路305號）</t>
+  </si>
+  <si>
+    <t>通霄慶雲寺臨時帳棚（五南37號附近）停駕</t>
+  </si>
+  <si>
+    <t>停駕通南里臨時帳棚</t>
+  </si>
+  <si>
+    <t>通霄火車站前圓環停駕</t>
+  </si>
+  <si>
+    <t>進通霄國中賜福</t>
+  </si>
+  <si>
+    <t>離開通霄國中</t>
+  </si>
+  <si>
+    <t>駐駕通灣慈后宮</t>
+  </si>
+  <si>
+    <t>通灣慈后宮起駕</t>
+  </si>
+  <si>
+    <t>秋茂園請出兩尊媽祖換轎</t>
+  </si>
+  <si>
+    <t>八人大轎起駕</t>
+  </si>
+  <si>
+    <t>內島里1鄰9號前空地停轎駕（休息至10：30）</t>
+  </si>
+  <si>
+    <t>停駕於通霄白沙屯郵局旁（通霄鎮白東里142號）</t>
+  </si>
+  <si>
+    <t>白沙屯拱天宮回宮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">停駕王功福海宮晚餐 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新街北辰派出所停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港媽祖醫院停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港朝天宮起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>駐駕彰化市現代汽車(南陽汽車)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>駐駕大甲洪發芋頭總店(大甲經國路農安街交叉口)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>逗陣迓媽祖團隊設立之臨時帳棚停駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>停駕龜殼村路口、台61西濱快速公路交叉處</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>05:50</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:13</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:54</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:05</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:47</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:58</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:48</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20:25</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>21:28</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>23:49</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>00:02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>04:50</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>05:15</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:20</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:29</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:43</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:28</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:48</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:33</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:26</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:59</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:36</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:49</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:41</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:31</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:58</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:16</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:56</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:49</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:28</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:17</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:50</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:24</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>至青一路民宅停駕</t>
-  </si>
-  <si>
-    <t>停駕立泰水泥（苗栗縣苑裡鎮新復里50號）</t>
-  </si>
-  <si>
-    <t>停駕於順心意點心會帳棚</t>
-  </si>
-  <si>
-    <t>停駕苑裡慈和宮（中山路305號）</t>
-  </si>
-  <si>
-    <t>通霄慶雲寺臨時帳棚（五南37號附近）停駕</t>
-  </si>
-  <si>
-    <t>停駕通南里臨時帳棚</t>
-  </si>
-  <si>
-    <t>通霄火車站前圓環停駕</t>
-  </si>
-  <si>
-    <t>進通霄國中賜福</t>
-  </si>
-  <si>
-    <t>離開通霄國中</t>
-  </si>
-  <si>
-    <t>駐駕通灣慈后宮</t>
-  </si>
-  <si>
-    <t>通灣慈后宮起駕</t>
-  </si>
-  <si>
-    <t>秋茂園請出兩尊媽祖換轎</t>
-  </si>
-  <si>
-    <t>八人大轎起駕</t>
-  </si>
-  <si>
-    <t>內島里1鄰9號前空地停轎駕（休息至10：30）</t>
-  </si>
-  <si>
-    <t>停駕於通霄白沙屯郵局旁（通霄鎮白東里142號）</t>
-  </si>
-  <si>
-    <t>白沙屯拱天宮回宮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">停駕王功福海宮晚餐 </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>新街北辰派出所停駕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>北港媽祖醫院停駕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>北港朝天宮起駕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>駐駕彰化市現代汽車(南陽汽車)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>駐駕大甲洪發芋頭總店(大甲經國路農安街交叉口)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>逗陣迓媽祖團隊設立之臨時帳棚停駕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>停駕龜殼村路口、台61西濱快速公路交叉處</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:17</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:05</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>19:29</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:27</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:35</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:06</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:56</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:08</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:26</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:18</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:58</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:57</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:06</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:07</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:25</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:50</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:04</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:52</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:29</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:51</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:38</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:37</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:11</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:18</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:46</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>05:59</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:59</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:23</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:17</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:39</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:26</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:17</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:52</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>05:44</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:32</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:50</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:40</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:23</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:49</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:41</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:25</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:35</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:55</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:31</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -15325,10 +15379,10 @@
         <v>138</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>807</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>13</v>
@@ -15352,10 +15406,10 @@
         <v>139</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>715</v>
+        <v>782</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>875</v>
+        <v>781</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -15382,7 +15436,7 @@
         <v>139</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>716</v>
+        <v>783</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>711</v>
@@ -15406,10 +15460,10 @@
         <v>139</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>717</v>
+        <v>784</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>808</v>
+        <v>715</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -15433,7 +15487,7 @@
         <v>139</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>718</v>
+        <v>785</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>711</v>
@@ -15457,10 +15511,10 @@
         <v>139</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>719</v>
+        <v>786</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>809</v>
+        <v>716</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -15484,10 +15538,10 @@
         <v>139</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>720</v>
+        <v>787</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>810</v>
+        <v>717</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -15508,10 +15562,10 @@
         <v>139</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>721</v>
+        <v>788</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>811</v>
+        <v>718</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -15535,10 +15589,10 @@
         <v>139</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>722</v>
+        <v>789</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>868</v>
+        <v>774</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
@@ -15562,7 +15616,7 @@
         <v>139</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>723</v>
+        <v>790</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>711</v>
@@ -15586,10 +15640,10 @@
         <v>139</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>724</v>
+        <v>791</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>812</v>
+        <v>719</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
@@ -15613,7 +15667,7 @@
         <v>168</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>725</v>
+        <v>792</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>711</v>
@@ -15636,10 +15690,10 @@
         <v>168</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>726</v>
+        <v>793</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>813</v>
+        <v>720</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
@@ -15662,10 +15716,10 @@
         <v>168</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>727</v>
+        <v>794</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>814</v>
+        <v>721</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -15688,10 +15742,10 @@
         <v>168</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>728</v>
+        <v>827</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>815</v>
+        <v>722</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
@@ -15714,10 +15768,10 @@
         <v>168</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>729</v>
+        <v>828</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>13</v>
@@ -15740,10 +15794,10 @@
         <v>168</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>730</v>
+        <v>829</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>869</v>
+        <v>775</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
@@ -15766,7 +15820,7 @@
         <v>168</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>731</v>
+        <v>830</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>711</v>
@@ -15789,10 +15843,10 @@
         <v>168</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>732</v>
+        <v>831</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>817</v>
+        <v>724</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>13</v>
@@ -15812,10 +15866,10 @@
         <v>168</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>733</v>
+        <v>832</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>818</v>
+        <v>725</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>13</v>
@@ -15835,10 +15889,10 @@
         <v>168</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>734</v>
+        <v>833</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>819</v>
+        <v>726</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>13</v>
@@ -15858,10 +15912,10 @@
         <v>168</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>735</v>
+        <v>834</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>820</v>
+        <v>727</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>13</v>
@@ -15881,10 +15935,10 @@
         <v>168</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>736</v>
+        <v>660</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>821</v>
+        <v>728</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>13</v>
@@ -15904,10 +15958,10 @@
         <v>179</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>737</v>
+        <v>835</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>871</v>
+        <v>777</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>166</v>
@@ -15927,10 +15981,10 @@
         <v>179</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>738</v>
+        <v>836</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>870</v>
+        <v>776</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>166</v>
@@ -15953,7 +16007,7 @@
         <v>179</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>739</v>
+        <v>837</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>711</v>
@@ -15976,10 +16030,10 @@
         <v>179</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>740</v>
+        <v>862</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>874</v>
+        <v>780</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>166</v>
@@ -16002,7 +16056,7 @@
         <v>179</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>741</v>
+        <v>99</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>14</v>
@@ -16025,10 +16079,10 @@
         <v>179</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>742</v>
+        <v>863</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>822</v>
+        <v>729</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>166</v>
@@ -16051,10 +16105,10 @@
         <v>179</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>743</v>
+        <v>864</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>823</v>
+        <v>730</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>166</v>
@@ -16074,10 +16128,10 @@
         <v>179</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>744</v>
+        <v>804</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>824</v>
+        <v>731</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>166</v>
@@ -16100,7 +16154,7 @@
         <v>179</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>736</v>
+        <v>660</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>14</v>
@@ -16123,10 +16177,10 @@
         <v>179</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>745</v>
+        <v>865</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>825</v>
+        <v>732</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>166</v>
@@ -16149,10 +16203,10 @@
         <v>188</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>746</v>
+        <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>826</v>
+        <v>733</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>166</v>
@@ -16172,10 +16226,10 @@
         <v>188</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>747</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>827</v>
+        <v>734</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>166</v>
@@ -16198,7 +16252,7 @@
         <v>188</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>748</v>
+        <v>861</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>14</v>
@@ -16221,10 +16275,10 @@
         <v>188</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>749</v>
+        <v>860</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>828</v>
+        <v>735</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>166</v>
@@ -16247,7 +16301,7 @@
         <v>188</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>750</v>
+        <v>845</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>14</v>
@@ -16270,10 +16324,10 @@
         <v>188</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>751</v>
+        <v>859</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>829</v>
+        <v>736</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>166</v>
@@ -16296,7 +16350,7 @@
         <v>188</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>752</v>
+        <v>811</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>14</v>
@@ -16319,10 +16373,10 @@
         <v>188</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>753</v>
+        <v>141</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>830</v>
+        <v>737</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>166</v>
@@ -16345,7 +16399,7 @@
         <v>188</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>754</v>
+        <v>858</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>14</v>
@@ -16368,10 +16422,10 @@
         <v>188</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>755</v>
+        <v>857</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>831</v>
+        <v>738</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>166</v>
@@ -16394,7 +16448,7 @@
         <v>188</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>756</v>
+        <v>856</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>14</v>
@@ -16417,10 +16471,10 @@
         <v>188</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>757</v>
+        <v>670</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>832</v>
+        <v>739</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>166</v>
@@ -16443,10 +16497,10 @@
         <v>196</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>746</v>
+        <v>34</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>833</v>
+        <v>740</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>166</v>
@@ -16466,10 +16520,10 @@
         <v>196</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>758</v>
+        <v>855</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>834</v>
+        <v>741</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>166</v>
@@ -16492,10 +16546,10 @@
         <v>196</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>759</v>
+        <v>854</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>835</v>
+        <v>742</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>166</v>
@@ -16518,10 +16572,10 @@
         <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>760</v>
+        <v>853</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>836</v>
+        <v>743</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>166</v>
@@ -16544,10 +16598,10 @@
         <v>196</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>761</v>
+        <v>852</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>837</v>
+        <v>744</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>166</v>
@@ -16570,7 +16624,7 @@
         <v>196</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>762</v>
+        <v>851</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>711</v>
@@ -16593,10 +16647,10 @@
         <v>196</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>763</v>
+        <v>850</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>838</v>
+        <v>745</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>166</v>
@@ -16619,7 +16673,7 @@
         <v>196</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>764</v>
+        <v>143</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>711</v>
@@ -16642,10 +16696,10 @@
         <v>196</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>765</v>
+        <v>849</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>839</v>
+        <v>746</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>166</v>
@@ -16668,7 +16722,7 @@
         <v>196</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>711</v>
@@ -16691,10 +16745,10 @@
         <v>196</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>767</v>
+        <v>848</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>872</v>
+        <v>778</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>166</v>
@@ -16717,10 +16771,10 @@
         <v>205</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>746</v>
+        <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>840</v>
+        <v>747</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>166</v>
@@ -16740,10 +16794,10 @@
         <v>205</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>768</v>
+        <v>847</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>841</v>
+        <v>748</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>166</v>
@@ -16766,7 +16820,7 @@
         <v>205</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>716</v>
+        <v>783</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>711</v>
@@ -16789,10 +16843,10 @@
         <v>205</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>769</v>
+        <v>846</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>842</v>
+        <v>749</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>166</v>
@@ -16815,7 +16869,7 @@
         <v>205</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>750</v>
+        <v>845</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>711</v>
@@ -16838,10 +16892,10 @@
         <v>205</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>770</v>
+        <v>825</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>843</v>
+        <v>750</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>166</v>
@@ -16864,7 +16918,7 @@
         <v>205</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>771</v>
+        <v>826</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>711</v>
@@ -16887,10 +16941,10 @@
         <v>205</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>772</v>
+        <v>844</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>844</v>
+        <v>751</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>166</v>
@@ -16913,7 +16967,7 @@
         <v>205</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>773</v>
+        <v>843</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>711</v>
@@ -16936,10 +16990,10 @@
         <v>205</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>774</v>
+        <v>842</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>845</v>
+        <v>752</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>166</v>
@@ -16962,7 +17016,7 @@
         <v>205</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>775</v>
+        <v>841</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>711</v>
@@ -16985,10 +17039,10 @@
         <v>205</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>776</v>
+        <v>840</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>846</v>
+        <v>753</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>166</v>
@@ -17011,7 +17065,7 @@
         <v>205</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>777</v>
+        <v>839</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>711</v>
@@ -17034,10 +17088,10 @@
         <v>205</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>778</v>
+        <v>838</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>847</v>
+        <v>754</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>166</v>
@@ -17060,7 +17114,7 @@
         <v>205</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>779</v>
+        <v>824</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>711</v>
@@ -17083,10 +17137,10 @@
         <v>205</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>780</v>
+        <v>681</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>848</v>
+        <v>755</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>166</v>
@@ -17109,7 +17163,7 @@
         <v>205</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>781</v>
+        <v>823</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>711</v>
@@ -17132,10 +17186,10 @@
         <v>205</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>782</v>
+        <v>822</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>849</v>
+        <v>756</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>166</v>
@@ -17158,7 +17212,7 @@
         <v>205</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>783</v>
+        <v>182</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>711</v>
@@ -17181,10 +17235,10 @@
         <v>205</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>873</v>
+        <v>779</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>166</v>
@@ -17210,7 +17264,7 @@
         <v>34</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>850</v>
+        <v>757</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>166</v>
@@ -17230,10 +17284,10 @@
         <v>211</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>785</v>
+        <v>820</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>851</v>
+        <v>758</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>166</v>
@@ -17256,7 +17310,7 @@
         <v>211</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>786</v>
+        <v>819</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>711</v>
@@ -17279,10 +17333,10 @@
         <v>211</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>852</v>
+        <v>818</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>166</v>
@@ -17305,7 +17359,7 @@
         <v>211</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>711</v>
@@ -17328,10 +17382,10 @@
         <v>211</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>789</v>
+        <v>815</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>853</v>
+        <v>759</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>166</v>
@@ -17354,7 +17408,7 @@
         <v>211</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>790</v>
+        <v>814</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>711</v>
@@ -17377,10 +17431,10 @@
         <v>211</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>854</v>
+        <v>760</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>166</v>
@@ -17403,7 +17457,7 @@
         <v>211</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>711</v>
@@ -17426,10 +17480,10 @@
         <v>211</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>752</v>
+        <v>811</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>855</v>
+        <v>761</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>166</v>
@@ -17452,7 +17506,7 @@
         <v>211</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>711</v>
@@ -17475,10 +17529,10 @@
         <v>211</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>856</v>
+        <v>762</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>166</v>
@@ -17501,7 +17555,7 @@
         <v>211</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>711</v>
@@ -17524,10 +17578,10 @@
         <v>211</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>719</v>
+        <v>786</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>857</v>
+        <v>763</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>166</v>
@@ -17550,7 +17604,7 @@
         <v>211</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>711</v>
@@ -17573,10 +17627,10 @@
         <v>211</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>858</v>
+        <v>764</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>166</v>
@@ -17599,7 +17653,7 @@
         <v>211</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>711</v>
@@ -17622,10 +17676,10 @@
         <v>211</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>744</v>
+        <v>804</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>859</v>
+        <v>765</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>166</v>
@@ -17645,10 +17699,10 @@
         <v>211</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>764</v>
+        <v>143</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>860</v>
+        <v>766</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>166</v>
@@ -17668,10 +17722,10 @@
         <v>211</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>861</v>
+        <v>767</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>166</v>
@@ -17694,10 +17748,10 @@
         <v>215</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>862</v>
+        <v>768</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>166</v>
@@ -17717,10 +17771,10 @@
         <v>215</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>863</v>
+        <v>769</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>166</v>
@@ -17740,10 +17794,10 @@
         <v>215</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>864</v>
+        <v>770</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>166</v>
@@ -17763,10 +17817,10 @@
         <v>215</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>865</v>
+        <v>771</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>166</v>
@@ -17786,7 +17840,7 @@
         <v>215</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>711</v>
@@ -17809,10 +17863,10 @@
         <v>215</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>866</v>
+        <v>772</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>166</v>
@@ -17835,7 +17889,7 @@
         <v>215</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>711</v>
@@ -17858,10 +17912,10 @@
         <v>215</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>867</v>
+        <v>773</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>166</v>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE27CF0-0823-48E7-A10D-3246AAE32C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D5886F-E93D-43E8-A01D-92E15CA4DE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="7" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
@@ -3819,7 +3819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3836,6 +3836,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15333,7 +15339,7 @@
     <col min="1" max="1" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="82" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="2"/>
@@ -15352,7 +15358,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -15378,7 +15384,7 @@
       <c r="D2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -15405,7 +15411,7 @@
       <c r="D3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>782</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -15435,7 +15441,7 @@
       <c r="D4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="7" t="s">
         <v>783</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -15459,7 +15465,7 @@
       <c r="D5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="7" t="s">
         <v>784</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -15486,7 +15492,7 @@
       <c r="D6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="7" t="s">
         <v>785</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -15510,7 +15516,7 @@
       <c r="D7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="7" t="s">
         <v>786</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -15537,7 +15543,7 @@
       <c r="D8" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="7" t="s">
         <v>787</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -15561,7 +15567,7 @@
       <c r="D9" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="7" t="s">
         <v>788</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -15588,7 +15594,7 @@
       <c r="D10" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="7" t="s">
         <v>789</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -15615,7 +15621,7 @@
       <c r="D11" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="7" t="s">
         <v>790</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -15639,7 +15645,7 @@
       <c r="D12" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="7" t="s">
         <v>791</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -15666,7 +15672,7 @@
       <c r="D13" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="7" t="s">
         <v>792</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -15689,7 +15695,7 @@
       <c r="D14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="7" t="s">
         <v>793</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -15715,7 +15721,7 @@
       <c r="D15" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="7" t="s">
         <v>794</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -15741,7 +15747,7 @@
       <c r="D16" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="7" t="s">
         <v>827</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -15767,7 +15773,7 @@
       <c r="D17" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="7" t="s">
         <v>828</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -15793,7 +15799,7 @@
       <c r="D18" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="7" t="s">
         <v>829</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -15819,7 +15825,7 @@
       <c r="D19" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="7" t="s">
         <v>830</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -15842,7 +15848,7 @@
       <c r="D20" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="7" t="s">
         <v>831</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -15865,7 +15871,7 @@
       <c r="D21" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="7" t="s">
         <v>832</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -15888,7 +15894,7 @@
       <c r="D22" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="7" t="s">
         <v>833</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -15911,7 +15917,7 @@
       <c r="D23" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="7" t="s">
         <v>834</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -15934,7 +15940,7 @@
       <c r="D24" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="7" t="s">
         <v>660</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -15957,7 +15963,7 @@
       <c r="D25" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="7" t="s">
         <v>835</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -15980,7 +15986,7 @@
       <c r="D26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="7" t="s">
         <v>836</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -16006,7 +16012,7 @@
       <c r="D27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="7" t="s">
         <v>837</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -16029,7 +16035,7 @@
       <c r="D28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="7" t="s">
         <v>862</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -16055,7 +16061,7 @@
       <c r="D29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="7" t="s">
         <v>99</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -16078,7 +16084,7 @@
       <c r="D30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="7" t="s">
         <v>863</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -16104,7 +16110,7 @@
       <c r="D31" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="7" t="s">
         <v>864</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -16127,7 +16133,7 @@
       <c r="D32" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="7" t="s">
         <v>804</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -16153,7 +16159,7 @@
       <c r="D33" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="7" t="s">
         <v>660</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -16176,7 +16182,7 @@
       <c r="D34" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="7" t="s">
         <v>865</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -16202,7 +16208,7 @@
       <c r="D35" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -16225,7 +16231,7 @@
       <c r="D36" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="7" t="s">
         <v>61</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -16251,7 +16257,7 @@
       <c r="D37" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="7" t="s">
         <v>861</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -16274,7 +16280,7 @@
       <c r="D38" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="7" t="s">
         <v>860</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -16300,7 +16306,7 @@
       <c r="D39" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="7" t="s">
         <v>845</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -16323,7 +16329,7 @@
       <c r="D40" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="7" t="s">
         <v>859</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -16349,7 +16355,7 @@
       <c r="D41" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="7" t="s">
         <v>811</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -16372,7 +16378,7 @@
       <c r="D42" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="7" t="s">
         <v>141</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -16398,7 +16404,7 @@
       <c r="D43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="7" t="s">
         <v>858</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -16421,7 +16427,7 @@
       <c r="D44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="7" t="s">
         <v>857</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -16447,7 +16453,7 @@
       <c r="D45" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="7" t="s">
         <v>856</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -16470,7 +16476,7 @@
       <c r="D46" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="7" t="s">
         <v>670</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -16496,7 +16502,7 @@
       <c r="D47" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -16519,7 +16525,7 @@
       <c r="D48" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="7" t="s">
         <v>855</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -16545,7 +16551,7 @@
       <c r="D49" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="7" t="s">
         <v>854</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -16571,7 +16577,7 @@
       <c r="D50" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="7" t="s">
         <v>853</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -16597,7 +16603,7 @@
       <c r="D51" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="7" t="s">
         <v>852</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -16623,7 +16629,7 @@
       <c r="D52" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="7" t="s">
         <v>851</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -16646,7 +16652,7 @@
       <c r="D53" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="7" t="s">
         <v>850</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -16672,7 +16678,7 @@
       <c r="D54" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="7" t="s">
         <v>143</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -16695,7 +16701,7 @@
       <c r="D55" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="7" t="s">
         <v>849</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -16721,7 +16727,7 @@
       <c r="D56" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="7" t="s">
         <v>803</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -16744,7 +16750,7 @@
       <c r="D57" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="7" t="s">
         <v>848</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -16770,7 +16776,7 @@
       <c r="D58" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -16793,7 +16799,7 @@
       <c r="D59" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="7" t="s">
         <v>847</v>
       </c>
       <c r="F59" s="1" t="s">
@@ -16819,7 +16825,7 @@
       <c r="D60" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="7" t="s">
         <v>783</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -16842,7 +16848,7 @@
       <c r="D61" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="7" t="s">
         <v>846</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -16868,7 +16874,7 @@
       <c r="D62" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="7" t="s">
         <v>845</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -16891,7 +16897,7 @@
       <c r="D63" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="7" t="s">
         <v>825</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -16917,7 +16923,7 @@
       <c r="D64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="7" t="s">
         <v>826</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -16940,7 +16946,7 @@
       <c r="D65" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="7" t="s">
         <v>844</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -16966,7 +16972,7 @@
       <c r="D66" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="7" t="s">
         <v>843</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -16989,7 +16995,7 @@
       <c r="D67" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="7" t="s">
         <v>842</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -17015,7 +17021,7 @@
       <c r="D68" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="7" t="s">
         <v>841</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -17038,7 +17044,7 @@
       <c r="D69" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="7" t="s">
         <v>840</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -17064,7 +17070,7 @@
       <c r="D70" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="7" t="s">
         <v>839</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -17087,7 +17093,7 @@
       <c r="D71" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="7" t="s">
         <v>838</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -17113,7 +17119,7 @@
       <c r="D72" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="7" t="s">
         <v>824</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -17136,7 +17142,7 @@
       <c r="D73" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="7" t="s">
         <v>681</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -17162,7 +17168,7 @@
       <c r="D74" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="7" t="s">
         <v>823</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -17185,7 +17191,7 @@
       <c r="D75" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="7" t="s">
         <v>822</v>
       </c>
       <c r="F75" s="1" t="s">
@@ -17211,7 +17217,7 @@
       <c r="D76" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="7" t="s">
         <v>182</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -17234,7 +17240,7 @@
       <c r="D77" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="7" t="s">
         <v>821</v>
       </c>
       <c r="F77" s="1" t="s">
@@ -17260,7 +17266,7 @@
       <c r="D78" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F78" s="1" t="s">
@@ -17283,7 +17289,7 @@
       <c r="D79" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="7" t="s">
         <v>820</v>
       </c>
       <c r="F79" s="1" t="s">
@@ -17309,7 +17315,7 @@
       <c r="D80" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="7" t="s">
         <v>819</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -17332,7 +17338,7 @@
       <c r="D81" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="7" t="s">
         <v>817</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -17358,7 +17364,7 @@
       <c r="D82" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="7" t="s">
         <v>816</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -17381,7 +17387,7 @@
       <c r="D83" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="7" t="s">
         <v>815</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -17407,7 +17413,7 @@
       <c r="D84" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="7" t="s">
         <v>814</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -17430,7 +17436,7 @@
       <c r="D85" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="7" t="s">
         <v>813</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -17456,7 +17462,7 @@
       <c r="D86" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="7" t="s">
         <v>812</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -17479,7 +17485,7 @@
       <c r="D87" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="7" t="s">
         <v>811</v>
       </c>
       <c r="F87" s="1" t="s">
@@ -17505,7 +17511,7 @@
       <c r="D88" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="7" t="s">
         <v>810</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -17528,7 +17534,7 @@
       <c r="D89" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="7" t="s">
         <v>809</v>
       </c>
       <c r="F89" s="1" t="s">
@@ -17554,7 +17560,7 @@
       <c r="D90" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="7" t="s">
         <v>808</v>
       </c>
       <c r="F90" s="1" t="s">
@@ -17577,7 +17583,7 @@
       <c r="D91" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="7" t="s">
         <v>786</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -17603,7 +17609,7 @@
       <c r="D92" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="7" t="s">
         <v>807</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -17626,7 +17632,7 @@
       <c r="D93" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="7" t="s">
         <v>806</v>
       </c>
       <c r="F93" s="1" t="s">
@@ -17652,7 +17658,7 @@
       <c r="D94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="7" t="s">
         <v>805</v>
       </c>
       <c r="F94" s="1" t="s">
@@ -17675,7 +17681,7 @@
       <c r="D95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" s="7" t="s">
         <v>804</v>
       </c>
       <c r="F95" s="1" t="s">
@@ -17698,7 +17704,7 @@
       <c r="D96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E96" s="7" t="s">
         <v>143</v>
       </c>
       <c r="F96" s="1" t="s">
@@ -17721,7 +17727,7 @@
       <c r="D97" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" s="7" t="s">
         <v>803</v>
       </c>
       <c r="F97" s="1" t="s">
@@ -17747,7 +17753,7 @@
       <c r="D98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="7" t="s">
         <v>802</v>
       </c>
       <c r="F98" s="1" t="s">
@@ -17770,7 +17776,7 @@
       <c r="D99" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" s="7" t="s">
         <v>801</v>
       </c>
       <c r="F99" s="1" t="s">
@@ -17793,7 +17799,7 @@
       <c r="D100" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" s="7" t="s">
         <v>800</v>
       </c>
       <c r="F100" s="1" t="s">
@@ -17816,7 +17822,7 @@
       <c r="D101" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="7" t="s">
         <v>799</v>
       </c>
       <c r="F101" s="1" t="s">
@@ -17839,7 +17845,7 @@
       <c r="D102" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="7" t="s">
         <v>798</v>
       </c>
       <c r="F102" s="1" t="s">
@@ -17862,7 +17868,7 @@
       <c r="D103" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="7" t="s">
         <v>797</v>
       </c>
       <c r="F103" s="1" t="s">
@@ -17888,7 +17894,7 @@
       <c r="D104" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E104" s="7" t="s">
         <v>796</v>
       </c>
       <c r="F104" s="1" t="s">
@@ -17911,7 +17917,7 @@
       <c r="D105" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="7" t="s">
         <v>795</v>
       </c>
       <c r="F105" s="1" t="s">

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D5886F-E93D-43E8-A01D-92E15CA4DE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BA9137-75CD-4B1E-9127-DFC12958DBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="7" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="6" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="868">
   <si>
     <t>年份</t>
   </si>
@@ -2624,30 +2624,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>中華佛教文物流通中心</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑫車汽車廣場</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雲林褒忠分駐所</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>野川堂秘境鍋物-虎尾店</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>埤頭合興宮</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大甲日南民宅</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>起駕</t>
   </si>
   <si>
@@ -3205,6 +3181,38 @@
   </si>
   <si>
     <t>18:31</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大慶通運股份有限公司駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>埤頭合興宮駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>野川堂秘境鍋物-虎尾店駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲日南民宅駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苗栗通霄慈后宮駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林褒忠分駐所駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑫車汽車廣場駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中華佛教文物流通中心駐駕</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3819,7 +3827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3836,12 +3844,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -14825,7 +14827,7 @@
         <v>686</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>705</v>
+        <v>867</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -14851,7 +14853,7 @@
         <v>687</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>705</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -14877,7 +14879,7 @@
         <v>688</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>706</v>
+        <v>866</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -14903,7 +14905,7 @@
         <v>689</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>706</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -14929,7 +14931,7 @@
         <v>690</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>707</v>
+        <v>865</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -14955,7 +14957,7 @@
         <v>691</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>707</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -15033,7 +15035,7 @@
         <v>694</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>708</v>
+        <v>862</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>166</v>
@@ -15059,7 +15061,7 @@
         <v>693</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>708</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>166</v>
@@ -15085,7 +15087,7 @@
         <v>695</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>709</v>
+        <v>861</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>166</v>
@@ -15111,7 +15113,7 @@
         <v>693</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>709</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>166</v>
@@ -15137,7 +15139,7 @@
         <v>696</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>160</v>
+        <v>860</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>166</v>
@@ -15163,7 +15165,7 @@
         <v>697</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>166</v>
@@ -15189,7 +15191,7 @@
         <v>698</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>710</v>
+        <v>863</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>166</v>
@@ -15215,7 +15217,7 @@
         <v>699</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>710</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>166</v>
@@ -15241,7 +15243,7 @@
         <v>700</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>680</v>
+        <v>864</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>166</v>
@@ -15267,7 +15269,7 @@
         <v>701</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>680</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>166</v>
@@ -15339,7 +15341,7 @@
     <col min="1" max="1" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="82" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="2"/>
@@ -15358,7 +15360,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -15373,10 +15375,10 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>187</v>
@@ -15384,11 +15386,11 @@
       <c r="D2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>13</v>
@@ -15400,10 +15402,10 @@
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>187</v>
@@ -15411,11 +15413,11 @@
       <c r="D3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>782</v>
+      <c r="E3" s="2" t="s">
+        <v>776</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>13</v>
@@ -15430,10 +15432,10 @@
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>187</v>
@@ -15441,11 +15443,11 @@
       <c r="D4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>783</v>
+      <c r="E4" s="2" t="s">
+        <v>777</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -15454,10 +15456,10 @@
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>187</v>
@@ -15465,11 +15467,11 @@
       <c r="D5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>784</v>
+      <c r="E5" s="2" t="s">
+        <v>778</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>13</v>
@@ -15481,10 +15483,10 @@
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>187</v>
@@ -15492,11 +15494,11 @@
       <c r="D6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>785</v>
+      <c r="E6" s="2" t="s">
+        <v>779</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -15505,10 +15507,10 @@
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>187</v>
@@ -15516,11 +15518,11 @@
       <c r="D7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>786</v>
+      <c r="E7" s="2" t="s">
+        <v>780</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -15532,10 +15534,10 @@
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>187</v>
@@ -15543,11 +15545,11 @@
       <c r="D8" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>787</v>
+      <c r="E8" s="2" t="s">
+        <v>781</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>13</v>
@@ -15556,10 +15558,10 @@
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>187</v>
@@ -15567,11 +15569,11 @@
       <c r="D9" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>788</v>
+      <c r="E9" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>13</v>
@@ -15583,10 +15585,10 @@
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>187</v>
@@ -15594,11 +15596,11 @@
       <c r="D10" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>789</v>
+      <c r="E10" s="2" t="s">
+        <v>783</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>13</v>
@@ -15610,10 +15612,10 @@
     </row>
     <row r="11" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>187</v>
@@ -15621,11 +15623,11 @@
       <c r="D11" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>790</v>
+      <c r="E11" s="2" t="s">
+        <v>784</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -15634,10 +15636,10 @@
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>187</v>
@@ -15645,11 +15647,11 @@
       <c r="D12" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>791</v>
+      <c r="E12" s="2" t="s">
+        <v>785</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
@@ -15661,10 +15663,10 @@
     </row>
     <row r="13" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>187</v>
@@ -15672,11 +15674,11 @@
       <c r="D13" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>792</v>
+      <c r="E13" s="2" t="s">
+        <v>786</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>13</v>
@@ -15684,10 +15686,10 @@
     </row>
     <row r="14" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>187</v>
@@ -15695,11 +15697,11 @@
       <c r="D14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>793</v>
+      <c r="E14" s="2" t="s">
+        <v>787</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
@@ -15710,10 +15712,10 @@
     </row>
     <row r="15" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>187</v>
@@ -15721,11 +15723,11 @@
       <c r="D15" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>794</v>
+      <c r="E15" s="2" t="s">
+        <v>788</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -15736,10 +15738,10 @@
     </row>
     <row r="16" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>187</v>
@@ -15747,11 +15749,11 @@
       <c r="D16" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>827</v>
+      <c r="E16" s="2" t="s">
+        <v>821</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
@@ -15762,10 +15764,10 @@
     </row>
     <row r="17" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>187</v>
@@ -15773,11 +15775,11 @@
       <c r="D17" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>828</v>
+      <c r="E17" s="2" t="s">
+        <v>822</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>13</v>
@@ -15788,10 +15790,10 @@
     </row>
     <row r="18" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>187</v>
@@ -15799,11 +15801,11 @@
       <c r="D18" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>829</v>
+      <c r="E18" s="2" t="s">
+        <v>823</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
@@ -15814,10 +15816,10 @@
     </row>
     <row r="19" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>187</v>
@@ -15825,11 +15827,11 @@
       <c r="D19" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>830</v>
+      <c r="E19" s="2" t="s">
+        <v>824</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>13</v>
@@ -15837,10 +15839,10 @@
     </row>
     <row r="20" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>187</v>
@@ -15848,11 +15850,11 @@
       <c r="D20" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>831</v>
+      <c r="E20" s="2" t="s">
+        <v>825</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>13</v>
@@ -15860,10 +15862,10 @@
     </row>
     <row r="21" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>187</v>
@@ -15871,11 +15873,11 @@
       <c r="D21" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>832</v>
+      <c r="E21" s="2" t="s">
+        <v>826</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>13</v>
@@ -15883,10 +15885,10 @@
     </row>
     <row r="22" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>187</v>
@@ -15894,11 +15896,11 @@
       <c r="D22" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>833</v>
+      <c r="E22" s="2" t="s">
+        <v>827</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>13</v>
@@ -15906,10 +15908,10 @@
     </row>
     <row r="23" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>187</v>
@@ -15917,11 +15919,11 @@
       <c r="D23" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>834</v>
+      <c r="E23" s="2" t="s">
+        <v>828</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>13</v>
@@ -15929,10 +15931,10 @@
     </row>
     <row r="24" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>187</v>
@@ -15940,11 +15942,11 @@
       <c r="D24" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="2" t="s">
         <v>660</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>13</v>
@@ -15952,10 +15954,10 @@
     </row>
     <row r="25" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>187</v>
@@ -15963,11 +15965,11 @@
       <c r="D25" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>835</v>
+      <c r="E25" s="2" t="s">
+        <v>829</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>166</v>
@@ -15975,10 +15977,10 @@
     </row>
     <row r="26" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>187</v>
@@ -15986,11 +15988,11 @@
       <c r="D26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>836</v>
+      <c r="E26" s="2" t="s">
+        <v>830</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>166</v>
@@ -16001,10 +16003,10 @@
     </row>
     <row r="27" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>187</v>
@@ -16012,11 +16014,11 @@
       <c r="D27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>837</v>
+      <c r="E27" s="2" t="s">
+        <v>831</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>166</v>
@@ -16024,10 +16026,10 @@
     </row>
     <row r="28" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>187</v>
@@ -16035,11 +16037,11 @@
       <c r="D28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>862</v>
+      <c r="E28" s="2" t="s">
+        <v>856</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>166</v>
@@ -16050,10 +16052,10 @@
     </row>
     <row r="29" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>187</v>
@@ -16061,7 +16063,7 @@
       <c r="D29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="2" t="s">
         <v>99</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -16073,10 +16075,10 @@
     </row>
     <row r="30" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>187</v>
@@ -16084,11 +16086,11 @@
       <c r="D30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>863</v>
+      <c r="E30" s="2" t="s">
+        <v>857</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>166</v>
@@ -16099,10 +16101,10 @@
     </row>
     <row r="31" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>187</v>
@@ -16110,11 +16112,11 @@
       <c r="D31" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>864</v>
+      <c r="E31" s="2" t="s">
+        <v>858</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>166</v>
@@ -16122,10 +16124,10 @@
     </row>
     <row r="32" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>187</v>
@@ -16133,11 +16135,11 @@
       <c r="D32" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>804</v>
+      <c r="E32" s="2" t="s">
+        <v>798</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>166</v>
@@ -16148,10 +16150,10 @@
     </row>
     <row r="33" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>187</v>
@@ -16159,7 +16161,7 @@
       <c r="D33" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="2" t="s">
         <v>660</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -16171,10 +16173,10 @@
     </row>
     <row r="34" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>187</v>
@@ -16182,11 +16184,11 @@
       <c r="D34" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>865</v>
+      <c r="E34" s="2" t="s">
+        <v>859</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>166</v>
@@ -16197,10 +16199,10 @@
     </row>
     <row r="35" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>187</v>
@@ -16208,11 +16210,11 @@
       <c r="D35" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>166</v>
@@ -16220,10 +16222,10 @@
     </row>
     <row r="36" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>187</v>
@@ -16231,11 +16233,11 @@
       <c r="D36" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>166</v>
@@ -16246,10 +16248,10 @@
     </row>
     <row r="37" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>187</v>
@@ -16257,8 +16259,8 @@
       <c r="D37" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>861</v>
+      <c r="E37" s="2" t="s">
+        <v>855</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>14</v>
@@ -16269,10 +16271,10 @@
     </row>
     <row r="38" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>187</v>
@@ -16280,11 +16282,11 @@
       <c r="D38" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>860</v>
+      <c r="E38" s="2" t="s">
+        <v>854</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>166</v>
@@ -16295,10 +16297,10 @@
     </row>
     <row r="39" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>187</v>
@@ -16306,8 +16308,8 @@
       <c r="D39" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>845</v>
+      <c r="E39" s="2" t="s">
+        <v>839</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>14</v>
@@ -16318,10 +16320,10 @@
     </row>
     <row r="40" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>187</v>
@@ -16329,11 +16331,11 @@
       <c r="D40" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>859</v>
+      <c r="E40" s="2" t="s">
+        <v>853</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>166</v>
@@ -16344,10 +16346,10 @@
     </row>
     <row r="41" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>187</v>
@@ -16355,8 +16357,8 @@
       <c r="D41" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>811</v>
+      <c r="E41" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>14</v>
@@ -16367,10 +16369,10 @@
     </row>
     <row r="42" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>187</v>
@@ -16378,11 +16380,11 @@
       <c r="D42" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>166</v>
@@ -16393,10 +16395,10 @@
     </row>
     <row r="43" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>187</v>
@@ -16404,8 +16406,8 @@
       <c r="D43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>858</v>
+      <c r="E43" s="2" t="s">
+        <v>852</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>14</v>
@@ -16416,10 +16418,10 @@
     </row>
     <row r="44" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>187</v>
@@ -16427,11 +16429,11 @@
       <c r="D44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>857</v>
+      <c r="E44" s="2" t="s">
+        <v>851</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>166</v>
@@ -16442,10 +16444,10 @@
     </row>
     <row r="45" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>187</v>
@@ -16453,8 +16455,8 @@
       <c r="D45" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>856</v>
+      <c r="E45" s="2" t="s">
+        <v>850</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>14</v>
@@ -16465,10 +16467,10 @@
     </row>
     <row r="46" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>187</v>
@@ -16476,11 +16478,11 @@
       <c r="D46" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="2" t="s">
         <v>670</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>166</v>
@@ -16491,10 +16493,10 @@
     </row>
     <row r="47" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>187</v>
@@ -16502,11 +16504,11 @@
       <c r="D47" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>166</v>
@@ -16514,10 +16516,10 @@
     </row>
     <row r="48" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>187</v>
@@ -16525,11 +16527,11 @@
       <c r="D48" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E48" s="7" t="s">
-        <v>855</v>
+      <c r="E48" s="2" t="s">
+        <v>849</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>166</v>
@@ -16540,10 +16542,10 @@
     </row>
     <row r="49" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>187</v>
@@ -16551,11 +16553,11 @@
       <c r="D49" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>854</v>
+      <c r="E49" s="2" t="s">
+        <v>848</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>166</v>
@@ -16566,10 +16568,10 @@
     </row>
     <row r="50" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>187</v>
@@ -16577,11 +16579,11 @@
       <c r="D50" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>853</v>
+      <c r="E50" s="2" t="s">
+        <v>847</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>166</v>
@@ -16592,10 +16594,10 @@
     </row>
     <row r="51" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>187</v>
@@ -16603,11 +16605,11 @@
       <c r="D51" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>852</v>
+      <c r="E51" s="2" t="s">
+        <v>846</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>166</v>
@@ -16618,10 +16620,10 @@
     </row>
     <row r="52" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>187</v>
@@ -16629,11 +16631,11 @@
       <c r="D52" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E52" s="7" t="s">
-        <v>851</v>
+      <c r="E52" s="2" t="s">
+        <v>845</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>166</v>
@@ -16641,10 +16643,10 @@
     </row>
     <row r="53" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>187</v>
@@ -16652,11 +16654,11 @@
       <c r="D53" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E53" s="7" t="s">
-        <v>850</v>
+      <c r="E53" s="2" t="s">
+        <v>844</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>166</v>
@@ -16667,10 +16669,10 @@
     </row>
     <row r="54" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>187</v>
@@ -16678,11 +16680,11 @@
       <c r="D54" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>166</v>
@@ -16690,10 +16692,10 @@
     </row>
     <row r="55" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>187</v>
@@ -16701,11 +16703,11 @@
       <c r="D55" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>849</v>
+      <c r="E55" s="2" t="s">
+        <v>843</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>166</v>
@@ -16716,10 +16718,10 @@
     </row>
     <row r="56" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>187</v>
@@ -16727,11 +16729,11 @@
       <c r="D56" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>803</v>
+      <c r="E56" s="2" t="s">
+        <v>797</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>166</v>
@@ -16739,10 +16741,10 @@
     </row>
     <row r="57" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>187</v>
@@ -16750,11 +16752,11 @@
       <c r="D57" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>848</v>
+      <c r="E57" s="2" t="s">
+        <v>842</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>166</v>
@@ -16765,10 +16767,10 @@
     </row>
     <row r="58" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>187</v>
@@ -16776,11 +16778,11 @@
       <c r="D58" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>166</v>
@@ -16788,10 +16790,10 @@
     </row>
     <row r="59" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>187</v>
@@ -16799,11 +16801,11 @@
       <c r="D59" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>847</v>
+      <c r="E59" s="2" t="s">
+        <v>841</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>166</v>
@@ -16814,10 +16816,10 @@
     </row>
     <row r="60" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>187</v>
@@ -16825,11 +16827,11 @@
       <c r="D60" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E60" s="7" t="s">
-        <v>783</v>
+      <c r="E60" s="2" t="s">
+        <v>777</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>166</v>
@@ -16837,10 +16839,10 @@
     </row>
     <row r="61" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>187</v>
@@ -16848,11 +16850,11 @@
       <c r="D61" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>846</v>
+      <c r="E61" s="2" t="s">
+        <v>840</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>166</v>
@@ -16863,10 +16865,10 @@
     </row>
     <row r="62" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>187</v>
@@ -16874,11 +16876,11 @@
       <c r="D62" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E62" s="7" t="s">
-        <v>845</v>
+      <c r="E62" s="2" t="s">
+        <v>839</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>166</v>
@@ -16886,10 +16888,10 @@
     </row>
     <row r="63" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>187</v>
@@ -16897,11 +16899,11 @@
       <c r="D63" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E63" s="7" t="s">
-        <v>825</v>
+      <c r="E63" s="2" t="s">
+        <v>819</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>166</v>
@@ -16912,10 +16914,10 @@
     </row>
     <row r="64" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>187</v>
@@ -16923,11 +16925,11 @@
       <c r="D64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E64" s="7" t="s">
-        <v>826</v>
+      <c r="E64" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>166</v>
@@ -16935,10 +16937,10 @@
     </row>
     <row r="65" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>187</v>
@@ -16946,11 +16948,11 @@
       <c r="D65" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>844</v>
+      <c r="E65" s="2" t="s">
+        <v>838</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>166</v>
@@ -16961,10 +16963,10 @@
     </row>
     <row r="66" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>187</v>
@@ -16972,11 +16974,11 @@
       <c r="D66" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>843</v>
+      <c r="E66" s="2" t="s">
+        <v>837</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>166</v>
@@ -16984,10 +16986,10 @@
     </row>
     <row r="67" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>187</v>
@@ -16995,11 +16997,11 @@
       <c r="D67" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>842</v>
+      <c r="E67" s="2" t="s">
+        <v>836</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>166</v>
@@ -17010,10 +17012,10 @@
     </row>
     <row r="68" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>187</v>
@@ -17021,11 +17023,11 @@
       <c r="D68" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E68" s="7" t="s">
-        <v>841</v>
+      <c r="E68" s="2" t="s">
+        <v>835</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>166</v>
@@ -17033,10 +17035,10 @@
     </row>
     <row r="69" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>187</v>
@@ -17044,11 +17046,11 @@
       <c r="D69" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>840</v>
+      <c r="E69" s="2" t="s">
+        <v>834</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>166</v>
@@ -17059,10 +17061,10 @@
     </row>
     <row r="70" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>187</v>
@@ -17070,11 +17072,11 @@
       <c r="D70" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>839</v>
+      <c r="E70" s="2" t="s">
+        <v>833</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>166</v>
@@ -17082,10 +17084,10 @@
     </row>
     <row r="71" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>187</v>
@@ -17093,11 +17095,11 @@
       <c r="D71" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E71" s="7" t="s">
-        <v>838</v>
+      <c r="E71" s="2" t="s">
+        <v>832</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>166</v>
@@ -17108,10 +17110,10 @@
     </row>
     <row r="72" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>187</v>
@@ -17119,11 +17121,11 @@
       <c r="D72" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>824</v>
+      <c r="E72" s="2" t="s">
+        <v>818</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>166</v>
@@ -17131,10 +17133,10 @@
     </row>
     <row r="73" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>187</v>
@@ -17142,11 +17144,11 @@
       <c r="D73" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="2" t="s">
         <v>681</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>166</v>
@@ -17157,10 +17159,10 @@
     </row>
     <row r="74" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>187</v>
@@ -17168,11 +17170,11 @@
       <c r="D74" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>823</v>
+      <c r="E74" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>166</v>
@@ -17180,10 +17182,10 @@
     </row>
     <row r="75" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>187</v>
@@ -17191,11 +17193,11 @@
       <c r="D75" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>822</v>
+      <c r="E75" s="2" t="s">
+        <v>816</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>166</v>
@@ -17206,10 +17208,10 @@
     </row>
     <row r="76" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>187</v>
@@ -17217,11 +17219,11 @@
       <c r="D76" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="2" t="s">
         <v>182</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>166</v>
@@ -17229,10 +17231,10 @@
     </row>
     <row r="77" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>187</v>
@@ -17240,11 +17242,11 @@
       <c r="D77" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>821</v>
+      <c r="E77" s="2" t="s">
+        <v>815</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>166</v>
@@ -17255,10 +17257,10 @@
     </row>
     <row r="78" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>187</v>
@@ -17266,11 +17268,11 @@
       <c r="D78" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>166</v>
@@ -17278,10 +17280,10 @@
     </row>
     <row r="79" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>187</v>
@@ -17289,11 +17291,11 @@
       <c r="D79" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>820</v>
+      <c r="E79" s="2" t="s">
+        <v>814</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>166</v>
@@ -17304,10 +17306,10 @@
     </row>
     <row r="80" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>187</v>
@@ -17315,11 +17317,11 @@
       <c r="D80" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E80" s="7" t="s">
-        <v>819</v>
+      <c r="E80" s="2" t="s">
+        <v>813</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>166</v>
@@ -17327,10 +17329,10 @@
     </row>
     <row r="81" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>187</v>
@@ -17338,11 +17340,11 @@
       <c r="D81" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>817</v>
+      <c r="E81" s="2" t="s">
+        <v>811</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>166</v>
@@ -17353,10 +17355,10 @@
     </row>
     <row r="82" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>187</v>
@@ -17364,11 +17366,11 @@
       <c r="D82" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E82" s="7" t="s">
-        <v>816</v>
+      <c r="E82" s="2" t="s">
+        <v>810</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>166</v>
@@ -17376,10 +17378,10 @@
     </row>
     <row r="83" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>187</v>
@@ -17387,11 +17389,11 @@
       <c r="D83" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E83" s="7" t="s">
-        <v>815</v>
+      <c r="E83" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>166</v>
@@ -17402,10 +17404,10 @@
     </row>
     <row r="84" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>187</v>
@@ -17413,11 +17415,11 @@
       <c r="D84" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E84" s="7" t="s">
-        <v>814</v>
+      <c r="E84" s="2" t="s">
+        <v>808</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>166</v>
@@ -17425,10 +17427,10 @@
     </row>
     <row r="85" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>187</v>
@@ -17436,11 +17438,11 @@
       <c r="D85" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E85" s="7" t="s">
-        <v>813</v>
+      <c r="E85" s="2" t="s">
+        <v>807</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>166</v>
@@ -17451,10 +17453,10 @@
     </row>
     <row r="86" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>187</v>
@@ -17462,11 +17464,11 @@
       <c r="D86" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>812</v>
+      <c r="E86" s="2" t="s">
+        <v>806</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>166</v>
@@ -17474,10 +17476,10 @@
     </row>
     <row r="87" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>187</v>
@@ -17485,11 +17487,11 @@
       <c r="D87" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E87" s="7" t="s">
-        <v>811</v>
+      <c r="E87" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>166</v>
@@ -17500,10 +17502,10 @@
     </row>
     <row r="88" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>187</v>
@@ -17511,11 +17513,11 @@
       <c r="D88" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E88" s="7" t="s">
-        <v>810</v>
+      <c r="E88" s="2" t="s">
+        <v>804</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>166</v>
@@ -17523,10 +17525,10 @@
     </row>
     <row r="89" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>187</v>
@@ -17534,11 +17536,11 @@
       <c r="D89" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E89" s="7" t="s">
-        <v>809</v>
+      <c r="E89" s="2" t="s">
+        <v>803</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>166</v>
@@ -17549,10 +17551,10 @@
     </row>
     <row r="90" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>187</v>
@@ -17560,11 +17562,11 @@
       <c r="D90" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E90" s="7" t="s">
-        <v>808</v>
+      <c r="E90" s="2" t="s">
+        <v>802</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>166</v>
@@ -17572,10 +17574,10 @@
     </row>
     <row r="91" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>187</v>
@@ -17583,11 +17585,11 @@
       <c r="D91" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E91" s="7" t="s">
-        <v>786</v>
+      <c r="E91" s="2" t="s">
+        <v>780</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>166</v>
@@ -17598,10 +17600,10 @@
     </row>
     <row r="92" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>187</v>
@@ -17609,11 +17611,11 @@
       <c r="D92" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E92" s="7" t="s">
-        <v>807</v>
+      <c r="E92" s="2" t="s">
+        <v>801</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>166</v>
@@ -17621,10 +17623,10 @@
     </row>
     <row r="93" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>187</v>
@@ -17632,11 +17634,11 @@
       <c r="D93" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E93" s="7" t="s">
-        <v>806</v>
+      <c r="E93" s="2" t="s">
+        <v>800</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>166</v>
@@ -17647,10 +17649,10 @@
     </row>
     <row r="94" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>187</v>
@@ -17658,11 +17660,11 @@
       <c r="D94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>805</v>
+      <c r="E94" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>166</v>
@@ -17670,10 +17672,10 @@
     </row>
     <row r="95" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>187</v>
@@ -17681,11 +17683,11 @@
       <c r="D95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E95" s="7" t="s">
-        <v>804</v>
+      <c r="E95" s="2" t="s">
+        <v>798</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>166</v>
@@ -17693,10 +17695,10 @@
     </row>
     <row r="96" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>187</v>
@@ -17704,11 +17706,11 @@
       <c r="D96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>166</v>
@@ -17716,10 +17718,10 @@
     </row>
     <row r="97" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>187</v>
@@ -17727,11 +17729,11 @@
       <c r="D97" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>803</v>
+      <c r="E97" s="2" t="s">
+        <v>797</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>166</v>
@@ -17742,10 +17744,10 @@
     </row>
     <row r="98" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>187</v>
@@ -17753,11 +17755,11 @@
       <c r="D98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>802</v>
+      <c r="E98" s="2" t="s">
+        <v>796</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>166</v>
@@ -17765,10 +17767,10 @@
     </row>
     <row r="99" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>187</v>
@@ -17776,11 +17778,11 @@
       <c r="D99" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>801</v>
+      <c r="E99" s="2" t="s">
+        <v>795</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>166</v>
@@ -17788,10 +17790,10 @@
     </row>
     <row r="100" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>187</v>
@@ -17799,11 +17801,11 @@
       <c r="D100" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>800</v>
+      <c r="E100" s="2" t="s">
+        <v>794</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>166</v>
@@ -17811,10 +17813,10 @@
     </row>
     <row r="101" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>187</v>
@@ -17822,11 +17824,11 @@
       <c r="D101" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E101" s="7" t="s">
-        <v>799</v>
+      <c r="E101" s="2" t="s">
+        <v>793</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>166</v>
@@ -17834,10 +17836,10 @@
     </row>
     <row r="102" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>187</v>
@@ -17845,11 +17847,11 @@
       <c r="D102" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>798</v>
+      <c r="E102" s="2" t="s">
+        <v>792</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>166</v>
@@ -17857,10 +17859,10 @@
     </row>
     <row r="103" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>187</v>
@@ -17868,11 +17870,11 @@
       <c r="D103" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>797</v>
+      <c r="E103" s="2" t="s">
+        <v>791</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>166</v>
@@ -17883,10 +17885,10 @@
     </row>
     <row r="104" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>187</v>
@@ -17894,11 +17896,11 @@
       <c r="D104" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>796</v>
+      <c r="E104" s="2" t="s">
+        <v>790</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>166</v>
@@ -17906,10 +17908,10 @@
     </row>
     <row r="105" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>187</v>
@@ -17917,11 +17919,11 @@
       <c r="D105" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>795</v>
+      <c r="E105" s="2" t="s">
+        <v>789</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>166</v>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BA9137-75CD-4B1E-9127-DFC12958DBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC66A3B-E5B0-48C5-A393-EC55AC24F346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="6" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="8" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="2020" sheetId="6" r:id="rId6"/>
     <sheet name="2019" sheetId="8" r:id="rId7"/>
     <sheet name="2018" sheetId="10" r:id="rId8"/>
+    <sheet name="2017" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2018'!$A$1:$G$105</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5371" uniqueCount="1115">
   <si>
     <t>年份</t>
   </si>
@@ -3213,6 +3214,750 @@
   </si>
   <si>
     <t>中華佛教文物流通中心駐駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>16:58</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>09:11</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>18:58</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:27</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>03:44</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>04:09</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>04:32</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>07:38</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>01:38</t>
+  </si>
+  <si>
+    <t>03:14</t>
+  </si>
+  <si>
+    <t>03:18</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>07:34</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>14:59</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>17:04</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>06:59</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:31</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>14:02</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>16:51</t>
+  </si>
+  <si>
+    <t>07:32</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>14:11</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>05:01</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>07:23</t>
+  </si>
+  <si>
+    <t>07:54</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>出發</t>
+  </si>
+  <si>
+    <t>民宅停駕</t>
+  </si>
+  <si>
+    <t>通霄媽祖廟慈惠宮停駕1小時</t>
+  </si>
+  <si>
+    <t>停駕民家(鑼手家)</t>
+  </si>
+  <si>
+    <t>房裡永春不產停駕，休息15分</t>
+  </si>
+  <si>
+    <t>停駕TOYOTA汽車休息20分</t>
+  </si>
+  <si>
+    <t>新順昌傢俱停駕休息到14點</t>
+  </si>
+  <si>
+    <t>大甲鎮瀾宮休息30分鐘</t>
+  </si>
+  <si>
+    <t>宏信汽車前設有香案神轎未轉向，僅原地行轎致意，(三府王爺-李府宮)</t>
+  </si>
+  <si>
+    <t>停駕源富汽車(大信汽修廠)電機廠前，休息10分鐘，「中部憨工團」所設的棚子。</t>
+  </si>
+  <si>
+    <t>停駕路邊棚子，一整排棚子都發放結緣食物，有肉粽、沙其馬等。</t>
+  </si>
+  <si>
+    <t>甲南湄安宮駐駕隔日早上6點起駕</t>
+  </si>
+  <si>
+    <t>笠毅工業股份有限公司停駕</t>
+  </si>
+  <si>
+    <t>三光佛具行停駕20分鐘</t>
+  </si>
+  <si>
+    <t>停駕沙鹿錦華街與中山路交叉路口的帳篷內(鹿寮成衣商圈)30分鐘</t>
+  </si>
+  <si>
+    <t>龍井山腳聖母會館停駕午休</t>
+  </si>
+  <si>
+    <t>停駕鴻長機械</t>
+  </si>
+  <si>
+    <t>停駕龍井分駐所(烏日分局)，停15分鐘</t>
+  </si>
+  <si>
+    <t>停駕民宅</t>
+  </si>
+  <si>
+    <t>烏日彰化交接處路邊停頓</t>
+  </si>
+  <si>
+    <t>民宅(家中男主人因細菌感染住院，幾天前就一直求媽祖幫忙)</t>
+  </si>
+  <si>
+    <t>福特汽車-福彰汽車(中山路三段)駐駕</t>
+  </si>
+  <si>
+    <t>彰化縣彰化市五權里金馬路停駕。</t>
+  </si>
+  <si>
+    <t>停駕果菜市場，停駕30分鐘</t>
+  </si>
+  <si>
+    <t>埔鹽國小停駕13:28下司令台</t>
+  </si>
+  <si>
+    <t>尚介讚便當店停駕10分鐘</t>
+  </si>
+  <si>
+    <t>富寓汽車停駕休息10分鐘</t>
+  </si>
+  <si>
+    <t>進入五綸織造股份有限公司</t>
+  </si>
+  <si>
+    <t>埤頭合興宮駐駕</t>
+  </si>
+  <si>
+    <t>停駕竹塘慈航宮休息20分鐘</t>
+  </si>
+  <si>
+    <t>起轎</t>
+  </si>
+  <si>
+    <t>竹塘鄉幸竹宮踩廟地、巡廟基(約10分鐘)</t>
+  </si>
+  <si>
+    <t>二崙自強果菜市場停駕15分鐘</t>
+  </si>
+  <si>
+    <t>雲林崙背羅厝啟安廟停駕</t>
+  </si>
+  <si>
+    <t>崙背慈聖太子殿停駕午休到14:00</t>
+  </si>
+  <si>
+    <t>旭心亭金香舖停駕15分鐘</t>
+  </si>
+  <si>
+    <t>仁仁超市(仁仁雜貨鋪子)停駕10分鐘</t>
+  </si>
+  <si>
+    <t>褒忠分駐所駐駕明天凌晨2點起駕</t>
+  </si>
+  <si>
+    <t>元長媽祖會停駕十分鐘</t>
+  </si>
+  <si>
+    <t>停駕法律地政事務所</t>
+  </si>
+  <si>
+    <t>元長鄉公所停駕</t>
+  </si>
+  <si>
+    <t>元長佛祖會停駕</t>
+  </si>
+  <si>
+    <t>檳榔攤停駕</t>
+  </si>
+  <si>
+    <t>停駕民宅(元長鄉民代表會副主席-李進明家)</t>
+  </si>
+  <si>
+    <t>停駕豐盛農業行</t>
+  </si>
+  <si>
+    <t>停駕聖仁彩色布帆</t>
+  </si>
+  <si>
+    <t>停駕西庄2-25號</t>
+  </si>
+  <si>
+    <t>溝皂真武殿牌樓後棚架內停駕(縣158交界處)</t>
+  </si>
+  <si>
+    <t>進僑美國小</t>
+  </si>
+  <si>
+    <t>出美國小</t>
+  </si>
+  <si>
+    <t>北辰派出所停駕</t>
+  </si>
+  <si>
+    <t>信藝花坊停駕</t>
+  </si>
+  <si>
+    <t>宏宬國際車業停駕10分鐘</t>
+  </si>
+  <si>
+    <t>經媽祖醫院</t>
+  </si>
+  <si>
+    <t>土庫秀潭龍興宮蘇王爺廟停駕休息30分</t>
+  </si>
+  <si>
+    <t>土庫順天宮停駕15分</t>
+  </si>
+  <si>
+    <t>土庫鎮農會活動中心停駕15分</t>
+  </si>
+  <si>
+    <t>TOYOTA虎尾服務廠停駕休息至14:00</t>
+  </si>
+  <si>
+    <t>進揚子中學</t>
+  </si>
+  <si>
+    <t>揚子中學行政大樓停駕5分鐘</t>
+  </si>
+  <si>
+    <t>民宅停駕10分鐘。</t>
+  </si>
+  <si>
+    <t>雲林白沙屯媽祖志工團停駕10分鐘。</t>
+  </si>
+  <si>
+    <t>新翰宮停駕</t>
+  </si>
+  <si>
+    <t>福安宮(糖廠媽)停駕30分。</t>
+  </si>
+  <si>
+    <t>虎尾高中駐駕</t>
+  </si>
+  <si>
+    <t>雲林縣警察局虎尾分局停駕10分鐘</t>
+  </si>
+  <si>
+    <t>白沙屯虎尾聖母聯誼會停駕</t>
+  </si>
+  <si>
+    <t>理想家上隆建設停駕十分鐘</t>
+  </si>
+  <si>
+    <t>吳厝朝興宮停駕30分鐘</t>
+  </si>
+  <si>
+    <t>魚寮鎮南宮停駕30分鐘</t>
+  </si>
+  <si>
+    <t>易利鐵材行停駕10分鐘</t>
+  </si>
+  <si>
+    <t>西螺果菜市場停駕午休至14點</t>
+  </si>
+  <si>
+    <t>社口福天宮社口媽祖廟停駕30分鐘</t>
+  </si>
+  <si>
+    <t>三條國小駐駕隔日早上6點起駕。</t>
+  </si>
+  <si>
+    <t>潮洋國小停駕5分</t>
+  </si>
+  <si>
+    <t>318文化廣場停駕15分</t>
+  </si>
+  <si>
+    <t>國姓宮新廟空地踏廟地</t>
+  </si>
+  <si>
+    <t>離開</t>
+  </si>
+  <si>
+    <t>頂寮巷往興天宮停駕15分</t>
+  </si>
+  <si>
+    <t>三合院民宅停駕10分鐘</t>
+  </si>
+  <si>
+    <t>三玄宮停駕休息至14:00</t>
+  </si>
+  <si>
+    <t>田中乾德宮駐駕隔天早上6點起駕</t>
+  </si>
+  <si>
+    <t>協天宮停駕30分鐘</t>
+  </si>
+  <si>
+    <t>民宅停駕20分鐘</t>
+  </si>
+  <si>
+    <t>員林愛買停駕午休</t>
+  </si>
+  <si>
+    <t>彰化市巨翎水果行駐駕</t>
+  </si>
+  <si>
+    <t>大肚追分國小停駕二十分鐘</t>
+  </si>
+  <si>
+    <t>大肚菜市場停駕20分鐘</t>
+  </si>
+  <si>
+    <t>慈興文教基金會停駕</t>
+  </si>
+  <si>
+    <t>梧棲奉安宮停駕二十分鐘</t>
+  </si>
+  <si>
+    <t>大里好運來金紙香量販店駐駕</t>
+  </si>
+  <si>
+    <t>賜海汽車停駕(含這次，第五次停駕賜海汽車)</t>
+  </si>
+  <si>
+    <t>日南靈山慈惠堂點心站停駕十五分鐘</t>
+  </si>
+  <si>
+    <t>停駕名記茶莊(已停駕過四次)</t>
+  </si>
+  <si>
+    <t>立泰水泥停駕</t>
+  </si>
+  <si>
+    <t>順心意點心站停駕</t>
+  </si>
+  <si>
+    <t>進龍德工商</t>
+  </si>
+  <si>
+    <t>離開校園</t>
+  </si>
+  <si>
+    <t>苑裡福特車廠停駕</t>
+  </si>
+  <si>
+    <t>苑裡中山路路口振龍堂停駕</t>
+  </si>
+  <si>
+    <t>苑裡國小停駕</t>
+  </si>
+  <si>
+    <t>五北社區，五北里下的天橋停駕</t>
+  </si>
+  <si>
+    <t>南華社區停駕，休息到一點三十分</t>
+  </si>
+  <si>
+    <t>停駕通霄車站外廣場</t>
+  </si>
+  <si>
+    <t>慈后宮駐駕過夜</t>
+  </si>
+  <si>
+    <t>秋茂園附近台1線省道旁換八人大轎搶頭香</t>
+  </si>
+  <si>
+    <t>停駕新埔北極殿</t>
+  </si>
+  <si>
+    <t>停駕內島里戲台(扮仙戲)</t>
+  </si>
+  <si>
+    <t>午歇白沙屯火車站的戲台</t>
+  </si>
+  <si>
+    <t>白沙屯拱天宮</t>
+  </si>
+  <si>
+    <t>2017</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁酉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>28</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -15426,8 +16171,8 @@
         <v>6</v>
       </c>
       <c r="I3" s="5" t="str">
-        <f>MID(F3, 10, LEN(F3))</f>
-        <v>61西濱快速公路交叉處</v>
+        <f>MID(F4, 6, LEN(F4))</f>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17937,4 +18682,4397 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F99027-ABBA-44D8-AF53-99BF7ED6E227}">
+  <dimension ref="A1:H190"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4818586E-69E9-44E6-B6AB-336AE41A30B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EED711-F76B-43F8-9ADD-1242BCE6EAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="8" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="3" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -4395,7 +4395,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4419,6 +4419,9 @@
     </xf>
     <xf numFmtId="20" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -11497,7 +11500,7 @@
     <col min="2" max="2" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="1"/>
@@ -11516,7 +11519,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -11542,7 +11545,7 @@
       <c r="D2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>180</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -11568,7 +11571,7 @@
       <c r="D3" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>181</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -11594,7 +11597,7 @@
       <c r="D4" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="8" t="s">
         <v>183</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -11620,7 +11623,7 @@
       <c r="D5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="8" t="s">
         <v>184</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -11646,7 +11649,7 @@
       <c r="D6" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="8" t="s">
         <v>185</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -11672,7 +11675,7 @@
       <c r="D7" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="8" t="s">
         <v>186</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -11698,7 +11701,7 @@
       <c r="D8" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -11724,7 +11727,7 @@
       <c r="D9" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="8" t="s">
         <v>190</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -11750,7 +11753,7 @@
       <c r="D10" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="8" t="s">
         <v>191</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -11776,7 +11779,7 @@
       <c r="D11" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="8" t="s">
         <v>193</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -11802,7 +11805,7 @@
       <c r="D12" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="8" t="s">
         <v>194</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -11828,7 +11831,7 @@
       <c r="D13" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -11854,7 +11857,7 @@
       <c r="D14" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -11880,7 +11883,7 @@
       <c r="D15" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="8" t="s">
         <v>199</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -11906,7 +11909,7 @@
       <c r="D16" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="8" t="s">
         <v>201</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -11932,7 +11935,7 @@
       <c r="D17" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="8" t="s">
         <v>202</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -11958,7 +11961,7 @@
       <c r="D18" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="8" t="s">
         <v>63</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -11984,7 +11987,7 @@
       <c r="D19" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -12010,7 +12013,7 @@
       <c r="D20" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="8" t="s">
         <v>205</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -12036,7 +12039,7 @@
       <c r="D21" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="8" t="s">
         <v>206</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -12062,7 +12065,7 @@
       <c r="D22" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="8" t="s">
         <v>207</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -12088,7 +12091,7 @@
       <c r="D23" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -12114,7 +12117,7 @@
       <c r="D24" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="8" t="s">
         <v>211</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -12140,7 +12143,7 @@
       <c r="D25" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="8" t="s">
         <v>212</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -12166,7 +12169,7 @@
       <c r="D26" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -12192,7 +12195,7 @@
       <c r="D27" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -12218,7 +12221,7 @@
       <c r="D28" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="8" t="s">
         <v>216</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -12244,7 +12247,7 @@
       <c r="D29" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="8" t="s">
         <v>202</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -12270,7 +12273,7 @@
       <c r="D30" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="8" t="s">
         <v>217</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -12296,7 +12299,7 @@
       <c r="D31" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="8" t="s">
         <v>171</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -12322,7 +12325,7 @@
       <c r="D32" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="8" t="s">
         <v>75</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -12348,7 +12351,7 @@
       <c r="D33" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F33" s="1" t="s">

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84503DB-5FD4-4781-8716-3710AAE8E416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2DBAF7-FB45-4AF8-83AC-F8365EBE87DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="8" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="-50" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="4" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -4044,7 +4044,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4101,6 +4101,24 @@
     </xf>
     <xf numFmtId="20" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -4484,7 +4502,7 @@
     <col min="2" max="2" width="5.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="11" customWidth="1"/>
     <col min="6" max="6" width="50.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.21875" style="11" bestFit="1" customWidth="1"/>
@@ -12130,7 +12148,7 @@
     <col min="2" max="2" width="6" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="13" customWidth="1"/>
     <col min="6" max="6" width="44.33203125" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="22.44140625" style="15" customWidth="1"/>
@@ -12138,193 +12156,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="20" t="s">
         <v>651</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="19" t="s">
         <v>666</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="19" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
+      <c r="A2" s="21">
         <v>2022</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="21">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="21">
         <v>20</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="23">
         <v>9.375E-2</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>645</v>
       </c>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+      <c r="A3" s="21">
         <v>2022</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="21">
         <v>5</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="21">
         <v>20</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="22" t="s">
         <v>466</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>13</v>
-      </c>
+      <c r="G3" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+      <c r="A4" s="21">
         <v>2022</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="21">
         <v>5</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="21">
         <v>20</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="G4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>13</v>
-      </c>
+      <c r="G4" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+      <c r="A5" s="21">
         <v>2022</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="21">
         <v>5</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="21">
         <v>20</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <v>0.52083333333333337</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="22" t="s">
         <v>743</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="22" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+      <c r="A6" s="21">
         <v>2022</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="21">
         <v>5</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="21">
         <v>20</v>
       </c>
-      <c r="E6" s="17">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="F6" s="15" t="s">
+      <c r="E6" s="23">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>13</v>
-      </c>
+      <c r="G6" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+      <c r="A7" s="21">
         <v>2022</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="21">
         <v>5</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="21">
         <v>20</v>
       </c>
-      <c r="E7" s="17">
-        <v>0.3263888888888889</v>
-      </c>
-      <c r="F7" s="15" t="s">
+      <c r="E7" s="23">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="15" t="s">
+      <c r="G7" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="22" t="s">
         <v>672</v>
       </c>
     </row>
@@ -12611,7 +12633,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="17">
-        <v>0.24305555555555555</v>
+        <v>0.74305555555555558</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>60</v>
@@ -12721,7 +12743,7 @@
         <v>24</v>
       </c>
       <c r="E22" s="17">
-        <v>0.23958333333333334</v>
+        <v>0.73958333333333337</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>139</v>
@@ -12831,7 +12853,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="17">
-        <v>0.24652777777777779</v>
+        <v>0.74652777777777779</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>646</v>
@@ -12941,7 +12963,7 @@
         <v>26</v>
       </c>
       <c r="E30" s="17">
-        <v>6.25E-2</v>
+        <v>0.5625</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>142</v>
@@ -13105,7 +13127,7 @@
   <cols>
     <col min="1" max="2" width="7.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="5.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="13" customWidth="1"/>
     <col min="6" max="6" width="46.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.88671875" style="15" bestFit="1" customWidth="1"/>
@@ -13168,373 +13190,385 @@
         <v>645</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15">
+    <row r="3" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22">
         <v>2021</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="21">
         <v>4</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="21">
         <v>12</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="G3" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
         <v>2021</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="21">
         <v>4</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="21">
         <v>12</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="G4" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
         <v>2021</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="21">
         <v>4</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="21">
         <v>12</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <v>0.18333333333333332</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="G5" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22">
         <v>2021</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="21">
         <v>4</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="21">
         <v>12</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="23">
         <v>0.22013888888888888</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
+      <c r="G6" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
         <v>2021</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="21">
         <v>4</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="21">
         <v>12</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="23">
         <v>0.23541666666666666</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="22" t="s">
         <v>652</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="G7" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22">
         <v>2021</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="21">
         <v>4</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="21">
         <v>12</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15">
+      <c r="G8" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22">
         <v>2021</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="21">
         <v>4</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="21">
         <v>12</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="23">
         <v>0.28541666666666665</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="G9" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22">
         <v>2021</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="21">
         <v>4</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="21">
         <v>12</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="23">
         <v>0.37708333333333333</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
+      <c r="G10" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
         <v>2021</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="21">
         <v>4</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="21">
         <v>12</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="23">
         <v>0.39791666666666664</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="G11" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22">
         <v>2021</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="21">
         <v>4</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="21">
         <v>12</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="23">
         <v>0.45347222222222222</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="22" t="s">
         <v>749</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="15" t="s">
+      <c r="G12" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="I12" s="15" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+      <c r="I12" s="22" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="22">
         <v>2021</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="21">
         <v>4</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="21">
         <v>12</v>
       </c>
-      <c r="E13" s="17">
-        <v>5.2083333333333336E-2</v>
-      </c>
-      <c r="F13" s="15" t="s">
+      <c r="E13" s="23">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="G13" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="22">
         <v>2021</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="21">
         <v>4</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="21">
         <v>12</v>
       </c>
-      <c r="E14" s="17">
-        <v>0.16388888888888889</v>
-      </c>
-      <c r="F14" s="15" t="s">
+      <c r="E14" s="23">
+        <v>0.66388888888888886</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15">
+      <c r="G14" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="22">
         <v>2021</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="21">
         <v>4</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="21">
         <v>12</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="G15" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22">
         <v>2021</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="21">
         <v>4</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="21">
         <v>12</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="15" t="s">
+      <c r="G16" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="22" t="s">
         <v>672</v>
       </c>
     </row>
@@ -14295,7 +14329,7 @@
         <v>15</v>
       </c>
       <c r="E45" s="17">
-        <v>0.12152777777777778</v>
+        <v>0.62152777777777779</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>82</v>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99EDDE3-605A-471A-83BB-3B98021F86EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48340C49-79C3-4DB0-94D0-B9B8CC2273A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3122" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="975">
   <si>
     <t>年份</t>
   </si>
@@ -4170,7 +4170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4263,6 +4263,9 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -10164,9 +10167,59 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="C2" s="11">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11">
+        <v>12</v>
+      </c>
+      <c r="E2" s="31">
+        <v>0.99652777777777779</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>645</v>
+      </c>
       <c r="N2" s="2" t="e">
         <f>MID(#REF!,6,LEN(#REF!))</f>
         <v>#REF!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="C3" s="11">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11">
+        <v>20</v>
+      </c>
+      <c r="E3" s="31">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="6:6" x14ac:dyDescent="0.3">

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48340C49-79C3-4DB0-94D0-B9B8CC2273A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383581D2-8E76-4822-8067-D21876B91A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
   <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="7" customWidth="1"/>
     <col min="4" max="5" width="5.77734375" style="27" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.21875" style="27" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="29" bestFit="1" customWidth="1"/>
@@ -4663,7 +4663,7 @@
       <c r="B1" s="7" t="s">
         <v>946</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="7" t="s">
         <v>948</v>
       </c>
       <c r="D1" s="27" t="s">
@@ -4698,7 +4698,7 @@
       <c r="B2" s="7" t="s">
         <v>947</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="7" t="s">
         <v>949</v>
       </c>
       <c r="D2" s="27" t="s">
@@ -4727,7 +4727,7 @@
       <c r="B3" s="26" t="s">
         <v>956</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="7" t="s">
         <v>957</v>
       </c>
       <c r="D3" s="27" t="s">
@@ -4759,7 +4759,7 @@
       <c r="B4" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="7" t="s">
         <v>960</v>
       </c>
       <c r="D4" s="27" t="s">
@@ -4791,7 +4791,7 @@
       <c r="B5" s="25" t="s">
         <v>964</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="7" t="s">
         <v>960</v>
       </c>
       <c r="D5" s="27" t="s">
@@ -4823,7 +4823,7 @@
       <c r="B6" s="25" t="s">
         <v>966</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="7" t="s">
         <v>949</v>
       </c>
       <c r="D6" s="27" t="s">
@@ -4855,7 +4855,7 @@
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="7" t="s">
         <v>949</v>
       </c>
       <c r="D7" s="27" t="s">
@@ -4887,7 +4887,7 @@
       <c r="B8" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="7" t="s">
         <v>960</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -4922,7 +4922,7 @@
       <c r="B9" s="25" t="s">
         <v>969</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="7" t="s">
         <v>957</v>
       </c>
       <c r="D9" s="27" t="s">
@@ -4954,7 +4954,7 @@
       <c r="B10" s="25" t="s">
         <v>971</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="7" t="s">
         <v>949</v>
       </c>
       <c r="D10" s="27" t="s">
@@ -4986,7 +4986,7 @@
       <c r="B11" s="25" t="s">
         <v>972</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="7" t="s">
         <v>973</v>
       </c>
       <c r="D11" s="27" t="s">

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383581D2-8E76-4822-8067-D21876B91A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6070649-F7E4-468C-B45A-BEFBA29ABAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="-50" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="11" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -24,8 +24,10 @@
     <sheet name="2019" sheetId="8" r:id="rId9"/>
     <sheet name="2018" sheetId="10" r:id="rId10"/>
     <sheet name="2017" sheetId="11" r:id="rId11"/>
+    <sheet name="2016" sheetId="15" r:id="rId12"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2016'!$A$1:$I$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'2017'!$A$1:$I$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2018'!$A$1:$I$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2020'!$A$1:$I$54</definedName>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1105">
   <si>
     <t>年份</t>
   </si>
@@ -3532,6 +3534,538 @@
   </si>
   <si>
     <t>7天</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>丙申</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11天10夜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/16/3/21 05:45</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇回鑾停駕戲棚地</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三仔老里長家門前</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新埔北極殿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>01:34起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宅(通灣里53-3號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>03:06起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至07:25起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苑裡李綜合醫院</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>立泰水泥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日南名記茶行</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第四次停駕於此</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>大甲北</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>裕塑膠(大甲區中山路二段903號)</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲天王星音響有限公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>笠毅工業</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔日05:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至06:52起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三光佛俱行</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至07:27起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山路533號與535號之間的中庭(兆豐銀行與元大銀行二棟大樓之間)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至08:34起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至09:20起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>東晉福亨宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至11:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宅(向上路七段顏清標住宅)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大肚派出所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化市中山路三段162巷(陽光城市大廈中庭)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化火車站</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化市果菜市場</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宅(福興鄉番婆村番婆街43-25號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至09:38起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>慶豐富實業公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上麥厝橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進王功</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>天地堂地靈宮地母廟(彰花芳苑鄉芳苑村芳漢路二段243號)(</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至07:01起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上西濱大橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西濱大橋橋下P7橋墩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵達沙崙</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拱範宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進台西鄉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進東勢鄉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>東勢鄉四美路19-1號對面</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>東勢鄉賜安宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔日04:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進四湖鄉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進元長鄉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>元長鄉中山路35號</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>元長觀音佛祖對面</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>元長白沙屯媽祖會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至09:03起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經新街巡天宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至10:43起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜天公</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息壓07:27起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經北港武德宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宅(元長鄉西庄村10-21號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雜糧生產合作社(元長鄉西庄村200號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>虎尾分局元長分駐所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至14:10起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上豐橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下豐橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進崙背鄉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔日06:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>崙背賜福安(雲林縣二崙鄉田尾村田尾路92號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至08:30起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西螺吳厝朝興宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西螺農運銷中心果菜批發市場農會大樓(西螺鎮新社205-100號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>福天宮(西螺鎮社口路88號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至16:27起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上西螺大橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下西螺大橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>溪州后天宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北斗農產運銷鎖北斗市場</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彩藝藝品中心(回尾鄉田尾村民族路一段143-2號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>碧天宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經永靖國小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>楓康超市永靖店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>五汴頭天聖宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進員林市</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進大村國中</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>花壇聯誼會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BMW昌一汽車巡視</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>永祥輪胎(彰化聯誼會)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經追分派出所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進追分國小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙田路一段450號門前</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙田路一段892號</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大肚公有零售市場(大月區沙田路二段707號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至10:20起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>極限羽球訓練中心(沙田路四段32號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經龍井區戶政事務所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進龍井</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進沙鹿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經鹿峰國小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經清水高中</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經清水紫雲巖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至18:08起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進大甲</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上大甲溪橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下大甲溪橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>欣芳塑鋼工業有限公司(大甲區中山路一段422號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔04:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲鎮瀾宮廟埕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上大安溪橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下大安溪橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>永春不動產苑裡加盟店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經文苑國小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>上東門橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下東門橋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苑裡振龍堂搭設之迎駕處</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苑裡鎮長服務處(苑裡鎮苑北里中山路165號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經苑裡車站</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經苑裡慈和宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進通霄鎮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄五福陸橋下</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄市區南華社區</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄媽祖廟</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宅(鎮長家)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至13:55起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至14:10</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經福智寺</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經通霄國中</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔07:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>換八人大轎</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>經埔口派出所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新埔里民搭設之帳篷</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宅(戲棚地)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3542,7 +4076,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3728,6 +4262,13 @@
       <color rgb="FF202122"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4170,7 +4711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4266,6 +4807,15 @@
     </xf>
     <xf numFmtId="20" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -4642,13 +5192,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3F28DB-C154-4233-B038-4B4939AF5845}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="7" customWidth="1"/>
     <col min="4" max="5" width="5.77734375" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="29" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15.21875" style="27" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" style="30"/>
@@ -4672,7 +5222,7 @@
       <c r="E1" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="7" t="s">
         <v>951</v>
       </c>
       <c r="G1" s="29" t="s">
@@ -4707,7 +5257,7 @@
       <c r="E2" s="27" t="s">
         <v>950</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="34">
         <v>46124.996527777781</v>
       </c>
       <c r="G2" s="29">
@@ -4736,7 +5286,7 @@
       <c r="E3" s="27" t="s">
         <v>959</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="34">
         <v>45778.975694444445</v>
       </c>
       <c r="G3" s="29">
@@ -4768,7 +5318,7 @@
       <c r="E4" s="27" t="s">
         <v>962</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="34">
         <v>45369.024305555555</v>
       </c>
       <c r="G4" s="29">
@@ -4800,7 +5350,7 @@
       <c r="E5" s="27" t="s">
         <v>962</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="7" t="s">
         <v>965</v>
       </c>
       <c r="G5" s="29">
@@ -4832,7 +5382,7 @@
       <c r="E6" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="34">
         <v>44701.09375</v>
       </c>
       <c r="G6" s="29">
@@ -4864,7 +5414,7 @@
       <c r="E7" s="27" t="s">
         <v>962</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="34">
         <v>44297.986111111109</v>
       </c>
       <c r="G7" s="29">
@@ -4896,7 +5446,7 @@
       <c r="E8" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="34">
         <v>44017.09375</v>
       </c>
       <c r="G8" s="29">
@@ -4931,7 +5481,7 @@
       <c r="E9" s="27" t="s">
         <v>961</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="34">
         <v>43563.055555555555</v>
       </c>
       <c r="G9" s="29">
@@ -4963,7 +5513,7 @@
       <c r="E10" s="27" t="s">
         <v>961</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="34">
         <v>43236.986111111109</v>
       </c>
       <c r="G10" s="29">
@@ -4995,7 +5545,7 @@
       <c r="E11" s="27" t="s">
         <v>974</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="34">
         <v>42792.104166666664</v>
       </c>
       <c r="G11" s="29">
@@ -5009,6 +5559,38 @@
       </c>
       <c r="J11" s="30">
         <v>26669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>2016</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>975</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>976</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>967</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>961</v>
+      </c>
+      <c r="F12" s="34">
+        <v>42445.020833333336</v>
+      </c>
+      <c r="G12" s="29">
+        <v>42449</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>977</v>
+      </c>
+      <c r="I12" s="28">
+        <v>42455.625</v>
+      </c>
+      <c r="J12" s="30">
+        <v>19437</v>
       </c>
     </row>
   </sheetData>
@@ -10109,6 +10691,3407 @@
         <v>113</v>
       </c>
       <c r="H121" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACA328A-A8D3-4347-9AEB-FEEF266FA468}">
+  <dimension ref="A1:I129"/>
+  <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.44140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H1" t="s">
+        <v>666</v>
+      </c>
+      <c r="I1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C2" s="33">
+        <v>3</v>
+      </c>
+      <c r="D2" s="33">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C3" s="33">
+        <v>3</v>
+      </c>
+      <c r="D3" s="33">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6">
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C4" s="33">
+        <v>3</v>
+      </c>
+      <c r="D4" s="33">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6">
+        <v>6.1111111111111109E-2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C5" s="33">
+        <v>3</v>
+      </c>
+      <c r="D5" s="33">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.12222222222222222</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C6" s="33">
+        <v>3</v>
+      </c>
+      <c r="D6" s="33">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C7" s="33">
+        <v>3</v>
+      </c>
+      <c r="D7" s="33">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.33194444444444443</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C8" s="33">
+        <v>3</v>
+      </c>
+      <c r="D8" s="33">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.37569444444444444</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C9" s="33">
+        <v>3</v>
+      </c>
+      <c r="D9" s="33">
+        <v>16</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.40763888888888888</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C10" s="33">
+        <v>3</v>
+      </c>
+      <c r="D10" s="33">
+        <v>16</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C11" s="33">
+        <v>3</v>
+      </c>
+      <c r="D11" s="33">
+        <v>16</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.67638888888888893</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C12" s="33">
+        <v>3</v>
+      </c>
+      <c r="D12" s="33">
+        <v>16</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.77361111111111114</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C13" s="33">
+        <v>3</v>
+      </c>
+      <c r="D13" s="33">
+        <v>17</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C14" s="33">
+        <v>3</v>
+      </c>
+      <c r="D14" s="33">
+        <v>17</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C15" s="33">
+        <v>3</v>
+      </c>
+      <c r="D15" s="33">
+        <v>17</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C16" s="33">
+        <v>3</v>
+      </c>
+      <c r="D16" s="33">
+        <v>17</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.34166666666666667</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C17" s="33">
+        <v>3</v>
+      </c>
+      <c r="D17" s="33">
+        <v>17</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C18" s="33">
+        <v>3</v>
+      </c>
+      <c r="D18" s="33">
+        <v>17</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C19" s="33">
+        <v>3</v>
+      </c>
+      <c r="D19" s="33">
+        <v>17</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C20" s="33">
+        <v>3</v>
+      </c>
+      <c r="D20" s="33">
+        <v>17</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.69236111111111109</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C21" s="33">
+        <v>3</v>
+      </c>
+      <c r="D21" s="33">
+        <v>17</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.81388888888888888</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C22" s="33">
+        <v>3</v>
+      </c>
+      <c r="D22" s="33">
+        <v>18</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C23" s="33">
+        <v>3</v>
+      </c>
+      <c r="D23" s="33">
+        <v>18</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C24" s="33">
+        <v>3</v>
+      </c>
+      <c r="D24" s="33">
+        <v>18</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C25" s="33">
+        <v>3</v>
+      </c>
+      <c r="D25" s="33">
+        <v>18</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C26" s="33">
+        <v>3</v>
+      </c>
+      <c r="D26" s="33">
+        <v>18</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.46805555555555556</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C27" s="33">
+        <v>3</v>
+      </c>
+      <c r="D27" s="33">
+        <v>18</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C28" s="33">
+        <v>3</v>
+      </c>
+      <c r="D28" s="33">
+        <v>18</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C29" s="33">
+        <v>3</v>
+      </c>
+      <c r="D29" s="33">
+        <v>18</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.70902777777777781</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C30" s="33">
+        <v>3</v>
+      </c>
+      <c r="D30" s="33">
+        <v>19</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C31" s="33">
+        <v>3</v>
+      </c>
+      <c r="D31" s="33">
+        <v>19</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.28402777777777777</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C32" s="33">
+        <v>3</v>
+      </c>
+      <c r="D32" s="33">
+        <v>19</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C33" s="33">
+        <v>3</v>
+      </c>
+      <c r="D33" s="33">
+        <v>19</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C34" s="33">
+        <v>3</v>
+      </c>
+      <c r="D34" s="33">
+        <v>19</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.6069444444444444</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C35" s="33">
+        <v>3</v>
+      </c>
+      <c r="D35" s="33">
+        <v>19</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.66041666666666665</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C36" s="33">
+        <v>3</v>
+      </c>
+      <c r="D36" s="33">
+        <v>19</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.68333333333333335</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C37" s="33">
+        <v>3</v>
+      </c>
+      <c r="D37" s="33">
+        <v>19</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C38" s="33">
+        <v>3</v>
+      </c>
+      <c r="D38" s="33">
+        <v>19</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C39" s="33">
+        <v>3</v>
+      </c>
+      <c r="D39" s="33">
+        <v>19</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C40" s="33">
+        <v>3</v>
+      </c>
+      <c r="D40" s="33">
+        <v>20</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C41" s="33">
+        <v>3</v>
+      </c>
+      <c r="D41" s="33">
+        <v>20</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.19583333333333333</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C42" s="33">
+        <v>3</v>
+      </c>
+      <c r="D42" s="33">
+        <v>20</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.21041666666666667</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C43" s="33">
+        <v>3</v>
+      </c>
+      <c r="D43" s="33">
+        <v>20</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.26805555555555555</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C44" s="33">
+        <v>3</v>
+      </c>
+      <c r="D44" s="33">
+        <v>20</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C45" s="33">
+        <v>3</v>
+      </c>
+      <c r="D45" s="33">
+        <v>20</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C46" s="33">
+        <v>3</v>
+      </c>
+      <c r="D46" s="33">
+        <v>20</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C47" s="33">
+        <v>3</v>
+      </c>
+      <c r="D47" s="33">
+        <v>20</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C48" s="33">
+        <v>3</v>
+      </c>
+      <c r="D48" s="33">
+        <v>20</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C49" s="33">
+        <v>3</v>
+      </c>
+      <c r="D49" s="33">
+        <v>20</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C50" s="33">
+        <v>3</v>
+      </c>
+      <c r="D50" s="33">
+        <v>21</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C51" s="33">
+        <v>3</v>
+      </c>
+      <c r="D51" s="33">
+        <v>21</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.28958333333333336</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C52" s="33">
+        <v>3</v>
+      </c>
+      <c r="D52" s="33">
+        <v>21</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.33194444444444443</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C53" s="33">
+        <v>3</v>
+      </c>
+      <c r="D53" s="33">
+        <v>21</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0.39166666666666666</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C54" s="33">
+        <v>3</v>
+      </c>
+      <c r="D54" s="33">
+        <v>21</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0.41180555555555554</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B55" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C55" s="33">
+        <v>3</v>
+      </c>
+      <c r="D55" s="33">
+        <v>21</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C56" s="33">
+        <v>3</v>
+      </c>
+      <c r="D56" s="33">
+        <v>21</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0.48472222222222222</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C57" s="33">
+        <v>3</v>
+      </c>
+      <c r="D57" s="33">
+        <v>21</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.71319444444444446</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C58" s="33">
+        <v>3</v>
+      </c>
+      <c r="D58" s="33">
+        <v>21</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.71944444444444444</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B59" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C59" s="33">
+        <v>3</v>
+      </c>
+      <c r="D59" s="33">
+        <v>21</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C60" s="33">
+        <v>3</v>
+      </c>
+      <c r="D60" s="33">
+        <v>21</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B61" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C61" s="33">
+        <v>3</v>
+      </c>
+      <c r="D61" s="33">
+        <v>22</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B62" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C62" s="33">
+        <v>3</v>
+      </c>
+      <c r="D62" s="33">
+        <v>22</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.3298611111111111</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B63" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C63" s="33">
+        <v>3</v>
+      </c>
+      <c r="D63" s="33">
+        <v>22</v>
+      </c>
+      <c r="E63" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B64" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C64" s="33">
+        <v>3</v>
+      </c>
+      <c r="D64" s="33">
+        <v>22</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0.43611111111111112</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B65" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C65" s="33">
+        <v>3</v>
+      </c>
+      <c r="D65" s="33">
+        <v>22</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B66" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C66" s="33">
+        <v>3</v>
+      </c>
+      <c r="D66" s="33">
+        <v>22</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B67" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C67" s="33">
+        <v>3</v>
+      </c>
+      <c r="D67" s="33">
+        <v>22</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.73541666666666672</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C68" s="33">
+        <v>3</v>
+      </c>
+      <c r="D68" s="33">
+        <v>22</v>
+      </c>
+      <c r="E68" s="6">
+        <v>0.75138888888888888</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B69" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C69" s="33">
+        <v>3</v>
+      </c>
+      <c r="D69" s="33">
+        <v>22</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B70" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C70" s="33">
+        <v>3</v>
+      </c>
+      <c r="D70" s="33">
+        <v>23</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C71" s="33">
+        <v>3</v>
+      </c>
+      <c r="D71" s="33">
+        <v>23</v>
+      </c>
+      <c r="E71" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B72" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C72" s="33">
+        <v>3</v>
+      </c>
+      <c r="D72" s="33">
+        <v>23</v>
+      </c>
+      <c r="E72" s="6">
+        <v>0.38819444444444445</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B73" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C73" s="33">
+        <v>3</v>
+      </c>
+      <c r="D73" s="33">
+        <v>23</v>
+      </c>
+      <c r="E73" s="6">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C74" s="33">
+        <v>3</v>
+      </c>
+      <c r="D74" s="33">
+        <v>23</v>
+      </c>
+      <c r="E74" s="6">
+        <v>0.47083333333333333</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B75" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C75" s="33">
+        <v>3</v>
+      </c>
+      <c r="D75" s="33">
+        <v>23</v>
+      </c>
+      <c r="E75" s="6">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B76" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C76" s="33">
+        <v>3</v>
+      </c>
+      <c r="D76" s="33">
+        <v>23</v>
+      </c>
+      <c r="E76" s="6">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B77" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C77" s="33">
+        <v>3</v>
+      </c>
+      <c r="D77" s="33">
+        <v>23</v>
+      </c>
+      <c r="E77" s="6">
+        <v>0.63055555555555554</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B78" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C78" s="33">
+        <v>3</v>
+      </c>
+      <c r="D78" s="33">
+        <v>23</v>
+      </c>
+      <c r="E78" s="6">
+        <v>0.70416666666666672</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C79" s="33">
+        <v>3</v>
+      </c>
+      <c r="D79" s="33">
+        <v>23</v>
+      </c>
+      <c r="E79" s="6">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B80" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C80" s="33">
+        <v>3</v>
+      </c>
+      <c r="D80" s="33">
+        <v>24</v>
+      </c>
+      <c r="E80" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C81" s="33">
+        <v>3</v>
+      </c>
+      <c r="D81" s="33">
+        <v>24</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0.16944444444444445</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C82" s="33">
+        <v>3</v>
+      </c>
+      <c r="D82" s="33">
+        <v>24</v>
+      </c>
+      <c r="E82" s="6">
+        <v>0.23472222222222222</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C83" s="33">
+        <v>3</v>
+      </c>
+      <c r="D83" s="33">
+        <v>24</v>
+      </c>
+      <c r="E83" s="6">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C84" s="33">
+        <v>3</v>
+      </c>
+      <c r="D84" s="33">
+        <v>24</v>
+      </c>
+      <c r="E84" s="6">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C85" s="33">
+        <v>3</v>
+      </c>
+      <c r="D85" s="33">
+        <v>24</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C86" s="33">
+        <v>3</v>
+      </c>
+      <c r="D86" s="33">
+        <v>24</v>
+      </c>
+      <c r="E86" s="6">
+        <v>0.37361111111111112</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B87" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C87" s="33">
+        <v>3</v>
+      </c>
+      <c r="D87" s="33">
+        <v>24</v>
+      </c>
+      <c r="E87" s="6">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C88" s="33">
+        <v>3</v>
+      </c>
+      <c r="D88" s="33">
+        <v>24</v>
+      </c>
+      <c r="E88" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B89" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C89" s="33">
+        <v>3</v>
+      </c>
+      <c r="D89" s="33">
+        <v>24</v>
+      </c>
+      <c r="E89" s="6">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B90" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C90" s="33">
+        <v>3</v>
+      </c>
+      <c r="D90" s="33">
+        <v>24</v>
+      </c>
+      <c r="E90" s="6">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B91" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C91" s="33">
+        <v>3</v>
+      </c>
+      <c r="D91" s="33">
+        <v>24</v>
+      </c>
+      <c r="E91" s="6">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B92" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C92" s="33">
+        <v>3</v>
+      </c>
+      <c r="D92" s="33">
+        <v>24</v>
+      </c>
+      <c r="E92" s="6">
+        <v>0.67222222222222228</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C93" s="33">
+        <v>3</v>
+      </c>
+      <c r="D93" s="33">
+        <v>24</v>
+      </c>
+      <c r="E93" s="6">
+        <v>0.68611111111111112</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C94" s="33">
+        <v>3</v>
+      </c>
+      <c r="D94" s="33">
+        <v>24</v>
+      </c>
+      <c r="E94" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B95" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C95" s="33">
+        <v>3</v>
+      </c>
+      <c r="D95" s="33">
+        <v>24</v>
+      </c>
+      <c r="E95" s="6">
+        <v>0.71388888888888891</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C96" s="33">
+        <v>3</v>
+      </c>
+      <c r="D96" s="33">
+        <v>24</v>
+      </c>
+      <c r="E96" s="6">
+        <v>0.7993055555555556</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C97" s="33">
+        <v>3</v>
+      </c>
+      <c r="D97" s="33">
+        <v>24</v>
+      </c>
+      <c r="E97" s="6">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B98" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C98" s="33">
+        <v>3</v>
+      </c>
+      <c r="D98" s="33">
+        <v>24</v>
+      </c>
+      <c r="E98" s="6">
+        <v>0.81527777777777777</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B99" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C99" s="33">
+        <v>3</v>
+      </c>
+      <c r="D99" s="33">
+        <v>24</v>
+      </c>
+      <c r="E99" s="6">
+        <v>0.82986111111111116</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B100" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C100" s="33">
+        <v>3</v>
+      </c>
+      <c r="D100" s="33">
+        <v>25</v>
+      </c>
+      <c r="E100" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B101" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C101" s="33">
+        <v>3</v>
+      </c>
+      <c r="D101" s="33">
+        <v>25</v>
+      </c>
+      <c r="E101" s="6">
+        <v>0.18055555555555555</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B102" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C102" s="33">
+        <v>3</v>
+      </c>
+      <c r="D102" s="33">
+        <v>25</v>
+      </c>
+      <c r="E102" s="6">
+        <v>0.21111111111111111</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B103" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C103" s="33">
+        <v>3</v>
+      </c>
+      <c r="D103" s="33">
+        <v>25</v>
+      </c>
+      <c r="E103" s="6">
+        <v>0.21875</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B104" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C104" s="33">
+        <v>3</v>
+      </c>
+      <c r="D104" s="33">
+        <v>25</v>
+      </c>
+      <c r="E104" s="6">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B105" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C105" s="33">
+        <v>3</v>
+      </c>
+      <c r="D105" s="33">
+        <v>25</v>
+      </c>
+      <c r="E105" s="6">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B106" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C106" s="33">
+        <v>3</v>
+      </c>
+      <c r="D106" s="33">
+        <v>25</v>
+      </c>
+      <c r="E106" s="6">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B107" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C107" s="33">
+        <v>3</v>
+      </c>
+      <c r="D107" s="33">
+        <v>25</v>
+      </c>
+      <c r="E107" s="6">
+        <v>0.32569444444444445</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B108" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C108" s="33">
+        <v>3</v>
+      </c>
+      <c r="D108" s="33">
+        <v>25</v>
+      </c>
+      <c r="E108" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B109" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C109" s="33">
+        <v>3</v>
+      </c>
+      <c r="D109" s="33">
+        <v>25</v>
+      </c>
+      <c r="E109" s="6">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B110" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C110" s="33">
+        <v>3</v>
+      </c>
+      <c r="D110" s="33">
+        <v>25</v>
+      </c>
+      <c r="E110" s="6">
+        <v>0.36319444444444443</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B111" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C111" s="33">
+        <v>3</v>
+      </c>
+      <c r="D111" s="33">
+        <v>25</v>
+      </c>
+      <c r="E111" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B112" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C112" s="33">
+        <v>3</v>
+      </c>
+      <c r="D112" s="33">
+        <v>25</v>
+      </c>
+      <c r="E112" s="6">
+        <v>0.39305555555555555</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B113" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C113" s="33">
+        <v>3</v>
+      </c>
+      <c r="D113" s="33">
+        <v>25</v>
+      </c>
+      <c r="E113" s="6">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B114" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C114" s="33">
+        <v>3</v>
+      </c>
+      <c r="D114" s="33">
+        <v>25</v>
+      </c>
+      <c r="E114" s="6">
+        <v>0.44305555555555554</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B115" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C115" s="33">
+        <v>3</v>
+      </c>
+      <c r="D115" s="33">
+        <v>25</v>
+      </c>
+      <c r="E115" s="6">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B116" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C116" s="33">
+        <v>3</v>
+      </c>
+      <c r="D116" s="33">
+        <v>25</v>
+      </c>
+      <c r="E116" s="6">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B117" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C117" s="33">
+        <v>3</v>
+      </c>
+      <c r="D117" s="33">
+        <v>25</v>
+      </c>
+      <c r="E117" s="6">
+        <v>0.55138888888888893</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B118" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C118" s="33">
+        <v>3</v>
+      </c>
+      <c r="D118" s="33">
+        <v>25</v>
+      </c>
+      <c r="E118" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B119" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C119" s="33">
+        <v>3</v>
+      </c>
+      <c r="D119" s="33">
+        <v>25</v>
+      </c>
+      <c r="E119" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B120" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C120" s="33">
+        <v>3</v>
+      </c>
+      <c r="D120" s="33">
+        <v>25</v>
+      </c>
+      <c r="E120" s="6">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B121" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C121" s="33">
+        <v>3</v>
+      </c>
+      <c r="D121" s="33">
+        <v>25</v>
+      </c>
+      <c r="E121" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B122" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C122" s="33">
+        <v>3</v>
+      </c>
+      <c r="D122" s="33">
+        <v>25</v>
+      </c>
+      <c r="E122" s="6">
+        <v>0.62291666666666667</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B123" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C123" s="33">
+        <v>3</v>
+      </c>
+      <c r="D123" s="33">
+        <v>26</v>
+      </c>
+      <c r="E123" s="6">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B124" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C124" s="33">
+        <v>3</v>
+      </c>
+      <c r="D124" s="33">
+        <v>26</v>
+      </c>
+      <c r="E124" s="6">
+        <v>0.35972222222222222</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B125" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C125" s="33">
+        <v>3</v>
+      </c>
+      <c r="D125" s="33">
+        <v>26</v>
+      </c>
+      <c r="E125" s="6">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B126" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C126" s="33">
+        <v>3</v>
+      </c>
+      <c r="D126" s="33">
+        <v>26</v>
+      </c>
+      <c r="E126" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B127" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C127" s="33">
+        <v>3</v>
+      </c>
+      <c r="D127" s="33">
+        <v>26</v>
+      </c>
+      <c r="E127" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B128" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C128" s="33">
+        <v>3</v>
+      </c>
+      <c r="D128" s="33">
+        <v>26</v>
+      </c>
+      <c r="E128" s="6">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="33">
+        <v>2016</v>
+      </c>
+      <c r="B129" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C129" s="33">
+        <v>3</v>
+      </c>
+      <c r="D129" s="33">
+        <v>26</v>
+      </c>
+      <c r="E129" s="6">
+        <v>0.62638888888888888</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H129" s="1" t="s">
         <v>126</v>
       </c>
     </row>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6070649-F7E4-468C-B45A-BEFBA29ABAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8968BE6-0DFE-40EA-BCA5-5D8F621F22C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="11" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="10" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -4711,7 +4711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4806,12 +4806,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -5257,7 +5251,7 @@
       <c r="E2" s="27" t="s">
         <v>950</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="32">
         <v>46124.996527777781</v>
       </c>
       <c r="G2" s="29">
@@ -5286,7 +5280,7 @@
       <c r="E3" s="27" t="s">
         <v>959</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="32">
         <v>45778.975694444445</v>
       </c>
       <c r="G3" s="29">
@@ -5318,7 +5312,7 @@
       <c r="E4" s="27" t="s">
         <v>962</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="32">
         <v>45369.024305555555</v>
       </c>
       <c r="G4" s="29">
@@ -5382,7 +5376,7 @@
       <c r="E6" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="32">
         <v>44701.09375</v>
       </c>
       <c r="G6" s="29">
@@ -5414,7 +5408,7 @@
       <c r="E7" s="27" t="s">
         <v>962</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="32">
         <v>44297.986111111109</v>
       </c>
       <c r="G7" s="29">
@@ -5446,7 +5440,7 @@
       <c r="E8" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="32">
         <v>44017.09375</v>
       </c>
       <c r="G8" s="29">
@@ -5481,7 +5475,7 @@
       <c r="E9" s="27" t="s">
         <v>961</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="32">
         <v>43563.055555555555</v>
       </c>
       <c r="G9" s="29">
@@ -5513,7 +5507,7 @@
       <c r="E10" s="27" t="s">
         <v>961</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="32">
         <v>43236.986111111109</v>
       </c>
       <c r="G10" s="29">
@@ -5545,7 +5539,7 @@
       <c r="E11" s="27" t="s">
         <v>974</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="32">
         <v>42792.104166666664</v>
       </c>
       <c r="G11" s="29">
@@ -5577,7 +5571,7 @@
       <c r="E12" s="27" t="s">
         <v>961</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="32">
         <v>42445.020833333336</v>
       </c>
       <c r="G12" s="29">
@@ -10705,10 +10699,10 @@
   <dimension ref="A1:I129"/>
   <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.77734375" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -10718,16 +10712,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
@@ -10747,16 +10741,16 @@
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33">
+      <c r="A2" s="2">
         <v>2016</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C2" s="33">
-        <v>3</v>
-      </c>
-      <c r="D2" s="33">
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2">
         <v>16</v>
       </c>
       <c r="E2" s="6">
@@ -10773,16 +10767,16 @@
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33">
+      <c r="A3" s="2">
         <v>2016</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C3" s="33">
-        <v>3</v>
-      </c>
-      <c r="D3" s="33">
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2">
         <v>16</v>
       </c>
       <c r="E3" s="6">
@@ -10799,16 +10793,16 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33">
+      <c r="A4" s="2">
         <v>2016</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C4" s="33">
-        <v>3</v>
-      </c>
-      <c r="D4" s="33">
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
         <v>16</v>
       </c>
       <c r="E4" s="6">
@@ -10828,16 +10822,16 @@
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33">
+      <c r="A5" s="2">
         <v>2016</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C5" s="33">
-        <v>3</v>
-      </c>
-      <c r="D5" s="33">
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
         <v>16</v>
       </c>
       <c r="E5" s="6">
@@ -10857,16 +10851,16 @@
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33">
+      <c r="A6" s="2">
         <v>2016</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C6" s="33">
-        <v>3</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
         <v>16</v>
       </c>
       <c r="E6" s="6">
@@ -10886,16 +10880,16 @@
       </c>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33">
+      <c r="A7" s="2">
         <v>2016</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C7" s="33">
-        <v>3</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
         <v>16</v>
       </c>
       <c r="E7" s="6">
@@ -10912,16 +10906,16 @@
       </c>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33">
+      <c r="A8" s="2">
         <v>2016</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C8" s="33">
-        <v>3</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
         <v>16</v>
       </c>
       <c r="E8" s="6">
@@ -10938,16 +10932,16 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33">
+      <c r="A9" s="2">
         <v>2016</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C9" s="33">
-        <v>3</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
         <v>16</v>
       </c>
       <c r="E9" s="6">
@@ -10967,16 +10961,16 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33">
+      <c r="A10" s="2">
         <v>2016</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C10" s="33">
-        <v>3</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
         <v>16</v>
       </c>
       <c r="E10" s="6">
@@ -10993,16 +10987,16 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33">
+      <c r="A11" s="2">
         <v>2016</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C11" s="33">
-        <v>3</v>
-      </c>
-      <c r="D11" s="33">
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
         <v>16</v>
       </c>
       <c r="E11" s="6">
@@ -11019,16 +11013,16 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33">
+      <c r="A12" s="2">
         <v>2016</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C12" s="33">
-        <v>3</v>
-      </c>
-      <c r="D12" s="33">
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
         <v>16</v>
       </c>
       <c r="E12" s="6">
@@ -11048,16 +11042,16 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33">
+      <c r="A13" s="2">
         <v>2016</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C13" s="33">
-        <v>3</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
         <v>17</v>
       </c>
       <c r="E13" s="6">
@@ -11074,16 +11068,16 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33">
+      <c r="A14" s="2">
         <v>2016</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C14" s="33">
-        <v>3</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
         <v>17</v>
       </c>
       <c r="E14" s="6">
@@ -11103,16 +11097,16 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33">
+      <c r="A15" s="2">
         <v>2016</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C15" s="33">
-        <v>3</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
         <v>17</v>
       </c>
       <c r="E15" s="6">
@@ -11132,16 +11126,16 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33">
+      <c r="A16" s="2">
         <v>2016</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C16" s="33">
-        <v>3</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
         <v>17</v>
       </c>
       <c r="E16" s="6">
@@ -11161,16 +11155,16 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33">
+      <c r="A17" s="2">
         <v>2016</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C17" s="33">
-        <v>3</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
         <v>17</v>
       </c>
       <c r="E17" s="6">
@@ -11190,16 +11184,16 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33">
+      <c r="A18" s="2">
         <v>2016</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C18" s="33">
-        <v>3</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
         <v>17</v>
       </c>
       <c r="E18" s="6">
@@ -11219,16 +11213,16 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33">
+      <c r="A19" s="2">
         <v>2016</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C19" s="33">
-        <v>3</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
         <v>17</v>
       </c>
       <c r="E19" s="6">
@@ -11248,16 +11242,16 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33">
+      <c r="A20" s="2">
         <v>2016</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C20" s="33">
-        <v>3</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
         <v>17</v>
       </c>
       <c r="E20" s="6">
@@ -11274,16 +11268,16 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="33">
+      <c r="A21" s="2">
         <v>2016</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C21" s="33">
-        <v>3</v>
-      </c>
-      <c r="D21" s="33">
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
         <v>17</v>
       </c>
       <c r="E21" s="6">
@@ -11303,16 +11297,16 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33">
+      <c r="A22" s="2">
         <v>2016</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C22" s="33">
-        <v>3</v>
-      </c>
-      <c r="D22" s="33">
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
         <v>18</v>
       </c>
       <c r="E22" s="6">
@@ -11329,16 +11323,16 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33">
+      <c r="A23" s="2">
         <v>2016</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C23" s="33">
-        <v>3</v>
-      </c>
-      <c r="D23" s="33">
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
         <v>18</v>
       </c>
       <c r="E23" s="6">
@@ -11352,16 +11346,16 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="33">
+      <c r="A24" s="2">
         <v>2016</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C24" s="33">
-        <v>3</v>
-      </c>
-      <c r="D24" s="33">
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>18</v>
       </c>
       <c r="E24" s="6">
@@ -11381,16 +11375,16 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="33">
+      <c r="A25" s="2">
         <v>2016</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C25" s="33">
-        <v>3</v>
-      </c>
-      <c r="D25" s="33">
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
         <v>18</v>
       </c>
       <c r="E25" s="6">
@@ -11410,16 +11404,16 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="33">
+      <c r="A26" s="2">
         <v>2016</v>
       </c>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C26" s="33">
-        <v>3</v>
-      </c>
-      <c r="D26" s="33">
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
         <v>18</v>
       </c>
       <c r="E26" s="6">
@@ -11439,16 +11433,16 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33">
+      <c r="A27" s="2">
         <v>2016</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C27" s="33">
-        <v>3</v>
-      </c>
-      <c r="D27" s="33">
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
         <v>18</v>
       </c>
       <c r="E27" s="6">
@@ -11462,16 +11456,16 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="33">
+      <c r="A28" s="2">
         <v>2016</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C28" s="33">
-        <v>3</v>
-      </c>
-      <c r="D28" s="33">
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
         <v>18</v>
       </c>
       <c r="E28" s="6">
@@ -11485,16 +11479,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="33">
+      <c r="A29" s="2">
         <v>2016</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C29" s="33">
-        <v>3</v>
-      </c>
-      <c r="D29" s="33">
+      <c r="C29" s="2">
+        <v>3</v>
+      </c>
+      <c r="D29" s="2">
         <v>18</v>
       </c>
       <c r="E29" s="6">
@@ -11514,16 +11508,16 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="33">
+      <c r="A30" s="2">
         <v>2016</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C30" s="33">
-        <v>3</v>
-      </c>
-      <c r="D30" s="33">
+      <c r="C30" s="2">
+        <v>3</v>
+      </c>
+      <c r="D30" s="2">
         <v>19</v>
       </c>
       <c r="E30" s="6">
@@ -11540,16 +11534,16 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="33">
+      <c r="A31" s="2">
         <v>2016</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C31" s="33">
-        <v>3</v>
-      </c>
-      <c r="D31" s="33">
+      <c r="C31" s="2">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2">
         <v>19</v>
       </c>
       <c r="E31" s="6">
@@ -11569,16 +11563,16 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33">
+      <c r="A32" s="2">
         <v>2016</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C32" s="33">
-        <v>3</v>
-      </c>
-      <c r="D32" s="33">
+      <c r="C32" s="2">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2">
         <v>19</v>
       </c>
       <c r="E32" s="6">
@@ -11592,16 +11586,16 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="33">
+      <c r="A33" s="2">
         <v>2016</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C33" s="33">
-        <v>3</v>
-      </c>
-      <c r="D33" s="33">
+      <c r="C33" s="2">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
         <v>19</v>
       </c>
       <c r="E33" s="6">
@@ -11621,16 +11615,16 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="33">
+      <c r="A34" s="2">
         <v>2016</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C34" s="33">
-        <v>3</v>
-      </c>
-      <c r="D34" s="33">
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
         <v>19</v>
       </c>
       <c r="E34" s="6">
@@ -11644,16 +11638,16 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="33">
+      <c r="A35" s="2">
         <v>2016</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C35" s="33">
-        <v>3</v>
-      </c>
-      <c r="D35" s="33">
+      <c r="C35" s="2">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2">
         <v>19</v>
       </c>
       <c r="E35" s="6">
@@ -11670,16 +11664,16 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="33">
+      <c r="A36" s="2">
         <v>2016</v>
       </c>
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C36" s="33">
-        <v>3</v>
-      </c>
-      <c r="D36" s="33">
+      <c r="C36" s="2">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2">
         <v>19</v>
       </c>
       <c r="E36" s="6">
@@ -11693,16 +11687,16 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="33">
+      <c r="A37" s="2">
         <v>2016</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C37" s="33">
-        <v>3</v>
-      </c>
-      <c r="D37" s="33">
+      <c r="C37" s="2">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2">
         <v>19</v>
       </c>
       <c r="E37" s="6">
@@ -11716,16 +11710,16 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="33">
+      <c r="A38" s="2">
         <v>2016</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C38" s="33">
-        <v>3</v>
-      </c>
-      <c r="D38" s="33">
+      <c r="C38" s="2">
+        <v>3</v>
+      </c>
+      <c r="D38" s="2">
         <v>19</v>
       </c>
       <c r="E38" s="6">
@@ -11742,16 +11736,16 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="33">
+      <c r="A39" s="2">
         <v>2016</v>
       </c>
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C39" s="33">
-        <v>3</v>
-      </c>
-      <c r="D39" s="33">
+      <c r="C39" s="2">
+        <v>3</v>
+      </c>
+      <c r="D39" s="2">
         <v>19</v>
       </c>
       <c r="E39" s="6">
@@ -11771,16 +11765,16 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="33">
+      <c r="A40" s="2">
         <v>2016</v>
       </c>
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C40" s="33">
-        <v>3</v>
-      </c>
-      <c r="D40" s="33">
+      <c r="C40" s="2">
+        <v>3</v>
+      </c>
+      <c r="D40" s="2">
         <v>20</v>
       </c>
       <c r="E40" s="6">
@@ -11797,16 +11791,16 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="33">
+      <c r="A41" s="2">
         <v>2016</v>
       </c>
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C41" s="33">
-        <v>3</v>
-      </c>
-      <c r="D41" s="33">
+      <c r="C41" s="2">
+        <v>3</v>
+      </c>
+      <c r="D41" s="2">
         <v>20</v>
       </c>
       <c r="E41" s="6">
@@ -11820,16 +11814,16 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="33">
+      <c r="A42" s="2">
         <v>2016</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C42" s="33">
-        <v>3</v>
-      </c>
-      <c r="D42" s="33">
+      <c r="C42" s="2">
+        <v>3</v>
+      </c>
+      <c r="D42" s="2">
         <v>20</v>
       </c>
       <c r="E42" s="6">
@@ -11843,16 +11837,16 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="33">
+      <c r="A43" s="2">
         <v>2016</v>
       </c>
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C43" s="33">
-        <v>3</v>
-      </c>
-      <c r="D43" s="33">
+      <c r="C43" s="2">
+        <v>3</v>
+      </c>
+      <c r="D43" s="2">
         <v>20</v>
       </c>
       <c r="E43" s="6">
@@ -11869,16 +11863,16 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="33">
+      <c r="A44" s="2">
         <v>2016</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C44" s="33">
-        <v>3</v>
-      </c>
-      <c r="D44" s="33">
+      <c r="C44" s="2">
+        <v>3</v>
+      </c>
+      <c r="D44" s="2">
         <v>20</v>
       </c>
       <c r="E44" s="6">
@@ -11898,16 +11892,16 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="33">
+      <c r="A45" s="2">
         <v>2016</v>
       </c>
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C45" s="33">
-        <v>3</v>
-      </c>
-      <c r="D45" s="33">
+      <c r="C45" s="2">
+        <v>3</v>
+      </c>
+      <c r="D45" s="2">
         <v>20</v>
       </c>
       <c r="E45" s="6">
@@ -11927,16 +11921,16 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="33">
+      <c r="A46" s="2">
         <v>2016</v>
       </c>
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C46" s="33">
-        <v>3</v>
-      </c>
-      <c r="D46" s="33">
+      <c r="C46" s="2">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2">
         <v>20</v>
       </c>
       <c r="E46" s="6">
@@ -11950,16 +11944,16 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="33">
+      <c r="A47" s="2">
         <v>2016</v>
       </c>
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C47" s="33">
-        <v>3</v>
-      </c>
-      <c r="D47" s="33">
+      <c r="C47" s="2">
+        <v>3</v>
+      </c>
+      <c r="D47" s="2">
         <v>20</v>
       </c>
       <c r="E47" s="6">
@@ -11979,16 +11973,16 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="33">
+      <c r="A48" s="2">
         <v>2016</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C48" s="33">
-        <v>3</v>
-      </c>
-      <c r="D48" s="33">
+      <c r="C48" s="2">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2">
         <v>20</v>
       </c>
       <c r="E48" s="6">
@@ -12005,16 +11999,16 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="33">
+      <c r="A49" s="2">
         <v>2016</v>
       </c>
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C49" s="33">
-        <v>3</v>
-      </c>
-      <c r="D49" s="33">
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="2">
         <v>20</v>
       </c>
       <c r="E49" s="6">
@@ -12031,16 +12025,16 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="33">
+      <c r="A50" s="2">
         <v>2016</v>
       </c>
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C50" s="33">
-        <v>3</v>
-      </c>
-      <c r="D50" s="33">
+      <c r="C50" s="2">
+        <v>3</v>
+      </c>
+      <c r="D50" s="2">
         <v>21</v>
       </c>
       <c r="E50" s="6">
@@ -12057,16 +12051,16 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="33">
+      <c r="A51" s="2">
         <v>2016</v>
       </c>
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C51" s="33">
-        <v>3</v>
-      </c>
-      <c r="D51" s="33">
+      <c r="C51" s="2">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2">
         <v>21</v>
       </c>
       <c r="E51" s="6">
@@ -12086,16 +12080,16 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="33">
+      <c r="A52" s="2">
         <v>2016</v>
       </c>
-      <c r="B52" s="33" t="s">
+      <c r="B52" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C52" s="33">
-        <v>3</v>
-      </c>
-      <c r="D52" s="33">
+      <c r="C52" s="2">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2">
         <v>21</v>
       </c>
       <c r="E52" s="6">
@@ -12109,16 +12103,16 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="33">
+      <c r="A53" s="2">
         <v>2016</v>
       </c>
-      <c r="B53" s="33" t="s">
+      <c r="B53" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C53" s="33">
-        <v>3</v>
-      </c>
-      <c r="D53" s="33">
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2">
         <v>21</v>
       </c>
       <c r="E53" s="6">
@@ -12138,16 +12132,16 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="33">
+      <c r="A54" s="2">
         <v>2016</v>
       </c>
-      <c r="B54" s="33" t="s">
+      <c r="B54" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C54" s="33">
-        <v>3</v>
-      </c>
-      <c r="D54" s="33">
+      <c r="C54" s="2">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2">
         <v>21</v>
       </c>
       <c r="E54" s="6">
@@ -12167,16 +12161,16 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="33">
+      <c r="A55" s="2">
         <v>2016</v>
       </c>
-      <c r="B55" s="33" t="s">
+      <c r="B55" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C55" s="33">
-        <v>3</v>
-      </c>
-      <c r="D55" s="33">
+      <c r="C55" s="2">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2">
         <v>21</v>
       </c>
       <c r="E55" s="6">
@@ -12196,16 +12190,16 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="33">
+      <c r="A56" s="2">
         <v>2016</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C56" s="33">
-        <v>3</v>
-      </c>
-      <c r="D56" s="33">
+      <c r="C56" s="2">
+        <v>3</v>
+      </c>
+      <c r="D56" s="2">
         <v>21</v>
       </c>
       <c r="E56" s="6">
@@ -12225,16 +12219,16 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="33">
+      <c r="A57" s="2">
         <v>2016</v>
       </c>
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C57" s="33">
-        <v>3</v>
-      </c>
-      <c r="D57" s="33">
+      <c r="C57" s="2">
+        <v>3</v>
+      </c>
+      <c r="D57" s="2">
         <v>21</v>
       </c>
       <c r="E57" s="6">
@@ -12248,16 +12242,16 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="33">
+      <c r="A58" s="2">
         <v>2016</v>
       </c>
-      <c r="B58" s="33" t="s">
+      <c r="B58" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C58" s="33">
-        <v>3</v>
-      </c>
-      <c r="D58" s="33">
+      <c r="C58" s="2">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2">
         <v>21</v>
       </c>
       <c r="E58" s="6">
@@ -12271,16 +12265,16 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="33">
+      <c r="A59" s="2">
         <v>2016</v>
       </c>
-      <c r="B59" s="33" t="s">
+      <c r="B59" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C59" s="33">
-        <v>3</v>
-      </c>
-      <c r="D59" s="33">
+      <c r="C59" s="2">
+        <v>3</v>
+      </c>
+      <c r="D59" s="2">
         <v>21</v>
       </c>
       <c r="E59" s="6">
@@ -12294,16 +12288,16 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="33">
+      <c r="A60" s="2">
         <v>2016</v>
       </c>
-      <c r="B60" s="33" t="s">
+      <c r="B60" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C60" s="33">
-        <v>3</v>
-      </c>
-      <c r="D60" s="33">
+      <c r="C60" s="2">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2">
         <v>21</v>
       </c>
       <c r="E60" s="6">
@@ -12323,16 +12317,16 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="33">
+      <c r="A61" s="2">
         <v>2016</v>
       </c>
-      <c r="B61" s="33" t="s">
+      <c r="B61" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C61" s="33">
-        <v>3</v>
-      </c>
-      <c r="D61" s="33">
+      <c r="C61" s="2">
+        <v>3</v>
+      </c>
+      <c r="D61" s="2">
         <v>22</v>
       </c>
       <c r="E61" s="6">
@@ -12349,16 +12343,16 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="33">
+      <c r="A62" s="2">
         <v>2016</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="B62" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C62" s="33">
-        <v>3</v>
-      </c>
-      <c r="D62" s="33">
+      <c r="C62" s="2">
+        <v>3</v>
+      </c>
+      <c r="D62" s="2">
         <v>22</v>
       </c>
       <c r="E62" s="6">
@@ -12378,16 +12372,16 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="33">
+      <c r="A63" s="2">
         <v>2016</v>
       </c>
-      <c r="B63" s="33" t="s">
+      <c r="B63" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C63" s="33">
-        <v>3</v>
-      </c>
-      <c r="D63" s="33">
+      <c r="C63" s="2">
+        <v>3</v>
+      </c>
+      <c r="D63" s="2">
         <v>22</v>
       </c>
       <c r="E63" s="6">
@@ -12407,16 +12401,16 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="33">
+      <c r="A64" s="2">
         <v>2016</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="B64" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C64" s="33">
-        <v>3</v>
-      </c>
-      <c r="D64" s="33">
+      <c r="C64" s="2">
+        <v>3</v>
+      </c>
+      <c r="D64" s="2">
         <v>22</v>
       </c>
       <c r="E64" s="6">
@@ -12436,16 +12430,16 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="33">
+      <c r="A65" s="2">
         <v>2016</v>
       </c>
-      <c r="B65" s="33" t="s">
+      <c r="B65" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C65" s="33">
-        <v>3</v>
-      </c>
-      <c r="D65" s="33">
+      <c r="C65" s="2">
+        <v>3</v>
+      </c>
+      <c r="D65" s="2">
         <v>22</v>
       </c>
       <c r="E65" s="6">
@@ -12465,16 +12459,16 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="33">
+      <c r="A66" s="2">
         <v>2016</v>
       </c>
-      <c r="B66" s="33" t="s">
+      <c r="B66" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C66" s="33">
-        <v>3</v>
-      </c>
-      <c r="D66" s="33">
+      <c r="C66" s="2">
+        <v>3</v>
+      </c>
+      <c r="D66" s="2">
         <v>22</v>
       </c>
       <c r="E66" s="6">
@@ -12494,16 +12488,16 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="33">
+      <c r="A67" s="2">
         <v>2016</v>
       </c>
-      <c r="B67" s="33" t="s">
+      <c r="B67" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C67" s="33">
-        <v>3</v>
-      </c>
-      <c r="D67" s="33">
+      <c r="C67" s="2">
+        <v>3</v>
+      </c>
+      <c r="D67" s="2">
         <v>22</v>
       </c>
       <c r="E67" s="6">
@@ -12517,16 +12511,16 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="33">
+      <c r="A68" s="2">
         <v>2016</v>
       </c>
-      <c r="B68" s="33" t="s">
+      <c r="B68" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C68" s="33">
-        <v>3</v>
-      </c>
-      <c r="D68" s="33">
+      <c r="C68" s="2">
+        <v>3</v>
+      </c>
+      <c r="D68" s="2">
         <v>22</v>
       </c>
       <c r="E68" s="6">
@@ -12540,16 +12534,16 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="33">
+      <c r="A69" s="2">
         <v>2016</v>
       </c>
-      <c r="B69" s="33" t="s">
+      <c r="B69" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C69" s="33">
-        <v>3</v>
-      </c>
-      <c r="D69" s="33">
+      <c r="C69" s="2">
+        <v>3</v>
+      </c>
+      <c r="D69" s="2">
         <v>22</v>
       </c>
       <c r="E69" s="6">
@@ -12569,16 +12563,16 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="33">
+      <c r="A70" s="2">
         <v>2016</v>
       </c>
-      <c r="B70" s="33" t="s">
+      <c r="B70" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C70" s="33">
-        <v>3</v>
-      </c>
-      <c r="D70" s="33">
+      <c r="C70" s="2">
+        <v>3</v>
+      </c>
+      <c r="D70" s="2">
         <v>23</v>
       </c>
       <c r="E70" s="6">
@@ -12595,16 +12589,16 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="33">
+      <c r="A71" s="2">
         <v>2016</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C71" s="33">
-        <v>3</v>
-      </c>
-      <c r="D71" s="33">
+      <c r="C71" s="2">
+        <v>3</v>
+      </c>
+      <c r="D71" s="2">
         <v>23</v>
       </c>
       <c r="E71" s="6">
@@ -12624,16 +12618,16 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="33">
+      <c r="A72" s="2">
         <v>2016</v>
       </c>
-      <c r="B72" s="33" t="s">
+      <c r="B72" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C72" s="33">
-        <v>3</v>
-      </c>
-      <c r="D72" s="33">
+      <c r="C72" s="2">
+        <v>3</v>
+      </c>
+      <c r="D72" s="2">
         <v>23</v>
       </c>
       <c r="E72" s="6">
@@ -12650,16 +12644,16 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="33">
+      <c r="A73" s="2">
         <v>2016</v>
       </c>
-      <c r="B73" s="33" t="s">
+      <c r="B73" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C73" s="33">
-        <v>3</v>
-      </c>
-      <c r="D73" s="33">
+      <c r="C73" s="2">
+        <v>3</v>
+      </c>
+      <c r="D73" s="2">
         <v>23</v>
       </c>
       <c r="E73" s="6">
@@ -12679,16 +12673,16 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="33">
+      <c r="A74" s="2">
         <v>2016</v>
       </c>
-      <c r="B74" s="33" t="s">
+      <c r="B74" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C74" s="33">
-        <v>3</v>
-      </c>
-      <c r="D74" s="33">
+      <c r="C74" s="2">
+        <v>3</v>
+      </c>
+      <c r="D74" s="2">
         <v>23</v>
       </c>
       <c r="E74" s="6">
@@ -12702,16 +12696,16 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="33">
+      <c r="A75" s="2">
         <v>2016</v>
       </c>
-      <c r="B75" s="33" t="s">
+      <c r="B75" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C75" s="33">
-        <v>3</v>
-      </c>
-      <c r="D75" s="33">
+      <c r="C75" s="2">
+        <v>3</v>
+      </c>
+      <c r="D75" s="2">
         <v>23</v>
       </c>
       <c r="E75" s="6">
@@ -12731,16 +12725,16 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="33">
+      <c r="A76" s="2">
         <v>2016</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C76" s="33">
-        <v>3</v>
-      </c>
-      <c r="D76" s="33">
+      <c r="C76" s="2">
+        <v>3</v>
+      </c>
+      <c r="D76" s="2">
         <v>23</v>
       </c>
       <c r="E76" s="6">
@@ -12757,16 +12751,16 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="33">
+      <c r="A77" s="2">
         <v>2016</v>
       </c>
-      <c r="B77" s="33" t="s">
+      <c r="B77" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C77" s="33">
-        <v>3</v>
-      </c>
-      <c r="D77" s="33">
+      <c r="C77" s="2">
+        <v>3</v>
+      </c>
+      <c r="D77" s="2">
         <v>23</v>
       </c>
       <c r="E77" s="6">
@@ -12780,16 +12774,16 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="33">
+      <c r="A78" s="2">
         <v>2016</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C78" s="33">
-        <v>3</v>
-      </c>
-      <c r="D78" s="33">
+      <c r="C78" s="2">
+        <v>3</v>
+      </c>
+      <c r="D78" s="2">
         <v>23</v>
       </c>
       <c r="E78" s="6">
@@ -12806,16 +12800,16 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="33">
+      <c r="A79" s="2">
         <v>2016</v>
       </c>
-      <c r="B79" s="33" t="s">
+      <c r="B79" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C79" s="33">
-        <v>3</v>
-      </c>
-      <c r="D79" s="33">
+      <c r="C79" s="2">
+        <v>3</v>
+      </c>
+      <c r="D79" s="2">
         <v>23</v>
       </c>
       <c r="E79" s="6">
@@ -12835,16 +12829,16 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="33">
+      <c r="A80" s="2">
         <v>2016</v>
       </c>
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C80" s="33">
-        <v>3</v>
-      </c>
-      <c r="D80" s="33">
+      <c r="C80" s="2">
+        <v>3</v>
+      </c>
+      <c r="D80" s="2">
         <v>24</v>
       </c>
       <c r="E80" s="6">
@@ -12861,16 +12855,16 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="33">
+      <c r="A81" s="2">
         <v>2016</v>
       </c>
-      <c r="B81" s="33" t="s">
+      <c r="B81" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C81" s="33">
-        <v>3</v>
-      </c>
-      <c r="D81" s="33">
+      <c r="C81" s="2">
+        <v>3</v>
+      </c>
+      <c r="D81" s="2">
         <v>24</v>
       </c>
       <c r="E81" s="6">
@@ -12884,16 +12878,16 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" s="33">
+      <c r="A82" s="2">
         <v>2016</v>
       </c>
-      <c r="B82" s="33" t="s">
+      <c r="B82" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C82" s="33">
-        <v>3</v>
-      </c>
-      <c r="D82" s="33">
+      <c r="C82" s="2">
+        <v>3</v>
+      </c>
+      <c r="D82" s="2">
         <v>24</v>
       </c>
       <c r="E82" s="6">
@@ -12910,16 +12904,16 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="33">
+      <c r="A83" s="2">
         <v>2016</v>
       </c>
-      <c r="B83" s="33" t="s">
+      <c r="B83" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C83" s="33">
-        <v>3</v>
-      </c>
-      <c r="D83" s="33">
+      <c r="C83" s="2">
+        <v>3</v>
+      </c>
+      <c r="D83" s="2">
         <v>24</v>
       </c>
       <c r="E83" s="6">
@@ -12933,16 +12927,16 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="33">
+      <c r="A84" s="2">
         <v>2016</v>
       </c>
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C84" s="33">
-        <v>3</v>
-      </c>
-      <c r="D84" s="33">
+      <c r="C84" s="2">
+        <v>3</v>
+      </c>
+      <c r="D84" s="2">
         <v>24</v>
       </c>
       <c r="E84" s="6">
@@ -12956,16 +12950,16 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" s="33">
+      <c r="A85" s="2">
         <v>2016</v>
       </c>
-      <c r="B85" s="33" t="s">
+      <c r="B85" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C85" s="33">
-        <v>3</v>
-      </c>
-      <c r="D85" s="33">
+      <c r="C85" s="2">
+        <v>3</v>
+      </c>
+      <c r="D85" s="2">
         <v>24</v>
       </c>
       <c r="E85" s="6">
@@ -12985,16 +12979,16 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" s="33">
+      <c r="A86" s="2">
         <v>2016</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C86" s="33">
-        <v>3</v>
-      </c>
-      <c r="D86" s="33">
+      <c r="C86" s="2">
+        <v>3</v>
+      </c>
+      <c r="D86" s="2">
         <v>24</v>
       </c>
       <c r="E86" s="6">
@@ -13014,16 +13008,16 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" s="33">
+      <c r="A87" s="2">
         <v>2016</v>
       </c>
-      <c r="B87" s="33" t="s">
+      <c r="B87" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C87" s="33">
-        <v>3</v>
-      </c>
-      <c r="D87" s="33">
+      <c r="C87" s="2">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2">
         <v>24</v>
       </c>
       <c r="E87" s="6">
@@ -13043,16 +13037,16 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" s="33">
+      <c r="A88" s="2">
         <v>2016</v>
       </c>
-      <c r="B88" s="33" t="s">
+      <c r="B88" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C88" s="33">
-        <v>3</v>
-      </c>
-      <c r="D88" s="33">
+      <c r="C88" s="2">
+        <v>3</v>
+      </c>
+      <c r="D88" s="2">
         <v>24</v>
       </c>
       <c r="E88" s="6">
@@ -13066,16 +13060,16 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" s="33">
+      <c r="A89" s="2">
         <v>2016</v>
       </c>
-      <c r="B89" s="33" t="s">
+      <c r="B89" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C89" s="33">
-        <v>3</v>
-      </c>
-      <c r="D89" s="33">
+      <c r="C89" s="2">
+        <v>3</v>
+      </c>
+      <c r="D89" s="2">
         <v>24</v>
       </c>
       <c r="E89" s="6">
@@ -13095,16 +13089,16 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" s="33">
+      <c r="A90" s="2">
         <v>2016</v>
       </c>
-      <c r="B90" s="33" t="s">
+      <c r="B90" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C90" s="33">
-        <v>3</v>
-      </c>
-      <c r="D90" s="33">
+      <c r="C90" s="2">
+        <v>3</v>
+      </c>
+      <c r="D90" s="2">
         <v>24</v>
       </c>
       <c r="E90" s="6">
@@ -13118,16 +13112,16 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="33">
+      <c r="A91" s="2">
         <v>2016</v>
       </c>
-      <c r="B91" s="33" t="s">
+      <c r="B91" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C91" s="33">
-        <v>3</v>
-      </c>
-      <c r="D91" s="33">
+      <c r="C91" s="2">
+        <v>3</v>
+      </c>
+      <c r="D91" s="2">
         <v>24</v>
       </c>
       <c r="E91" s="6">
@@ -13141,16 +13135,16 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" s="33">
+      <c r="A92" s="2">
         <v>2016</v>
       </c>
-      <c r="B92" s="33" t="s">
+      <c r="B92" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C92" s="33">
-        <v>3</v>
-      </c>
-      <c r="D92" s="33">
+      <c r="C92" s="2">
+        <v>3</v>
+      </c>
+      <c r="D92" s="2">
         <v>24</v>
       </c>
       <c r="E92" s="6">
@@ -13164,16 +13158,16 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" s="33">
+      <c r="A93" s="2">
         <v>2016</v>
       </c>
-      <c r="B93" s="33" t="s">
+      <c r="B93" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C93" s="33">
-        <v>3</v>
-      </c>
-      <c r="D93" s="33">
+      <c r="C93" s="2">
+        <v>3</v>
+      </c>
+      <c r="D93" s="2">
         <v>24</v>
       </c>
       <c r="E93" s="6">
@@ -13187,16 +13181,16 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="33">
+      <c r="A94" s="2">
         <v>2016</v>
       </c>
-      <c r="B94" s="33" t="s">
+      <c r="B94" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C94" s="33">
-        <v>3</v>
-      </c>
-      <c r="D94" s="33">
+      <c r="C94" s="2">
+        <v>3</v>
+      </c>
+      <c r="D94" s="2">
         <v>24</v>
       </c>
       <c r="E94" s="6">
@@ -13210,16 +13204,16 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="33">
+      <c r="A95" s="2">
         <v>2016</v>
       </c>
-      <c r="B95" s="33" t="s">
+      <c r="B95" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C95" s="33">
-        <v>3</v>
-      </c>
-      <c r="D95" s="33">
+      <c r="C95" s="2">
+        <v>3</v>
+      </c>
+      <c r="D95" s="2">
         <v>24</v>
       </c>
       <c r="E95" s="6">
@@ -13239,16 +13233,16 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="33">
+      <c r="A96" s="2">
         <v>2016</v>
       </c>
-      <c r="B96" s="33" t="s">
+      <c r="B96" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C96" s="33">
-        <v>3</v>
-      </c>
-      <c r="D96" s="33">
+      <c r="C96" s="2">
+        <v>3</v>
+      </c>
+      <c r="D96" s="2">
         <v>24</v>
       </c>
       <c r="E96" s="6">
@@ -13262,16 +13256,16 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="33">
+      <c r="A97" s="2">
         <v>2016</v>
       </c>
-      <c r="B97" s="33" t="s">
+      <c r="B97" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C97" s="33">
-        <v>3</v>
-      </c>
-      <c r="D97" s="33">
+      <c r="C97" s="2">
+        <v>3</v>
+      </c>
+      <c r="D97" s="2">
         <v>24</v>
       </c>
       <c r="E97" s="6">
@@ -13285,16 +13279,16 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="33">
+      <c r="A98" s="2">
         <v>2016</v>
       </c>
-      <c r="B98" s="33" t="s">
+      <c r="B98" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C98" s="33">
-        <v>3</v>
-      </c>
-      <c r="D98" s="33">
+      <c r="C98" s="2">
+        <v>3</v>
+      </c>
+      <c r="D98" s="2">
         <v>24</v>
       </c>
       <c r="E98" s="6">
@@ -13308,16 +13302,16 @@
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="33">
+      <c r="A99" s="2">
         <v>2016</v>
       </c>
-      <c r="B99" s="33" t="s">
+      <c r="B99" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C99" s="33">
-        <v>3</v>
-      </c>
-      <c r="D99" s="33">
+      <c r="C99" s="2">
+        <v>3</v>
+      </c>
+      <c r="D99" s="2">
         <v>24</v>
       </c>
       <c r="E99" s="6">
@@ -13337,16 +13331,16 @@
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="33">
+      <c r="A100" s="2">
         <v>2016</v>
       </c>
-      <c r="B100" s="33" t="s">
+      <c r="B100" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C100" s="33">
-        <v>3</v>
-      </c>
-      <c r="D100" s="33">
+      <c r="C100" s="2">
+        <v>3</v>
+      </c>
+      <c r="D100" s="2">
         <v>25</v>
       </c>
       <c r="E100" s="6">
@@ -13360,16 +13354,16 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="33">
+      <c r="A101" s="2">
         <v>2016</v>
       </c>
-      <c r="B101" s="33" t="s">
+      <c r="B101" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C101" s="33">
-        <v>3</v>
-      </c>
-      <c r="D101" s="33">
+      <c r="C101" s="2">
+        <v>3</v>
+      </c>
+      <c r="D101" s="2">
         <v>25</v>
       </c>
       <c r="E101" s="6">
@@ -13386,16 +13380,16 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="33">
+      <c r="A102" s="2">
         <v>2016</v>
       </c>
-      <c r="B102" s="33" t="s">
+      <c r="B102" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C102" s="33">
-        <v>3</v>
-      </c>
-      <c r="D102" s="33">
+      <c r="C102" s="2">
+        <v>3</v>
+      </c>
+      <c r="D102" s="2">
         <v>25</v>
       </c>
       <c r="E102" s="6">
@@ -13409,16 +13403,16 @@
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="33">
+      <c r="A103" s="2">
         <v>2016</v>
       </c>
-      <c r="B103" s="33" t="s">
+      <c r="B103" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C103" s="33">
-        <v>3</v>
-      </c>
-      <c r="D103" s="33">
+      <c r="C103" s="2">
+        <v>3</v>
+      </c>
+      <c r="D103" s="2">
         <v>25</v>
       </c>
       <c r="E103" s="6">
@@ -13432,16 +13426,16 @@
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="33">
+      <c r="A104" s="2">
         <v>2016</v>
       </c>
-      <c r="B104" s="33" t="s">
+      <c r="B104" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C104" s="33">
-        <v>3</v>
-      </c>
-      <c r="D104" s="33">
+      <c r="C104" s="2">
+        <v>3</v>
+      </c>
+      <c r="D104" s="2">
         <v>25</v>
       </c>
       <c r="E104" s="6">
@@ -13458,16 +13452,16 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="33">
+      <c r="A105" s="2">
         <v>2016</v>
       </c>
-      <c r="B105" s="33" t="s">
+      <c r="B105" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C105" s="33">
-        <v>3</v>
-      </c>
-      <c r="D105" s="33">
+      <c r="C105" s="2">
+        <v>3</v>
+      </c>
+      <c r="D105" s="2">
         <v>25</v>
       </c>
       <c r="E105" s="6">
@@ -13481,16 +13475,16 @@
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="33">
+      <c r="A106" s="2">
         <v>2016</v>
       </c>
-      <c r="B106" s="33" t="s">
+      <c r="B106" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C106" s="33">
-        <v>3</v>
-      </c>
-      <c r="D106" s="33">
+      <c r="C106" s="2">
+        <v>3</v>
+      </c>
+      <c r="D106" s="2">
         <v>25</v>
       </c>
       <c r="E106" s="6">
@@ -13504,16 +13498,16 @@
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="33">
+      <c r="A107" s="2">
         <v>2016</v>
       </c>
-      <c r="B107" s="33" t="s">
+      <c r="B107" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C107" s="33">
-        <v>3</v>
-      </c>
-      <c r="D107" s="33">
+      <c r="C107" s="2">
+        <v>3</v>
+      </c>
+      <c r="D107" s="2">
         <v>25</v>
       </c>
       <c r="E107" s="6">
@@ -13527,16 +13521,16 @@
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="33">
+      <c r="A108" s="2">
         <v>2016</v>
       </c>
-      <c r="B108" s="33" t="s">
+      <c r="B108" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C108" s="33">
-        <v>3</v>
-      </c>
-      <c r="D108" s="33">
+      <c r="C108" s="2">
+        <v>3</v>
+      </c>
+      <c r="D108" s="2">
         <v>25</v>
       </c>
       <c r="E108" s="6">
@@ -13553,16 +13547,16 @@
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="33">
+      <c r="A109" s="2">
         <v>2016</v>
       </c>
-      <c r="B109" s="33" t="s">
+      <c r="B109" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C109" s="33">
-        <v>3</v>
-      </c>
-      <c r="D109" s="33">
+      <c r="C109" s="2">
+        <v>3</v>
+      </c>
+      <c r="D109" s="2">
         <v>25</v>
       </c>
       <c r="E109" s="6">
@@ -13579,16 +13573,16 @@
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="33">
+      <c r="A110" s="2">
         <v>2016</v>
       </c>
-      <c r="B110" s="33" t="s">
+      <c r="B110" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C110" s="33">
-        <v>3</v>
-      </c>
-      <c r="D110" s="33">
+      <c r="C110" s="2">
+        <v>3</v>
+      </c>
+      <c r="D110" s="2">
         <v>25</v>
       </c>
       <c r="E110" s="6">
@@ -13602,16 +13596,16 @@
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="33">
+      <c r="A111" s="2">
         <v>2016</v>
       </c>
-      <c r="B111" s="33" t="s">
+      <c r="B111" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C111" s="33">
-        <v>3</v>
-      </c>
-      <c r="D111" s="33">
+      <c r="C111" s="2">
+        <v>3</v>
+      </c>
+      <c r="D111" s="2">
         <v>25</v>
       </c>
       <c r="E111" s="6">
@@ -13625,16 +13619,16 @@
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="33">
+      <c r="A112" s="2">
         <v>2016</v>
       </c>
-      <c r="B112" s="33" t="s">
+      <c r="B112" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C112" s="33">
-        <v>3</v>
-      </c>
-      <c r="D112" s="33">
+      <c r="C112" s="2">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2">
         <v>25</v>
       </c>
       <c r="E112" s="6">
@@ -13648,16 +13642,16 @@
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="33">
+      <c r="A113" s="2">
         <v>2016</v>
       </c>
-      <c r="B113" s="33" t="s">
+      <c r="B113" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C113" s="33">
-        <v>3</v>
-      </c>
-      <c r="D113" s="33">
+      <c r="C113" s="2">
+        <v>3</v>
+      </c>
+      <c r="D113" s="2">
         <v>25</v>
       </c>
       <c r="E113" s="6">
@@ -13674,16 +13668,16 @@
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" s="33">
+      <c r="A114" s="2">
         <v>2016</v>
       </c>
-      <c r="B114" s="33" t="s">
+      <c r="B114" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C114" s="33">
-        <v>3</v>
-      </c>
-      <c r="D114" s="33">
+      <c r="C114" s="2">
+        <v>3</v>
+      </c>
+      <c r="D114" s="2">
         <v>25</v>
       </c>
       <c r="E114" s="6">
@@ -13700,16 +13694,16 @@
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="33">
+      <c r="A115" s="2">
         <v>2016</v>
       </c>
-      <c r="B115" s="33" t="s">
+      <c r="B115" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C115" s="33">
-        <v>3</v>
-      </c>
-      <c r="D115" s="33">
+      <c r="C115" s="2">
+        <v>3</v>
+      </c>
+      <c r="D115" s="2">
         <v>25</v>
       </c>
       <c r="E115" s="6">
@@ -13726,16 +13720,16 @@
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="33">
+      <c r="A116" s="2">
         <v>2016</v>
       </c>
-      <c r="B116" s="33" t="s">
+      <c r="B116" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C116" s="33">
-        <v>3</v>
-      </c>
-      <c r="D116" s="33">
+      <c r="C116" s="2">
+        <v>3</v>
+      </c>
+      <c r="D116" s="2">
         <v>25</v>
       </c>
       <c r="E116" s="6">
@@ -13752,16 +13746,16 @@
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="33">
+      <c r="A117" s="2">
         <v>2016</v>
       </c>
-      <c r="B117" s="33" t="s">
+      <c r="B117" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C117" s="33">
-        <v>3</v>
-      </c>
-      <c r="D117" s="33">
+      <c r="C117" s="2">
+        <v>3</v>
+      </c>
+      <c r="D117" s="2">
         <v>25</v>
       </c>
       <c r="E117" s="6">
@@ -13778,16 +13772,16 @@
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="33">
+      <c r="A118" s="2">
         <v>2016</v>
       </c>
-      <c r="B118" s="33" t="s">
+      <c r="B118" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C118" s="33">
-        <v>3</v>
-      </c>
-      <c r="D118" s="33">
+      <c r="C118" s="2">
+        <v>3</v>
+      </c>
+      <c r="D118" s="2">
         <v>25</v>
       </c>
       <c r="E118" s="6">
@@ -13807,16 +13801,16 @@
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="33">
+      <c r="A119" s="2">
         <v>2016</v>
       </c>
-      <c r="B119" s="33" t="s">
+      <c r="B119" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C119" s="33">
-        <v>3</v>
-      </c>
-      <c r="D119" s="33">
+      <c r="C119" s="2">
+        <v>3</v>
+      </c>
+      <c r="D119" s="2">
         <v>25</v>
       </c>
       <c r="E119" s="6">
@@ -13836,16 +13830,16 @@
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="33">
+      <c r="A120" s="2">
         <v>2016</v>
       </c>
-      <c r="B120" s="33" t="s">
+      <c r="B120" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C120" s="33">
-        <v>3</v>
-      </c>
-      <c r="D120" s="33">
+      <c r="C120" s="2">
+        <v>3</v>
+      </c>
+      <c r="D120" s="2">
         <v>25</v>
       </c>
       <c r="E120" s="6">
@@ -13859,16 +13853,16 @@
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="33">
+      <c r="A121" s="2">
         <v>2016</v>
       </c>
-      <c r="B121" s="33" t="s">
+      <c r="B121" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C121" s="33">
-        <v>3</v>
-      </c>
-      <c r="D121" s="33">
+      <c r="C121" s="2">
+        <v>3</v>
+      </c>
+      <c r="D121" s="2">
         <v>25</v>
       </c>
       <c r="E121" s="6">
@@ -13882,16 +13876,16 @@
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="33">
+      <c r="A122" s="2">
         <v>2016</v>
       </c>
-      <c r="B122" s="33" t="s">
+      <c r="B122" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C122" s="33">
-        <v>3</v>
-      </c>
-      <c r="D122" s="33">
+      <c r="C122" s="2">
+        <v>3</v>
+      </c>
+      <c r="D122" s="2">
         <v>25</v>
       </c>
       <c r="E122" s="6">
@@ -13911,16 +13905,16 @@
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="33">
+      <c r="A123" s="2">
         <v>2016</v>
       </c>
-      <c r="B123" s="33" t="s">
+      <c r="B123" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C123" s="33">
-        <v>3</v>
-      </c>
-      <c r="D123" s="33">
+      <c r="C123" s="2">
+        <v>3</v>
+      </c>
+      <c r="D123" s="2">
         <v>26</v>
       </c>
       <c r="E123" s="6">
@@ -13937,16 +13931,16 @@
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="33">
+      <c r="A124" s="2">
         <v>2016</v>
       </c>
-      <c r="B124" s="33" t="s">
+      <c r="B124" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C124" s="33">
-        <v>3</v>
-      </c>
-      <c r="D124" s="33">
+      <c r="C124" s="2">
+        <v>3</v>
+      </c>
+      <c r="D124" s="2">
         <v>26</v>
       </c>
       <c r="E124" s="6">
@@ -13966,16 +13960,16 @@
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="33">
+      <c r="A125" s="2">
         <v>2016</v>
       </c>
-      <c r="B125" s="33" t="s">
+      <c r="B125" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C125" s="33">
-        <v>3</v>
-      </c>
-      <c r="D125" s="33">
+      <c r="C125" s="2">
+        <v>3</v>
+      </c>
+      <c r="D125" s="2">
         <v>26</v>
       </c>
       <c r="E125" s="6">
@@ -13989,16 +13983,16 @@
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="33">
+      <c r="A126" s="2">
         <v>2016</v>
       </c>
-      <c r="B126" s="33" t="s">
+      <c r="B126" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C126" s="33">
-        <v>3</v>
-      </c>
-      <c r="D126" s="33">
+      <c r="C126" s="2">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2">
         <v>26</v>
       </c>
       <c r="E126" s="6">
@@ -14015,16 +14009,16 @@
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="33">
+      <c r="A127" s="2">
         <v>2016</v>
       </c>
-      <c r="B127" s="33" t="s">
+      <c r="B127" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C127" s="33">
-        <v>3</v>
-      </c>
-      <c r="D127" s="33">
+      <c r="C127" s="2">
+        <v>3</v>
+      </c>
+      <c r="D127" s="2">
         <v>26</v>
       </c>
       <c r="E127" s="6">
@@ -14041,16 +14035,16 @@
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="33">
+      <c r="A128" s="2">
         <v>2016</v>
       </c>
-      <c r="B128" s="33" t="s">
+      <c r="B128" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C128" s="33">
-        <v>3</v>
-      </c>
-      <c r="D128" s="33">
+      <c r="C128" s="2">
+        <v>3</v>
+      </c>
+      <c r="D128" s="2">
         <v>26</v>
       </c>
       <c r="E128" s="6">
@@ -14070,16 +14064,16 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="33">
+      <c r="A129" s="2">
         <v>2016</v>
       </c>
-      <c r="B129" s="33" t="s">
+      <c r="B129" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C129" s="33">
-        <v>3</v>
-      </c>
-      <c r="D129" s="33">
+      <c r="C129" s="2">
+        <v>3</v>
+      </c>
+      <c r="D129" s="2">
         <v>26</v>
       </c>
       <c r="E129" s="6">

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEF620F-4AAE-4D31-BE33-7442120B2784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4A1490-EB94-4555-B5B7-8A2C3910B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" activeTab="6" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" firstSheet="6" activeTab="18" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -25,6 +25,13 @@
     <sheet name="2018" sheetId="10" r:id="rId10"/>
     <sheet name="2017" sheetId="11" r:id="rId11"/>
     <sheet name="2016" sheetId="15" r:id="rId12"/>
+    <sheet name="2015" sheetId="16" r:id="rId13"/>
+    <sheet name="2014" sheetId="17" r:id="rId14"/>
+    <sheet name="2013" sheetId="18" r:id="rId15"/>
+    <sheet name="2012" sheetId="19" r:id="rId16"/>
+    <sheet name="2011" sheetId="20" r:id="rId17"/>
+    <sheet name="2010" sheetId="21" r:id="rId18"/>
+    <sheet name="2009" sheetId="22" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2016'!$A$1:$I$121</definedName>
@@ -56,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="1127">
   <si>
     <t>年份</t>
   </si>
@@ -3478,17 +3485,9 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2024 3/26 14:35</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>癸卯</t>
   </si>
   <si>
-    <t>2023 2/12 01:25</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>壬寅</t>
   </si>
   <si>
@@ -3496,10 +3495,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2022/5/37 15:05</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>己亥</t>
   </si>
   <si>
@@ -3526,10 +3521,6 @@
   </si>
   <si>
     <t>11天10夜</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2/16/3/21 05:45</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -4080,13 +4071,107 @@
     <t>六房媽祖紅壇(雲林縣土庫鎮仁美街2巷60號旁)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>辛巳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3月12日第4天下午03:23，潦過濁水溪</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>壬午</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>癸未</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>乙未</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天6夜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲午</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>癸巳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>壬辰</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>庚寅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>辛卯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>己丑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>6天5夜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>戊子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁亥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白沙屯媽祖與大甲媽祖龍井與沙鹿連二次相會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>60年首度駐駕大甲鎮瀾宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>丙戌</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第六天，田尾路段相遇大甲媽</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>乙酉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲申</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙鹿路段相遇大甲媽，首度相會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>60年第二次駐駕大甲鎮瀾宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
+    <numFmt numFmtId="180" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="181" formatCode="yyyy/mm/dd\ hh:mm"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -4736,7 +4821,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4812,29 +4897,11 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -4848,14 +4915,35 @@
     <xf numFmtId="20" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -5232,410 +5320,928 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3F28DB-C154-4233-B038-4B4939AF5845}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="7" customWidth="1"/>
-    <col min="4" max="5" width="5.77734375" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="30"/>
-    <col min="11" max="11" width="235.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="25"/>
+    <col min="11" max="11" width="79.109375" style="40" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>941</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>942</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>944</v>
       </c>
-      <c r="D1" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="D1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>947</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="36" t="s">
         <v>948</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="35" t="s">
         <v>949</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="35" t="s">
         <v>950</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="37" t="s">
         <v>951</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="39" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+    <row r="2" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10">
         <v>2026</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>943</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="35">
         <v>46124.996527777781</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="36">
         <v>46128</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="35">
         <v>46129.006944444445</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="35">
         <v>46132.673611111109</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+      <c r="J2" s="37"/>
+      <c r="K2" s="39"/>
+    </row>
+    <row r="3" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>2025</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="38" t="s">
         <v>952</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>953</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="10" t="s">
         <v>955</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="35">
         <v>45778.975694444445</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="36">
         <v>45780</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="35">
         <v>45781.027777777781</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="35">
         <v>45788.65625</v>
       </c>
-      <c r="J3" s="30">
+      <c r="J3" s="37">
         <v>329118</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="K3" s="39"/>
+    </row>
+    <row r="4" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>2024</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="35">
         <v>45369.024305555555</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="36">
         <v>45374</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="35">
         <v>45375.006944444445</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="35">
+        <v>45377.607638888891</v>
+      </c>
+      <c r="J4" s="37">
+        <v>179971</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>959</v>
       </c>
-      <c r="J4" s="30">
-        <v>179971</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="C5" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="F5" s="35">
+        <v>44969.059027777781</v>
+      </c>
+      <c r="G5" s="36">
+        <v>44974</v>
+      </c>
+      <c r="H5" s="35">
+        <v>44974.986111111109</v>
+      </c>
+      <c r="I5" s="35">
+        <v>44977.666666666664</v>
+      </c>
+      <c r="J5" s="37">
+        <v>113621</v>
+      </c>
+      <c r="K5" s="39"/>
+    </row>
+    <row r="6" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="38" t="s">
         <v>960</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="F6" s="35">
+        <v>44701.09375</v>
+      </c>
+      <c r="G6" s="36">
+        <v>44703</v>
+      </c>
+      <c r="H6" s="35">
+        <v>44704.010416666664</v>
+      </c>
+      <c r="I6" s="35">
+        <v>44708.628472222219</v>
+      </c>
+      <c r="J6" s="37">
+        <v>90928</v>
+      </c>
+      <c r="K6" s="39"/>
+    </row>
+    <row r="7" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="F7" s="35">
+        <v>44297.986111111109</v>
+      </c>
+      <c r="G7" s="36">
+        <v>44302</v>
+      </c>
+      <c r="H7" s="35">
+        <v>44302.958333333336</v>
+      </c>
+      <c r="I7" s="35">
+        <v>44305.614583333336</v>
+      </c>
+      <c r="J7" s="37">
+        <v>78672</v>
+      </c>
+      <c r="K7" s="39"/>
+    </row>
+    <row r="8" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D8" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="F8" s="35">
+        <v>44017.09375</v>
+      </c>
+      <c r="G8" s="36">
+        <v>44020</v>
+      </c>
+      <c r="H8" s="35">
+        <v>44021.21875</v>
+      </c>
+      <c r="I8" s="35">
+        <v>44025.638888888891</v>
+      </c>
+      <c r="J8" s="37">
+        <v>54599</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>2019</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>962</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="F9" s="35">
+        <v>43563.055555555555</v>
+      </c>
+      <c r="G9" s="36">
+        <v>43566</v>
+      </c>
+      <c r="H9" s="35">
+        <v>43567.208333333336</v>
+      </c>
+      <c r="I9" s="35">
+        <v>43572.600694444445</v>
+      </c>
+      <c r="J9" s="37">
+        <v>50001</v>
+      </c>
+      <c r="K9" s="39"/>
+    </row>
+    <row r="10" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>2018</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>964</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="F10" s="35">
+        <v>43236.986111111109</v>
+      </c>
+      <c r="G10" s="36">
+        <v>43238</v>
+      </c>
+      <c r="H10" s="35">
+        <v>43239.288194444445</v>
+      </c>
+      <c r="I10" s="35">
+        <v>43244.597222222219</v>
+      </c>
+      <c r="J10" s="37">
+        <v>43205</v>
+      </c>
+      <c r="K10" s="39"/>
+    </row>
+    <row r="11" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>2017</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>965</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>967</v>
+      </c>
+      <c r="F11" s="35">
+        <v>42792.104166666664</v>
+      </c>
+      <c r="G11" s="36">
+        <v>42796</v>
+      </c>
+      <c r="H11" s="35">
+        <v>42797.052083333336</v>
+      </c>
+      <c r="I11" s="35">
+        <v>42803.5625</v>
+      </c>
+      <c r="J11" s="37">
+        <v>26669</v>
+      </c>
+      <c r="K11" s="39"/>
+    </row>
+    <row r="12" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
+        <v>2016</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="F12" s="35">
+        <v>42445.020833333336</v>
+      </c>
+      <c r="G12" s="36">
+        <v>42449</v>
+      </c>
+      <c r="H12" s="35">
+        <v>42450.239583333336</v>
+      </c>
+      <c r="I12" s="35">
+        <v>42455.625</v>
+      </c>
+      <c r="J12" s="37">
+        <v>19437</v>
+      </c>
+      <c r="K12" s="39"/>
+    </row>
+    <row r="13" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>2015</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="F13" s="35">
+        <v>42146.003472222219</v>
+      </c>
+      <c r="G13" s="36">
+        <v>42147</v>
+      </c>
+      <c r="H13" s="35">
+        <v>42147.135416666664</v>
+      </c>
+      <c r="I13" s="35">
+        <v>42152.635416666664</v>
+      </c>
+      <c r="J13" s="37">
+        <v>18579</v>
+      </c>
+      <c r="K13" s="39"/>
+    </row>
+    <row r="14" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>2014</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="E14" s="10" t="s">
+        <v>955</v>
+      </c>
+      <c r="F14" s="35">
+        <v>41719.166666666664</v>
+      </c>
+      <c r="G14" s="36">
+        <v>41721</v>
+      </c>
+      <c r="H14" s="35">
+        <v>41722.229166666664</v>
+      </c>
+      <c r="I14" s="35">
+        <v>41719.607638888891</v>
+      </c>
+      <c r="J14" s="37">
+        <v>11398</v>
+      </c>
+      <c r="K14" s="39"/>
+    </row>
+    <row r="15" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>2013</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>955</v>
+      </c>
+      <c r="F15" s="35">
+        <v>41382.986111111109</v>
+      </c>
+      <c r="G15" s="36">
+        <v>41384</v>
+      </c>
+      <c r="H15" s="35">
+        <v>41385.21875</v>
+      </c>
+      <c r="I15" s="35">
+        <v>41392.614583333336</v>
+      </c>
+      <c r="J15" s="37">
+        <v>8939</v>
+      </c>
+      <c r="K15" s="39"/>
+    </row>
+    <row r="16" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="G5" s="29">
-        <v>44974</v>
-      </c>
-      <c r="H5" s="28">
-        <v>44974.986111111109</v>
-      </c>
-      <c r="I5" s="28">
-        <v>44977.666666666664</v>
-      </c>
-      <c r="J5" s="30">
-        <v>113621</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>962</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="F16" s="35">
+        <v>40950.232638888891</v>
+      </c>
+      <c r="G16" s="36">
+        <v>40953</v>
+      </c>
+      <c r="H16" s="35">
+        <v>40954.21875</v>
+      </c>
+      <c r="I16" s="35">
+        <v>40958.625</v>
+      </c>
+      <c r="J16" s="37">
+        <v>6328</v>
+      </c>
+      <c r="K16" s="39"/>
+    </row>
+    <row r="17" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>2011</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D17" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="F17" s="35">
+        <v>40608.989583333336</v>
+      </c>
+      <c r="G17" s="36">
+        <v>40610</v>
+      </c>
+      <c r="H17" s="35">
+        <v>40611.263888888891</v>
+      </c>
+      <c r="I17" s="35">
+        <v>40616.607638888891</v>
+      </c>
+      <c r="J17" s="37">
+        <v>5465</v>
+      </c>
+      <c r="K17" s="39"/>
+    </row>
+    <row r="18" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <v>2010</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="F18" s="35">
+        <v>40321.291666666664</v>
+      </c>
+      <c r="G18" s="36">
+        <v>40325</v>
+      </c>
+      <c r="H18" s="35">
+        <v>40326.010416666664</v>
+      </c>
+      <c r="I18" s="35">
+        <v>40331.604166666664</v>
+      </c>
+      <c r="J18" s="37">
+        <v>4994</v>
+      </c>
+      <c r="K18" s="39"/>
+    </row>
+    <row r="19" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>2009</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="F19" s="35">
+        <v>39899.013888888891</v>
+      </c>
+      <c r="G19" s="36">
+        <v>39900</v>
+      </c>
+      <c r="H19" s="35">
+        <v>39900.986111111109</v>
+      </c>
+      <c r="I19" s="35">
+        <v>39904.604166666664</v>
+      </c>
+      <c r="J19" s="37">
+        <v>4938</v>
+      </c>
+      <c r="K19" s="39"/>
+    </row>
+    <row r="20" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>2008</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="F20" s="35">
+        <v>39508.041666666664</v>
+      </c>
+      <c r="G20" s="36">
+        <v>39509</v>
+      </c>
+      <c r="H20" s="35">
+        <v>39510</v>
+      </c>
+      <c r="I20" s="35">
+        <v>39515.597222222219</v>
+      </c>
+      <c r="J20" s="37">
+        <v>4314</v>
+      </c>
+      <c r="K20" s="39"/>
+    </row>
+    <row r="21" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>2007</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="E6" s="27" t="s">
-        <v>963</v>
-      </c>
-      <c r="F6" s="32">
-        <v>44701.09375</v>
-      </c>
-      <c r="G6" s="29">
-        <v>44703</v>
-      </c>
-      <c r="H6" s="28">
-        <v>44704.010416666664</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>964</v>
-      </c>
-      <c r="J6" s="30">
-        <v>90928</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>2021</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="E21" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="F21" s="35">
+        <v>39195.319444444445</v>
+      </c>
+      <c r="G21" s="36">
+        <v>39197</v>
+      </c>
+      <c r="H21" s="35">
+        <v>39198.135416666664</v>
+      </c>
+      <c r="I21" s="35">
+        <v>39203.583333333336</v>
+      </c>
+      <c r="J21" s="37">
+        <v>3607</v>
+      </c>
+      <c r="K21" s="39" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
+        <v>2006</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>963</v>
-      </c>
-      <c r="E7" s="27" t="s">
+      <c r="D22" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="F22" s="35">
+        <v>38766.354166666664</v>
+      </c>
+      <c r="G22" s="36">
+        <v>38769</v>
+      </c>
+      <c r="H22" s="35">
+        <v>38770.041666666664</v>
+      </c>
+      <c r="I22" s="35">
+        <v>38773.5625</v>
+      </c>
+      <c r="J22" s="37">
+        <v>3342</v>
+      </c>
+      <c r="K22" s="39" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
+        <v>2005</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="F23" s="35">
+        <v>38448.34375</v>
+      </c>
+      <c r="G23" s="36">
+        <v>38451</v>
+      </c>
+      <c r="H23" s="35">
+        <v>38452.145833333336</v>
+      </c>
+      <c r="I23" s="35">
+        <v>38456.5625</v>
+      </c>
+      <c r="J23" s="37">
+        <v>3486</v>
+      </c>
+      <c r="K23" s="39" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>2004</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="F24" s="35">
+        <v>38101.319444444445</v>
+      </c>
+      <c r="G24" s="36">
+        <v>38104</v>
+      </c>
+      <c r="H24" s="35">
+        <v>38104.958333333336</v>
+      </c>
+      <c r="I24" s="35">
+        <v>38109.583333333336</v>
+      </c>
+      <c r="J24" s="37">
+        <v>3230</v>
+      </c>
+      <c r="K24" s="39" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>2003</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F7" s="32">
-        <v>44297.986111111109</v>
-      </c>
-      <c r="G7" s="29">
-        <v>44302</v>
-      </c>
-      <c r="H7" s="28">
-        <v>44302.958333333336</v>
-      </c>
-      <c r="I7" s="28">
-        <v>44305.614583333336</v>
-      </c>
-      <c r="J7" s="30">
-        <v>78672</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>2020</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="F25" s="35">
+        <v>37749.375</v>
+      </c>
+      <c r="G25" s="36">
+        <v>37753</v>
+      </c>
+      <c r="H25" s="35">
+        <v>37754.083333333336</v>
+      </c>
+      <c r="I25" s="35">
+        <v>37756.604166666664</v>
+      </c>
+      <c r="J25" s="37">
+        <v>3173</v>
+      </c>
+      <c r="K25" s="39"/>
+    </row>
+    <row r="26" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10">
+        <v>2002</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D26" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>963</v>
-      </c>
-      <c r="F8" s="32">
-        <v>44017.09375</v>
-      </c>
-      <c r="G8" s="29">
-        <v>44020</v>
-      </c>
-      <c r="H8" s="28">
-        <v>44021.21875</v>
-      </c>
-      <c r="I8" s="28">
-        <v>44025.638888888891</v>
-      </c>
-      <c r="J8" s="30">
-        <v>54599</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>2019</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>965</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="F26" s="35">
+        <v>37332.34375</v>
+      </c>
+      <c r="G26" s="36">
+        <v>37336</v>
+      </c>
+      <c r="H26" s="35">
+        <v>37336.986111111109</v>
+      </c>
+      <c r="I26" s="35">
+        <v>37340.572916666664</v>
+      </c>
+      <c r="J26" s="37">
+        <v>3141</v>
+      </c>
+      <c r="K26" s="39"/>
+    </row>
+    <row r="27" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10">
+        <v>2001</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>953</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>946</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>957</v>
-      </c>
-      <c r="F9" s="32">
-        <v>43563.055555555555</v>
-      </c>
-      <c r="G9" s="29">
-        <v>43566</v>
-      </c>
-      <c r="H9" s="28">
-        <v>43567.208333333336</v>
-      </c>
-      <c r="I9" s="28">
-        <v>43572.600694444445</v>
-      </c>
-      <c r="J9" s="30">
-        <v>50001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>2018</v>
-      </c>
-      <c r="B10" s="25" t="s">
+      <c r="D27" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>967</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>954</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>957</v>
-      </c>
-      <c r="F10" s="32">
-        <v>43236.986111111109</v>
-      </c>
-      <c r="G10" s="29">
-        <v>43238</v>
-      </c>
-      <c r="H10" s="28">
-        <v>43239.288194444445</v>
-      </c>
-      <c r="I10" s="28">
-        <v>43244.597222222219</v>
-      </c>
-      <c r="J10" s="30">
-        <v>43205</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>2017</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>968</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>969</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>963</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>970</v>
-      </c>
-      <c r="F11" s="32">
-        <v>42792.104166666664</v>
-      </c>
-      <c r="G11" s="29">
-        <v>42796</v>
-      </c>
-      <c r="H11" s="28">
-        <v>42797.052083333336</v>
-      </c>
-      <c r="I11" s="28">
-        <v>42803.5625</v>
-      </c>
-      <c r="J11" s="30">
-        <v>26669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>2016</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>971</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>972</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>963</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>957</v>
-      </c>
-      <c r="F12" s="32">
-        <v>42445.020833333336</v>
-      </c>
-      <c r="G12" s="29">
-        <v>42449</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>973</v>
-      </c>
-      <c r="I12" s="28">
-        <v>42455.625</v>
-      </c>
-      <c r="J12" s="30">
-        <v>19437</v>
-      </c>
-    </row>
+      <c r="F27" s="35">
+        <v>36959.298611111109</v>
+      </c>
+      <c r="G27" s="36">
+        <v>36961</v>
+      </c>
+      <c r="H27" s="35">
+        <v>36962.038194444445</v>
+      </c>
+      <c r="I27" s="35">
+        <v>36968.611111111109</v>
+      </c>
+      <c r="J27" s="37"/>
+      <c r="K27" s="39" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10791,7 +11397,7 @@
         <v>2016</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -10817,7 +11423,7 @@
         <v>2016</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
@@ -10829,13 +11435,13 @@
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -10843,7 +11449,7 @@
         <v>2016</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -10855,7 +11461,7 @@
         <v>6.1111111111111109E-2</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>
@@ -10864,7 +11470,7 @@
         <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -10872,7 +11478,7 @@
         <v>2016</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -10884,7 +11490,7 @@
         <v>0.12222222222222222</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
@@ -10893,7 +11499,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -10901,7 +11507,7 @@
         <v>2016</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -10922,7 +11528,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -10930,7 +11536,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -10942,7 +11548,7 @@
         <v>0.33194444444444443</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>10</v>
@@ -10956,7 +11562,7 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -10968,7 +11574,7 @@
         <v>0.37569444444444444</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>10</v>
@@ -10982,7 +11588,7 @@
         <v>2016</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C9" s="2">
         <v>3</v>
@@ -10994,7 +11600,7 @@
         <v>0.40763888888888888</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>10</v>
@@ -11003,7 +11609,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11011,7 +11617,7 @@
         <v>2016</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -11023,7 +11629,7 @@
         <v>0.45</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>10</v>
@@ -11037,7 +11643,7 @@
         <v>2016</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -11049,7 +11655,7 @@
         <v>0.67638888888888893</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>10</v>
@@ -11063,7 +11669,7 @@
         <v>2016</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C12" s="2">
         <v>3</v>
@@ -11075,7 +11681,7 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>10</v>
@@ -11084,7 +11690,7 @@
         <v>26</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11092,7 +11698,7 @@
         <v>2016</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
@@ -11104,7 +11710,7 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>10</v>
@@ -11118,7 +11724,7 @@
         <v>2016</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -11139,7 +11745,7 @@
         <v>13</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11147,7 +11753,7 @@
         <v>2016</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -11159,7 +11765,7 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>10</v>
@@ -11168,7 +11774,7 @@
         <v>13</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11176,7 +11782,7 @@
         <v>2016</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -11188,7 +11794,7 @@
         <v>0.34166666666666667</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>10</v>
@@ -11197,7 +11803,7 @@
         <v>13</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11205,7 +11811,7 @@
         <v>2016</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
@@ -11226,7 +11832,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11234,7 +11840,7 @@
         <v>2016</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
@@ -11246,7 +11852,7 @@
         <v>0.43333333333333335</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>10</v>
@@ -11255,7 +11861,7 @@
         <v>13</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11263,7 +11869,7 @@
         <v>2016</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -11275,7 +11881,7 @@
         <v>0.51249999999999996</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>10</v>
@@ -11292,7 +11898,7 @@
         <v>2016</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -11304,7 +11910,7 @@
         <v>0.69236111111111109</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>10</v>
@@ -11318,7 +11924,7 @@
         <v>2016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -11330,7 +11936,7 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>10</v>
@@ -11339,7 +11945,7 @@
         <v>26</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11347,7 +11953,7 @@
         <v>2016</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -11359,7 +11965,7 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>10</v>
@@ -11373,7 +11979,7 @@
         <v>2016</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -11385,7 +11991,7 @@
         <v>0.23749999999999999</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>10</v>
@@ -11396,7 +12002,7 @@
         <v>2016</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -11408,7 +12014,7 @@
         <v>0.26874999999999999</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>10</v>
@@ -11425,7 +12031,7 @@
         <v>2016</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -11437,7 +12043,7 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>10</v>
@@ -11446,7 +12052,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11454,7 +12060,7 @@
         <v>2016</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -11466,7 +12072,7 @@
         <v>0.46805555555555556</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>10</v>
@@ -11483,7 +12089,7 @@
         <v>2016</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
@@ -11495,7 +12101,7 @@
         <v>0.6</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>10</v>
@@ -11506,7 +12112,7 @@
         <v>2016</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -11518,7 +12124,7 @@
         <v>0.64930555555555558</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>10</v>
@@ -11529,7 +12135,7 @@
         <v>2016</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C29" s="2">
         <v>3</v>
@@ -11558,7 +12164,7 @@
         <v>2016</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C30" s="2">
         <v>3</v>
@@ -11584,7 +12190,7 @@
         <v>2016</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C31" s="2">
         <v>3</v>
@@ -11596,7 +12202,7 @@
         <v>0.28402777777777777</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>10</v>
@@ -11605,7 +12211,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11613,7 +12219,7 @@
         <v>2016</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C32" s="2">
         <v>3</v>
@@ -11625,7 +12231,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>10</v>
@@ -11636,7 +12242,7 @@
         <v>2016</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C33" s="2">
         <v>3</v>
@@ -11648,7 +12254,7 @@
         <v>0.47708333333333336</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>10</v>
@@ -11665,7 +12271,7 @@
         <v>2016</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C34" s="2">
         <v>3</v>
@@ -11677,7 +12283,7 @@
         <v>0.6069444444444444</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>10</v>
@@ -11688,7 +12294,7 @@
         <v>2016</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C35" s="2">
         <v>3</v>
@@ -11700,7 +12306,7 @@
         <v>0.66041666666666665</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>10</v>
@@ -11714,7 +12320,7 @@
         <v>2016</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C36" s="2">
         <v>3</v>
@@ -11726,7 +12332,7 @@
         <v>0.68333333333333335</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>10</v>
@@ -11737,7 +12343,7 @@
         <v>2016</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C37" s="2">
         <v>3</v>
@@ -11749,7 +12355,7 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>10</v>
@@ -11760,7 +12366,7 @@
         <v>2016</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C38" s="2">
         <v>3</v>
@@ -11772,7 +12378,7 @@
         <v>0.75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>10</v>
@@ -11786,7 +12392,7 @@
         <v>2016</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C39" s="2">
         <v>3</v>
@@ -11798,7 +12404,7 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>10</v>
@@ -11807,7 +12413,7 @@
         <v>26</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11815,7 +12421,7 @@
         <v>2016</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
@@ -11827,7 +12433,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>10</v>
@@ -11841,7 +12447,7 @@
         <v>2016</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C41" s="2">
         <v>3</v>
@@ -11853,7 +12459,7 @@
         <v>0.19583333333333333</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>10</v>
@@ -11864,7 +12470,7 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C42" s="2">
         <v>3</v>
@@ -11876,7 +12482,7 @@
         <v>0.21041666666666667</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>10</v>
@@ -11887,7 +12493,7 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C43" s="2">
         <v>3</v>
@@ -11899,7 +12505,7 @@
         <v>0.26805555555555555</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>10</v>
@@ -11913,7 +12519,7 @@
         <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C44" s="2">
         <v>3</v>
@@ -11925,7 +12531,7 @@
         <v>0.3</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>10</v>
@@ -11934,7 +12540,7 @@
         <v>13</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11942,7 +12548,7 @@
         <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C45" s="2">
         <v>3</v>
@@ -11954,7 +12560,7 @@
         <v>0.36805555555555558</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>10</v>
@@ -11963,7 +12569,7 @@
         <v>13</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11971,7 +12577,7 @@
         <v>2016</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C46" s="2">
         <v>3</v>
@@ -11983,7 +12589,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
@@ -11994,7 +12600,7 @@
         <v>2016</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C47" s="2">
         <v>3</v>
@@ -12015,7 +12621,7 @@
         <v>13</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12023,7 +12629,7 @@
         <v>2016</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C48" s="2">
         <v>3</v>
@@ -12049,7 +12655,7 @@
         <v>2016</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C49" s="2">
         <v>3</v>
@@ -12067,7 +12673,7 @@
         <v>10</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12075,7 +12681,7 @@
         <v>2016</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C50" s="2">
         <v>3</v>
@@ -12101,7 +12707,7 @@
         <v>2016</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C51" s="2">
         <v>3</v>
@@ -12122,7 +12728,7 @@
         <v>13</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12130,7 +12736,7 @@
         <v>2016</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C52" s="2">
         <v>3</v>
@@ -12142,7 +12748,7 @@
         <v>0.33194444444444443</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>109</v>
@@ -12153,7 +12759,7 @@
         <v>2016</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C53" s="2">
         <v>3</v>
@@ -12165,7 +12771,7 @@
         <v>0.39166666666666666</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>109</v>
@@ -12174,7 +12780,7 @@
         <v>13</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12182,7 +12788,7 @@
         <v>2016</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C54" s="2">
         <v>3</v>
@@ -12194,7 +12800,7 @@
         <v>0.41180555555555554</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>109</v>
@@ -12211,7 +12817,7 @@
         <v>2016</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C55" s="2">
         <v>3</v>
@@ -12232,7 +12838,7 @@
         <v>13</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12240,7 +12846,7 @@
         <v>2016</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C56" s="2">
         <v>3</v>
@@ -12252,7 +12858,7 @@
         <v>0.48472222222222222</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>109</v>
@@ -12261,7 +12867,7 @@
         <v>640</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12269,7 +12875,7 @@
         <v>2016</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C57" s="2">
         <v>3</v>
@@ -12281,7 +12887,7 @@
         <v>0.71319444444444446</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>109</v>
@@ -12292,7 +12898,7 @@
         <v>2016</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C58" s="2">
         <v>3</v>
@@ -12304,7 +12910,7 @@
         <v>0.71944444444444444</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>109</v>
@@ -12315,7 +12921,7 @@
         <v>2016</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C59" s="2">
         <v>3</v>
@@ -12327,7 +12933,7 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>109</v>
@@ -12338,7 +12944,7 @@
         <v>2016</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C60" s="2">
         <v>3</v>
@@ -12359,7 +12965,7 @@
         <v>26</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12367,7 +12973,7 @@
         <v>2016</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
@@ -12393,7 +12999,7 @@
         <v>2016</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C62" s="2">
         <v>3</v>
@@ -12405,7 +13011,7 @@
         <v>0.3298611111111111</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>109</v>
@@ -12414,7 +13020,7 @@
         <v>13</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12422,7 +13028,7 @@
         <v>2016</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C63" s="2">
         <v>3</v>
@@ -12434,7 +13040,7 @@
         <v>0.375</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>109</v>
@@ -12451,7 +13057,7 @@
         <v>2016</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C64" s="2">
         <v>3</v>
@@ -12480,7 +13086,7 @@
         <v>2016</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C65" s="2">
         <v>3</v>
@@ -12492,7 +13098,7 @@
         <v>0.56597222222222221</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>109</v>
@@ -12509,7 +13115,7 @@
         <v>2016</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C66" s="2">
         <v>3</v>
@@ -12521,7 +13127,7 @@
         <v>0.64375000000000004</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>109</v>
@@ -12530,7 +13136,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12538,7 +13144,7 @@
         <v>2016</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C67" s="2">
         <v>3</v>
@@ -12550,7 +13156,7 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>109</v>
@@ -12561,7 +13167,7 @@
         <v>2016</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C68" s="2">
         <v>3</v>
@@ -12573,7 +13179,7 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>109</v>
@@ -12584,7 +13190,7 @@
         <v>2016</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C69" s="2">
         <v>3</v>
@@ -12596,7 +13202,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>109</v>
@@ -12605,7 +13211,7 @@
         <v>26</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12613,7 +13219,7 @@
         <v>2016</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C70" s="2">
         <v>3</v>
@@ -12625,7 +13231,7 @@
         <v>0.25</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>109</v>
@@ -12639,7 +13245,7 @@
         <v>2016</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C71" s="2">
         <v>3</v>
@@ -12651,7 +13257,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>109</v>
@@ -12660,7 +13266,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12668,7 +13274,7 @@
         <v>2016</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C72" s="2">
         <v>3</v>
@@ -12680,7 +13286,7 @@
         <v>0.38819444444444445</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>109</v>
@@ -12694,7 +13300,7 @@
         <v>2016</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C73" s="2">
         <v>3</v>
@@ -12706,7 +13312,7 @@
         <v>0.42986111111111114</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>109</v>
@@ -12715,7 +13321,7 @@
         <v>13</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12723,7 +13329,7 @@
         <v>2016</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C74" s="2">
         <v>3</v>
@@ -12735,7 +13341,7 @@
         <v>0.47083333333333333</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>109</v>
@@ -12746,7 +13352,7 @@
         <v>2016</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C75" s="2">
         <v>3</v>
@@ -12758,7 +13364,7 @@
         <v>0.48055555555555557</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>109</v>
@@ -12775,7 +13381,7 @@
         <v>2016</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C76" s="2">
         <v>3</v>
@@ -12787,7 +13393,7 @@
         <v>0.61250000000000004</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>109</v>
@@ -12801,7 +13407,7 @@
         <v>2016</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C77" s="2">
         <v>3</v>
@@ -12813,7 +13419,7 @@
         <v>0.63055555555555554</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>109</v>
@@ -12824,7 +13430,7 @@
         <v>2016</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C78" s="2">
         <v>3</v>
@@ -12836,7 +13442,7 @@
         <v>0.70416666666666672</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>109</v>
@@ -12850,7 +13456,7 @@
         <v>2016</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C79" s="2">
         <v>3</v>
@@ -12862,7 +13468,7 @@
         <v>0.78333333333333333</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>109</v>
@@ -12871,7 +13477,7 @@
         <v>26</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12879,7 +13485,7 @@
         <v>2016</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C80" s="2">
         <v>3</v>
@@ -12891,7 +13497,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>109</v>
@@ -12905,7 +13511,7 @@
         <v>2016</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C81" s="2">
         <v>3</v>
@@ -12917,7 +13523,7 @@
         <v>0.16944444444444445</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>109</v>
@@ -12928,7 +13534,7 @@
         <v>2016</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C82" s="2">
         <v>3</v>
@@ -12940,7 +13546,7 @@
         <v>0.23472222222222222</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>109</v>
@@ -12954,7 +13560,7 @@
         <v>2016</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C83" s="2">
         <v>3</v>
@@ -12966,7 +13572,7 @@
         <v>0.31805555555555554</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>109</v>
@@ -12977,7 +13583,7 @@
         <v>2016</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C84" s="2">
         <v>3</v>
@@ -12989,7 +13595,7 @@
         <v>0.3215277777777778</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>109</v>
@@ -13000,7 +13606,7 @@
         <v>2016</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C85" s="2">
         <v>3</v>
@@ -13012,7 +13618,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>109</v>
@@ -13021,7 +13627,7 @@
         <v>13</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13029,7 +13635,7 @@
         <v>2016</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C86" s="2">
         <v>3</v>
@@ -13041,7 +13647,7 @@
         <v>0.37361111111111112</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>109</v>
@@ -13050,7 +13656,7 @@
         <v>13</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13058,7 +13664,7 @@
         <v>2016</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C87" s="2">
         <v>3</v>
@@ -13070,7 +13676,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>109</v>
@@ -13079,7 +13685,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13087,7 +13693,7 @@
         <v>2016</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C88" s="2">
         <v>3</v>
@@ -13099,7 +13705,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>109</v>
@@ -13110,7 +13716,7 @@
         <v>2016</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C89" s="2">
         <v>3</v>
@@ -13122,7 +13728,7 @@
         <v>0.46180555555555558</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>109</v>
@@ -13139,7 +13745,7 @@
         <v>2016</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C90" s="2">
         <v>3</v>
@@ -13151,7 +13757,7 @@
         <v>0.56041666666666667</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>109</v>
@@ -13162,7 +13768,7 @@
         <v>2016</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C91" s="2">
         <v>3</v>
@@ -13174,7 +13780,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>109</v>
@@ -13185,7 +13791,7 @@
         <v>2016</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C92" s="2">
         <v>3</v>
@@ -13197,7 +13803,7 @@
         <v>0.67222222222222228</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>109</v>
@@ -13208,7 +13814,7 @@
         <v>2016</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C93" s="2">
         <v>3</v>
@@ -13220,7 +13826,7 @@
         <v>0.68611111111111112</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>109</v>
@@ -13231,7 +13837,7 @@
         <v>2016</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C94" s="2">
         <v>3</v>
@@ -13243,7 +13849,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>109</v>
@@ -13254,7 +13860,7 @@
         <v>2016</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C95" s="2">
         <v>3</v>
@@ -13275,7 +13881,7 @@
         <v>13</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13283,7 +13889,7 @@
         <v>2016</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C96" s="2">
         <v>3</v>
@@ -13295,7 +13901,7 @@
         <v>0.7993055555555556</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>109</v>
@@ -13306,7 +13912,7 @@
         <v>2016</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C97" s="2">
         <v>3</v>
@@ -13318,7 +13924,7 @@
         <v>0.80555555555555558</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>109</v>
@@ -13329,7 +13935,7 @@
         <v>2016</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C98" s="2">
         <v>3</v>
@@ -13341,7 +13947,7 @@
         <v>0.81527777777777777</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>109</v>
@@ -13352,7 +13958,7 @@
         <v>2016</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C99" s="2">
         <v>3</v>
@@ -13364,7 +13970,7 @@
         <v>0.82986111111111116</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>109</v>
@@ -13373,7 +13979,7 @@
         <v>26</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13381,7 +13987,7 @@
         <v>2016</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C100" s="2">
         <v>3</v>
@@ -13393,7 +13999,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>109</v>
@@ -13404,7 +14010,7 @@
         <v>2016</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C101" s="2">
         <v>3</v>
@@ -13416,7 +14022,7 @@
         <v>0.18055555555555555</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>109</v>
@@ -13430,7 +14036,7 @@
         <v>2016</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C102" s="2">
         <v>3</v>
@@ -13442,7 +14048,7 @@
         <v>0.21111111111111111</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>109</v>
@@ -13453,7 +14059,7 @@
         <v>2016</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C103" s="2">
         <v>3</v>
@@ -13465,7 +14071,7 @@
         <v>0.21875</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>109</v>
@@ -13476,7 +14082,7 @@
         <v>2016</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C104" s="2">
         <v>3</v>
@@ -13488,7 +14094,7 @@
         <v>0.2986111111111111</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>109</v>
@@ -13502,7 +14108,7 @@
         <v>2016</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C105" s="2">
         <v>3</v>
@@ -13514,7 +14120,7 @@
         <v>0.31944444444444442</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>109</v>
@@ -13525,7 +14131,7 @@
         <v>2016</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C106" s="2">
         <v>3</v>
@@ -13537,7 +14143,7 @@
         <v>0.32291666666666669</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>109</v>
@@ -13548,7 +14154,7 @@
         <v>2016</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C107" s="2">
         <v>3</v>
@@ -13560,7 +14166,7 @@
         <v>0.32569444444444445</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>109</v>
@@ -13571,7 +14177,7 @@
         <v>2016</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C108" s="2">
         <v>3</v>
@@ -13583,7 +14189,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>109</v>
@@ -13597,7 +14203,7 @@
         <v>2016</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C109" s="2">
         <v>3</v>
@@ -13609,7 +14215,7 @@
         <v>0.35069444444444442</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>109</v>
@@ -13623,7 +14229,7 @@
         <v>2016</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C110" s="2">
         <v>3</v>
@@ -13635,7 +14241,7 @@
         <v>0.36319444444444443</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>109</v>
@@ -13646,7 +14252,7 @@
         <v>2016</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C111" s="2">
         <v>3</v>
@@ -13658,7 +14264,7 @@
         <v>0.375</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>109</v>
@@ -13669,7 +14275,7 @@
         <v>2016</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C112" s="2">
         <v>3</v>
@@ -13681,7 +14287,7 @@
         <v>0.39305555555555555</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>109</v>
@@ -13692,7 +14298,7 @@
         <v>2016</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C113" s="2">
         <v>3</v>
@@ -13718,7 +14324,7 @@
         <v>2016</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C114" s="2">
         <v>3</v>
@@ -13730,7 +14336,7 @@
         <v>0.44305555555555554</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>109</v>
@@ -13744,7 +14350,7 @@
         <v>2016</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C115" s="2">
         <v>3</v>
@@ -13756,7 +14362,7 @@
         <v>0.47569444444444442</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>109</v>
@@ -13770,7 +14376,7 @@
         <v>2016</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C116" s="2">
         <v>3</v>
@@ -13782,7 +14388,7 @@
         <v>0.53472222222222221</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>109</v>
@@ -13796,7 +14402,7 @@
         <v>2016</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C117" s="2">
         <v>3</v>
@@ -13808,7 +14414,7 @@
         <v>0.55138888888888893</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>109</v>
@@ -13822,7 +14428,7 @@
         <v>2016</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C118" s="2">
         <v>3</v>
@@ -13843,7 +14449,7 @@
         <v>13</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13851,7 +14457,7 @@
         <v>2016</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C119" s="2">
         <v>3</v>
@@ -13872,7 +14478,7 @@
         <v>13</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13880,7 +14486,7 @@
         <v>2016</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C120" s="2">
         <v>3</v>
@@ -13892,7 +14498,7 @@
         <v>0.59444444444444444</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>109</v>
@@ -13903,7 +14509,7 @@
         <v>2016</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C121" s="2">
         <v>3</v>
@@ -13915,7 +14521,7 @@
         <v>0.59722222222222221</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>109</v>
@@ -13926,7 +14532,7 @@
         <v>2016</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C122" s="2">
         <v>3</v>
@@ -13947,7 +14553,7 @@
         <v>26</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13955,7 +14561,7 @@
         <v>2016</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C123" s="2">
         <v>3</v>
@@ -13981,7 +14587,7 @@
         <v>2016</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C124" s="2">
         <v>3</v>
@@ -14002,7 +14608,7 @@
         <v>646</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -14010,7 +14616,7 @@
         <v>2016</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C125" s="2">
         <v>3</v>
@@ -14022,7 +14628,7 @@
         <v>0.38055555555555554</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>109</v>
@@ -14033,7 +14639,7 @@
         <v>2016</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C126" s="2">
         <v>3</v>
@@ -14045,7 +14651,7 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>109</v>
@@ -14059,7 +14665,7 @@
         <v>2016</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C127" s="2">
         <v>3</v>
@@ -14071,7 +14677,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>109</v>
@@ -14085,7 +14691,7 @@
         <v>2016</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C128" s="2">
         <v>3</v>
@@ -14114,7 +14720,7 @@
         <v>2016</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C129" s="2">
         <v>3</v>
@@ -14133,6 +14739,286 @@
       </c>
       <c r="H129" s="1" t="s">
         <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{238C4319-3B5C-4026-A29F-DFFEC3829F6F}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71112823-5116-4DED-BE2B-28BC05E9BD54}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E1737E-0608-49B0-A59D-D04F23EE2FA4}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071DC04A-B6F2-42A1-B34C-F841B6BC9DE2}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CF3F325-53A3-44B1-BBCE-A5EEC48B43F8}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2267F0-4444-434D-AFD4-6426E1490789}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41F0BBF-0A24-488B-A0FE-5C1735F12A0C}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -14202,7 +15088,7 @@
       <c r="D2" s="11">
         <v>12</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="26">
         <v>0.99652777777777779</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -14232,7 +15118,7 @@
       <c r="D3" s="11">
         <v>20</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="26">
         <v>0.67361111111111116</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -22915,7 +23801,7 @@
   <cols>
     <col min="1" max="2" width="7.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="5.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="38" customWidth="1"/>
+    <col min="5" max="5" width="16" style="13" customWidth="1"/>
     <col min="6" max="6" width="46.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.88671875" style="15" bestFit="1" customWidth="1"/>
@@ -22924,31 +23810,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>647</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="27" t="s">
         <v>662</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="27" t="s">
         <v>663</v>
       </c>
     </row>
@@ -22965,7 +23851,7 @@
       <c r="D2" s="11">
         <v>11</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="15" t="s">
@@ -22979,384 +23865,384 @@
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34">
+      <c r="A3" s="28">
         <v>2021</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="29">
         <v>4</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="29">
         <v>12</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="34"/>
+      <c r="G3" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34">
+      <c r="A4" s="28">
         <v>2021</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="29">
         <v>4</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="29">
         <v>12</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="34"/>
+      <c r="G4" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="28"/>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34">
+      <c r="A5" s="28">
         <v>2021</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="29">
         <v>4</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="29">
         <v>12</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="30">
         <v>0.18333333333333332</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="34"/>
+      <c r="G5" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="28"/>
     </row>
     <row r="6" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34">
+      <c r="A6" s="28">
         <v>2021</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="29">
         <v>4</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="29">
         <v>12</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="30">
         <v>0.22013888888888888</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="34"/>
+      <c r="G6" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="28"/>
     </row>
     <row r="7" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34">
+      <c r="A7" s="28">
         <v>2021</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="29">
         <v>4</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="29">
         <v>12</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="30">
         <v>0.23541666666666666</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="28" t="s">
         <v>648</v>
       </c>
-      <c r="G7" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="34"/>
+      <c r="G7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="28"/>
     </row>
     <row r="8" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34">
+      <c r="A8" s="28">
         <v>2021</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="29">
         <v>4</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="29">
         <v>12</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="34"/>
+      <c r="G8" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34">
+      <c r="A9" s="28">
         <v>2021</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="29">
         <v>4</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="29">
         <v>12</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="30">
         <v>0.28541666666666665</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="34"/>
+      <c r="G9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="28"/>
     </row>
     <row r="10" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34">
+      <c r="A10" s="28">
         <v>2021</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="29">
         <v>4</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="29">
         <v>12</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="30">
         <v>0.37708333333333333</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="34"/>
+      <c r="G10" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="28"/>
     </row>
     <row r="11" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34">
+      <c r="A11" s="28">
         <v>2021</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="29">
         <v>4</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="29">
         <v>12</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="30">
         <v>0.39791666666666664</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="34"/>
+      <c r="G11" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="28"/>
     </row>
     <row r="12" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34">
+      <c r="A12" s="28">
         <v>2021</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="29">
         <v>4</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="29">
         <v>12</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="30">
         <v>0.45347222222222222</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="28" t="s">
         <v>745</v>
       </c>
-      <c r="G12" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="34" t="s">
+      <c r="G12" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="28" t="s">
         <v>640</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="28" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34">
+      <c r="A13" s="28">
         <v>2021</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="29">
         <v>4</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="29">
         <v>12</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="30">
         <v>0.55208333333333337</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="34"/>
+      <c r="G13" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34">
+      <c r="A14" s="28">
         <v>2021</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="29">
         <v>4</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="29">
         <v>12</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="30">
         <v>0.66388888888888886</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="34"/>
+      <c r="G14" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="28"/>
     </row>
     <row r="15" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="34">
+      <c r="A15" s="28">
         <v>2021</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="29">
         <v>4</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="29">
         <v>12</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="30">
         <v>0.70138888888888884</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="34"/>
+      <c r="G15" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="34">
+      <c r="A16" s="28">
         <v>2021</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="29">
         <v>4</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="29">
         <v>12</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="30">
         <v>0.72569444444444442</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="34" t="s">
+      <c r="G16" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="28" t="s">
         <v>668</v>
       </c>
     </row>
@@ -23425,7 +24311,7 @@
       <c r="D19" s="11">
         <v>13</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="13" t="s">
         <v>42</v>
       </c>
       <c r="F19" s="15" t="s">
@@ -23454,7 +24340,7 @@
       <c r="D20" s="11">
         <v>13</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="15" t="s">
@@ -23493,7 +24379,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -23587,7 +24473,7 @@
       <c r="D25" s="11">
         <v>13</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="13" t="s">
         <v>45</v>
       </c>
       <c r="F25" s="15" t="s">
@@ -23924,7 +24810,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -23953,7 +24839,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -23982,7 +24868,7 @@
         <v>13</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -24011,7 +24897,7 @@
         <v>13</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -24124,7 +25010,7 @@
         <v>13</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -24196,7 +25082,7 @@
         <v>69</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G47" s="15" t="s">
         <v>10</v>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4A1490-EB94-4555-B5B7-8A2C3910B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E712794D-9BF9-4A39-A45E-FEA40CF56AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" firstSheet="6" activeTab="18" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -32,6 +32,14 @@
     <sheet name="2011" sheetId="20" r:id="rId17"/>
     <sheet name="2010" sheetId="21" r:id="rId18"/>
     <sheet name="2009" sheetId="22" r:id="rId19"/>
+    <sheet name="2008" sheetId="23" r:id="rId20"/>
+    <sheet name="2007" sheetId="24" r:id="rId21"/>
+    <sheet name="2006" sheetId="25" r:id="rId22"/>
+    <sheet name="2005" sheetId="26" r:id="rId23"/>
+    <sheet name="2004" sheetId="27" r:id="rId24"/>
+    <sheet name="2003" sheetId="28" r:id="rId25"/>
+    <sheet name="2002" sheetId="29" r:id="rId26"/>
+    <sheet name="2001" sheetId="30" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2016'!$A$1:$I$121</definedName>
@@ -4170,8 +4178,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
-    <numFmt numFmtId="180" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="181" formatCode="yyyy/mm/dd\ hh:mm"/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy/mm/dd\ hh:mm"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -4921,16 +4929,16 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -5320,8 +5328,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3F28DB-C154-4233-B038-4B4939AF5845}">
-  <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultRowHeight="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" style="7" bestFit="1" customWidth="1"/>
@@ -5330,11 +5338,11 @@
     <col min="7" max="7" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="16.33203125" style="34" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" style="25"/>
-    <col min="11" max="11" width="79.109375" style="40" customWidth="1"/>
+    <col min="11" max="11" width="150.88671875" style="40" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>941</v>
       </c>
@@ -5369,7 +5377,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>2026</v>
       </c>
@@ -5400,7 +5408,7 @@
       <c r="J2" s="37"/>
       <c r="K2" s="39"/>
     </row>
-    <row r="3" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2025</v>
       </c>
@@ -5433,7 +5441,7 @@
       </c>
       <c r="K3" s="39"/>
     </row>
-    <row r="4" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>2024</v>
       </c>
@@ -5468,7 +5476,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>2023</v>
       </c>
@@ -5501,7 +5509,7 @@
       </c>
       <c r="K5" s="39"/>
     </row>
-    <row r="6" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>2022</v>
       </c>
@@ -5534,7 +5542,7 @@
       </c>
       <c r="K6" s="39"/>
     </row>
-    <row r="7" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>2021</v>
       </c>
@@ -5567,7 +5575,7 @@
       </c>
       <c r="K7" s="39"/>
     </row>
-    <row r="8" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>2020</v>
       </c>
@@ -5602,7 +5610,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>2019</v>
       </c>
@@ -5635,7 +5643,7 @@
       </c>
       <c r="K9" s="39"/>
     </row>
-    <row r="10" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>2018</v>
       </c>
@@ -5668,7 +5676,7 @@
       </c>
       <c r="K10" s="39"/>
     </row>
-    <row r="11" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>2017</v>
       </c>
@@ -5701,7 +5709,7 @@
       </c>
       <c r="K11" s="39"/>
     </row>
-    <row r="12" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>2016</v>
       </c>
@@ -5734,7 +5742,7 @@
       </c>
       <c r="K12" s="39"/>
     </row>
-    <row r="13" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>2015</v>
       </c>
@@ -5767,7 +5775,7 @@
       </c>
       <c r="K13" s="39"/>
     </row>
-    <row r="14" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>2014</v>
       </c>
@@ -5800,7 +5808,7 @@
       </c>
       <c r="K14" s="39"/>
     </row>
-    <row r="15" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>2013</v>
       </c>
@@ -5833,7 +5841,7 @@
       </c>
       <c r="K15" s="39"/>
     </row>
-    <row r="16" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>2012</v>
       </c>
@@ -5866,7 +5874,7 @@
       </c>
       <c r="K16" s="39"/>
     </row>
-    <row r="17" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>2011</v>
       </c>
@@ -5899,7 +5907,7 @@
       </c>
       <c r="K17" s="39"/>
     </row>
-    <row r="18" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>2010</v>
       </c>
@@ -5932,7 +5940,7 @@
       </c>
       <c r="K18" s="39"/>
     </row>
-    <row r="19" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>2009</v>
       </c>
@@ -5965,7 +5973,7 @@
       </c>
       <c r="K19" s="39"/>
     </row>
-    <row r="20" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>2008</v>
       </c>
@@ -5998,7 +6006,7 @@
       </c>
       <c r="K20" s="39"/>
     </row>
-    <row r="21" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>2007</v>
       </c>
@@ -6033,7 +6041,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>2006</v>
       </c>
@@ -6068,7 +6076,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>2005</v>
       </c>
@@ -6103,7 +6111,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>2004</v>
       </c>
@@ -6138,7 +6146,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>2003</v>
       </c>
@@ -6171,7 +6179,7 @@
       </c>
       <c r="K25" s="39"/>
     </row>
-    <row r="26" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2002</v>
       </c>
@@ -6204,7 +6212,7 @@
       </c>
       <c r="K26" s="39"/>
     </row>
-    <row r="27" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>2001</v>
       </c>
@@ -6237,7 +6245,6 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="30.7" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15167,6 +15174,86 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5399A3CB-40E8-4F87-9DC6-AC738ADB3624}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594C237D-52BB-4F8F-BA89-944DE94740EF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1ED302-16F8-4594-8992-F5BE7AFA0126}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA33765F-C99D-4C2E-BD6C-D3E5C66D2286}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F4A28B-F86A-4A31-9F01-D11CAD731F87}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDB0580-307B-4CE0-9192-3DF05A2E112C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{111A1D3D-BE07-47E5-8B70-2CB526C36494}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A4FD4C-5042-4295-A599-06BD19DB8CE1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6791F27F-B0F5-44C5-B051-C2E20ECCAC54}">
   <dimension ref="A1:N64"/>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E712794D-9BF9-4A39-A45E-FEA40CF56AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDB7086-3E43-47EB-A0E9-10E3A98E048F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3779" uniqueCount="1127">
   <si>
     <t>年份</t>
   </si>
@@ -15036,7 +15036,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD22D530-CC3B-44CF-9F92-B519A5B48D14}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" style="11" bestFit="1" customWidth="1"/>
@@ -15053,7 +15053,7 @@
     <col min="15" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -15082,61 +15082,11 @@
         <v>663</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>943</v>
-      </c>
-      <c r="C2" s="11">
-        <v>4</v>
-      </c>
-      <c r="D2" s="11">
-        <v>12</v>
-      </c>
-      <c r="E2" s="26">
-        <v>0.99652777777777779</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>641</v>
-      </c>
-      <c r="N2" s="2" t="e">
-        <f>MID(#REF!,6,LEN(#REF!))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>943</v>
-      </c>
-      <c r="C3" s="11">
-        <v>4</v>
-      </c>
-      <c r="D3" s="11">
-        <v>20</v>
-      </c>
-      <c r="E3" s="26">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>122</v>
-      </c>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E2" s="26"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E3" s="26"/>
     </row>
     <row r="32" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F32" s="12"/>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDB7086-3E43-47EB-A0E9-10E3A98E048F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E07EE-89F5-4833-A75E-45BF309F2E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="-50" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3779" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="1128">
   <si>
     <t>年份</t>
   </si>
@@ -4169,6 +4169,10 @@
   </si>
   <si>
     <t>60年第二次駐駕大甲鎮瀾宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>相隔三年再度停駕大甲鎮瀾宮。首度拱天宮大媽、拱天宮爐主媽、山邊媽同轎</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -5405,8 +5409,12 @@
       <c r="I2" s="35">
         <v>46132.673611111109</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="39"/>
+      <c r="J2" s="37">
+        <v>463558</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>1127</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E07EE-89F5-4833-A75E-45BF309F2E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D86946D-4A27-4720-B496-ED97F22D7218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
+    <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
   <sheets>
     <sheet name="年度資訊" sheetId="12" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2023'!$A$1:$I$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2024'!$A$1:$I$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025'!$A$1:$I$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$A$1:$I$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4168" uniqueCount="1195">
   <si>
     <t>年份</t>
   </si>
@@ -4173,6 +4173,273 @@
   </si>
   <si>
     <t>相隔三年再度停駕大甲鎮瀾宮。首度拱天宮大媽、拱天宮爐主媽、山邊媽同轎</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港六媽金順崇轎班會紅壇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄通灣里鎮安宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄永芬汽車保養廠，通霄白沙屯聖母會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苑裡鎮農會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOYOTA苑裡營業所服務廠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水正牌米糕莊點心站</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大甲永信藥品工業股份有限公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>文昌國小讓小朋友鑽轎底賜福</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>南投三龍府紅壇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫雲巖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水正牌米糕莊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中范陽堂神壇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>台新服裝行臨時紅壇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙鹿聯誼會棚架(沙田路17號旁空地)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>海口聯合點心站</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中市龍井區公所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大肚公有零售市場門前</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白沙屯大肚聯誼會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>福懋油脂股份有限公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>興農股份有限公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>許瑞興工業股份有限公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰全輪胎五金有限公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化縣警察局交通警察隊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>秀傳紀念醫院</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大通電子公司</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白沙屯花壇聯誼會和山邊媽彰化聯誼會（中間紅壇）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中華賓士員林展示中心</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>田尾國小司令臺禮義廉恥前</t>
+  </si>
+  <si>
+    <t>白沙屯郵局旁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>內島里看戲處</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新埔看戲處</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息至09:50起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄通灣里慈后宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通霄車站前臨時棚架</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔天06:00起起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>五南里</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中玄誠會 慈祥飾品 宣威國際</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>苑裡站前丸勝點心站</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>外燴先生美食料理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>船頭埔海鮮餐廳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>安益輪胎行</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>童綜合醫院</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣大道八段698號</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大庄浩天宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>梧棲安良港觀玄宮紅壇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>慈心聖母聯誼會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>盧厝普安宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西螺福興宮，午休至14:00起駕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>西螺廣福宮老大媽廟</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>東昇幼兒園</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鴻宜建設機構-善水玥舍</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>廟口餐廳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>無名手沖咖啡</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林元長鄉振興路24號，雲145縣道與雲172縣交叉路口</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>北港鎮民代表會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>典尙DS HAIR</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彰化警察局溪湖分局埔鹽分駐所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹塘幸竹宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>埤頭合興宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林埤腳慈聖宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>土庫國小點心攤(中央公路與東陽路一段交叉口）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林慈聖太子殿(元帥府)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>園民牧場(元長鄉中山路257-6號)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>元長鰲峰宮</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>元長鄉舊公所</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>溝皂真武殿牌樓下棚架</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>草湖白沙屯媽祖會</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -4912,9 +5179,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4956,6 +5220,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -5338,11 +5605,11 @@
     <col min="1" max="2" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.33203125" style="33" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" style="25"/>
-    <col min="11" max="11" width="150.88671875" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="150.88671875" style="39" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
@@ -5362,22 +5629,22 @@
       <c r="E1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="34" t="s">
         <v>947</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="35" t="s">
         <v>948</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>949</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="36" t="s">
         <v>951</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="38" t="s">
         <v>663</v>
       </c>
     </row>
@@ -5397,22 +5664,22 @@
       <c r="E2" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="34">
         <v>46124.996527777781</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="35">
         <v>46128</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="34">
         <v>46129.006944444445</v>
       </c>
-      <c r="I2" s="35">
+      <c r="I2" s="34">
         <v>46132.673611111109</v>
       </c>
-      <c r="J2" s="37">
+      <c r="J2" s="36">
         <v>463558</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="38" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -5420,7 +5687,7 @@
       <c r="A3" s="10">
         <v>2025</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="37" t="s">
         <v>952</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -5432,22 +5699,22 @@
       <c r="E3" s="10" t="s">
         <v>955</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="34">
         <v>45778.975694444445</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="35">
         <v>45780</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="34">
         <v>45781.027777777781</v>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="34">
         <v>45788.65625</v>
       </c>
-      <c r="J3" s="37">
+      <c r="J3" s="36">
         <v>329118</v>
       </c>
-      <c r="K3" s="39"/>
+      <c r="K3" s="38"/>
     </row>
     <row r="4" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
@@ -5465,22 +5732,22 @@
       <c r="E4" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="34">
         <v>45369.024305555555</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="35">
         <v>45374</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="34">
         <v>45375.006944444445</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="34">
         <v>45377.607638888891</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="36">
         <v>179971</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="38" t="s">
         <v>1126</v>
       </c>
     </row>
@@ -5488,7 +5755,7 @@
       <c r="A5" s="10">
         <v>2023</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="37" t="s">
         <v>959</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -5500,28 +5767,28 @@
       <c r="E5" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="34">
         <v>44969.059027777781</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="35">
         <v>44974</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="34">
         <v>44974.986111111109</v>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="34">
         <v>44977.666666666664</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="36">
         <v>113621</v>
       </c>
-      <c r="K5" s="39"/>
+      <c r="K5" s="38"/>
     </row>
     <row r="6" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>2022</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="37" t="s">
         <v>960</v>
       </c>
       <c r="C6" s="10" t="s">
@@ -5533,22 +5800,22 @@
       <c r="E6" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="34">
         <v>44701.09375</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="35">
         <v>44703</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="34">
         <v>44704.010416666664</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="34">
         <v>44708.628472222219</v>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="36">
         <v>90928</v>
       </c>
-      <c r="K6" s="39"/>
+      <c r="K6" s="38"/>
     </row>
     <row r="7" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
@@ -5566,22 +5833,22 @@
       <c r="E7" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="34">
         <v>44297.986111111109</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="35">
         <v>44302</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="34">
         <v>44302.958333333336</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="34">
         <v>44305.614583333336</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="36">
         <v>78672</v>
       </c>
-      <c r="K7" s="39"/>
+      <c r="K7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
@@ -5599,22 +5866,22 @@
       <c r="E8" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <v>44017.09375</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="35">
         <v>44020</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="34">
         <v>44021.21875</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="34">
         <v>44025.638888888891</v>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="36">
         <v>54599</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="38" t="s">
         <v>963</v>
       </c>
     </row>
@@ -5622,7 +5889,7 @@
       <c r="A9" s="10">
         <v>2019</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="37" t="s">
         <v>962</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -5634,28 +5901,28 @@
       <c r="E9" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <v>43563.055555555555</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="35">
         <v>43566</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="34">
         <v>43567.208333333336</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <v>43572.600694444445</v>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="36">
         <v>50001</v>
       </c>
-      <c r="K9" s="39"/>
+      <c r="K9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>2018</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="37" t="s">
         <v>964</v>
       </c>
       <c r="C10" s="10" t="s">
@@ -5667,28 +5934,28 @@
       <c r="E10" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="34">
         <v>43236.986111111109</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="35">
         <v>43238</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="34">
         <v>43239.288194444445</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <v>43244.597222222219</v>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="36">
         <v>43205</v>
       </c>
-      <c r="K10" s="39"/>
+      <c r="K10" s="38"/>
     </row>
     <row r="11" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>2017</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="37" t="s">
         <v>965</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -5700,22 +5967,22 @@
       <c r="E11" s="10" t="s">
         <v>967</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>42792.104166666664</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="35">
         <v>42796</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>42797.052083333336</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <v>42803.5625</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="36">
         <v>26669</v>
       </c>
-      <c r="K11" s="39"/>
+      <c r="K11" s="38"/>
     </row>
     <row r="12" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
@@ -5733,22 +6000,22 @@
       <c r="E12" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="34">
         <v>42445.020833333336</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="35">
         <v>42449</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="34">
         <v>42450.239583333336</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="34">
         <v>42455.625</v>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="36">
         <v>19437</v>
       </c>
-      <c r="K12" s="39"/>
+      <c r="K12" s="38"/>
     </row>
     <row r="13" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
@@ -5766,22 +6033,22 @@
       <c r="E13" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="34">
         <v>42146.003472222219</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <v>42147</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="34">
         <v>42147.135416666664</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="34">
         <v>42152.635416666664</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="36">
         <v>18579</v>
       </c>
-      <c r="K13" s="39"/>
+      <c r="K13" s="38"/>
     </row>
     <row r="14" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
@@ -5799,22 +6066,22 @@
       <c r="E14" s="10" t="s">
         <v>955</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="34">
         <v>41719.166666666664</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="35">
         <v>41721</v>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="34">
         <v>41722.229166666664</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="34">
         <v>41719.607638888891</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="36">
         <v>11398</v>
       </c>
-      <c r="K14" s="39"/>
+      <c r="K14" s="38"/>
     </row>
     <row r="15" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
@@ -5832,22 +6099,22 @@
       <c r="E15" s="10" t="s">
         <v>955</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="34">
         <v>41382.986111111109</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="35">
         <v>41384</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="34">
         <v>41385.21875</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="34">
         <v>41392.614583333336</v>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="36">
         <v>8939</v>
       </c>
-      <c r="K15" s="39"/>
+      <c r="K15" s="38"/>
     </row>
     <row r="16" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
@@ -5865,22 +6132,22 @@
       <c r="E16" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="34">
         <v>40950.232638888891</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="35">
         <v>40953</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="34">
         <v>40954.21875</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="34">
         <v>40958.625</v>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="36">
         <v>6328</v>
       </c>
-      <c r="K16" s="39"/>
+      <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
@@ -5898,22 +6165,22 @@
       <c r="E17" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="34">
         <v>40608.989583333336</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="35">
         <v>40610</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="34">
         <v>40611.263888888891</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="34">
         <v>40616.607638888891</v>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="36">
         <v>5465</v>
       </c>
-      <c r="K17" s="39"/>
+      <c r="K17" s="38"/>
     </row>
     <row r="18" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
@@ -5931,22 +6198,22 @@
       <c r="E18" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="34">
         <v>40321.291666666664</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="35">
         <v>40325</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="34">
         <v>40326.010416666664</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="34">
         <v>40331.604166666664</v>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="36">
         <v>4994</v>
       </c>
-      <c r="K18" s="39"/>
+      <c r="K18" s="38"/>
     </row>
     <row r="19" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
@@ -5964,22 +6231,22 @@
       <c r="E19" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="34">
         <v>39899.013888888891</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="35">
         <v>39900</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="34">
         <v>39900.986111111109</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <v>39904.604166666664</v>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="36">
         <v>4938</v>
       </c>
-      <c r="K19" s="39"/>
+      <c r="K19" s="38"/>
     </row>
     <row r="20" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
@@ -5997,22 +6264,22 @@
       <c r="E20" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <v>39508.041666666664</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="35">
         <v>39509</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>39510</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>39515.597222222219</v>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="36">
         <v>4314</v>
       </c>
-      <c r="K20" s="39"/>
+      <c r="K20" s="38"/>
     </row>
     <row r="21" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
@@ -6030,22 +6297,22 @@
       <c r="E21" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="34">
         <v>39195.319444444445</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="35">
         <v>39197</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="34">
         <v>39198.135416666664</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="34">
         <v>39203.583333333336</v>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="36">
         <v>3607</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="38" t="s">
         <v>1119</v>
       </c>
     </row>
@@ -6065,22 +6332,22 @@
       <c r="E22" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="34">
         <v>38766.354166666664</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="35">
         <v>38769</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="34">
         <v>38770.041666666664</v>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="34">
         <v>38773.5625</v>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="36">
         <v>3342</v>
       </c>
-      <c r="K22" s="39" t="s">
+      <c r="K22" s="38" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -6100,22 +6367,22 @@
       <c r="E23" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="34">
         <v>38448.34375</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="35">
         <v>38451</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="34">
         <v>38452.145833333336</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="34">
         <v>38456.5625</v>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="36">
         <v>3486</v>
       </c>
-      <c r="K23" s="39" t="s">
+      <c r="K23" s="38" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -6135,22 +6402,22 @@
       <c r="E24" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="34">
         <v>38101.319444444445</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="35">
         <v>38104</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="34">
         <v>38104.958333333336</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="34">
         <v>38109.583333333336</v>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="36">
         <v>3230</v>
       </c>
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="38" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -6170,22 +6437,22 @@
       <c r="E25" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="34">
         <v>37749.375</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="35">
         <v>37753</v>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="34">
         <v>37754.083333333336</v>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="34">
         <v>37756.604166666664</v>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="36">
         <v>3173</v>
       </c>
-      <c r="K25" s="39"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
@@ -6203,22 +6470,22 @@
       <c r="E26" s="10" t="s">
         <v>946</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="34">
         <v>37332.34375</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="35">
         <v>37336</v>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="34">
         <v>37336.986111111109</v>
       </c>
-      <c r="I26" s="35">
+      <c r="I26" s="34">
         <v>37340.572916666664</v>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="36">
         <v>3141</v>
       </c>
-      <c r="K26" s="39"/>
+      <c r="K26" s="38"/>
     </row>
     <row r="27" spans="1:11" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
@@ -6236,20 +6503,20 @@
       <c r="E27" s="10" t="s">
         <v>967</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="34">
         <v>36959.298611111109</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="35">
         <v>36961</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="34">
         <v>36962.038194444445</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="34">
         <v>36968.611111111109</v>
       </c>
-      <c r="J27" s="37"/>
-      <c r="K27" s="39" t="s">
+      <c r="J27" s="36"/>
+      <c r="K27" s="38" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -15044,14 +15311,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD22D530-CC3B-44CF-9F92-B519A5B48D14}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="28" style="40" customWidth="1"/>
     <col min="6" max="6" width="50.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.21875" style="11" bestFit="1" customWidth="1"/>
@@ -15074,9 +15341,6 @@
       <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>647</v>
-      </c>
       <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
@@ -15091,40 +15355,2487 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E2" s="26"/>
+      <c r="A2" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C2" s="11">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11">
+        <v>13</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E3" s="26"/>
-    </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F41" s="12"/>
+      <c r="A3" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C3" s="11">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11">
+        <v>13</v>
+      </c>
+      <c r="E3" s="17">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C4" s="11">
+        <v>4</v>
+      </c>
+      <c r="D4" s="11">
+        <v>13</v>
+      </c>
+      <c r="E4" s="17">
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C5" s="11">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11">
+        <v>13</v>
+      </c>
+      <c r="E5" s="17">
+        <v>0.18888888888888888</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C6" s="11">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11">
+        <v>13</v>
+      </c>
+      <c r="E6" s="17">
+        <v>0.22430555555555556</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C7" s="11">
+        <v>4</v>
+      </c>
+      <c r="D7" s="11">
+        <v>13</v>
+      </c>
+      <c r="E7" s="17">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C8" s="11">
+        <v>4</v>
+      </c>
+      <c r="D8" s="11">
+        <v>13</v>
+      </c>
+      <c r="E8" s="17">
+        <v>0.30486111111111114</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C9" s="11">
+        <v>4</v>
+      </c>
+      <c r="D9" s="11">
+        <v>13</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C10" s="11">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11">
+        <v>13</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0.4152777777777778</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C11" s="11">
+        <v>4</v>
+      </c>
+      <c r="D11" s="11">
+        <v>13</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C12" s="11">
+        <v>4</v>
+      </c>
+      <c r="D12" s="11">
+        <v>13</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C13" s="11">
+        <v>4</v>
+      </c>
+      <c r="D13" s="11">
+        <v>13</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C14" s="11">
+        <v>4</v>
+      </c>
+      <c r="D14" s="11">
+        <v>13</v>
+      </c>
+      <c r="E14" s="17">
+        <v>0.6791666666666667</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C15" s="11">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11">
+        <v>14</v>
+      </c>
+      <c r="E15" s="17">
+        <v>0.11388888888888889</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C16" s="11">
+        <v>4</v>
+      </c>
+      <c r="D16" s="11">
+        <v>14</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0.12986111111111112</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C17" s="11">
+        <v>4</v>
+      </c>
+      <c r="D17" s="11">
+        <v>14</v>
+      </c>
+      <c r="E17" s="17">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C18" s="11">
+        <v>4</v>
+      </c>
+      <c r="D18" s="11">
+        <v>14</v>
+      </c>
+      <c r="E18" s="17">
+        <v>0.15416666666666667</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C19" s="11">
+        <v>4</v>
+      </c>
+      <c r="D19" s="11">
+        <v>14</v>
+      </c>
+      <c r="E19" s="17">
+        <v>0.17152777777777778</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C20" s="11">
+        <v>4</v>
+      </c>
+      <c r="D20" s="11">
+        <v>14</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C21" s="11">
+        <v>4</v>
+      </c>
+      <c r="D21" s="11">
+        <v>14</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0.22777777777777777</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C22" s="11">
+        <v>4</v>
+      </c>
+      <c r="D22" s="11">
+        <v>14</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0.24722222222222223</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C23" s="11">
+        <v>4</v>
+      </c>
+      <c r="D23" s="11">
+        <v>14</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0.30277777777777776</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C24" s="11">
+        <v>4</v>
+      </c>
+      <c r="D24" s="11">
+        <v>14</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0.33263888888888887</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C25" s="11">
+        <v>4</v>
+      </c>
+      <c r="D25" s="11">
+        <v>14</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C26" s="11">
+        <v>4</v>
+      </c>
+      <c r="D26" s="11">
+        <v>14</v>
+      </c>
+      <c r="E26" s="17">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C27" s="11">
+        <v>4</v>
+      </c>
+      <c r="D27" s="11">
+        <v>14</v>
+      </c>
+      <c r="E27" s="17">
+        <v>0.46736111111111112</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C28" s="11">
+        <v>4</v>
+      </c>
+      <c r="D28" s="11">
+        <v>14</v>
+      </c>
+      <c r="E28" s="17">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C29" s="11">
+        <v>4</v>
+      </c>
+      <c r="D29" s="11">
+        <v>14</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.64027777777777772</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C30" s="11">
+        <v>4</v>
+      </c>
+      <c r="D30" s="11">
+        <v>14</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.67569444444444449</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C31" s="11">
+        <v>4</v>
+      </c>
+      <c r="D31" s="11">
+        <v>14</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0.70763888888888893</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C32" s="11">
+        <v>4</v>
+      </c>
+      <c r="D32" s="11">
+        <v>14</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.74027777777777781</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C33" s="11">
+        <v>4</v>
+      </c>
+      <c r="D33" s="11">
+        <v>14</v>
+      </c>
+      <c r="E33" s="17">
+        <v>0.81111111111111112</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C34" s="11">
+        <v>4</v>
+      </c>
+      <c r="D34" s="11">
+        <v>15</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C35" s="11">
+        <v>4</v>
+      </c>
+      <c r="D35" s="11">
+        <v>15</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C36" s="11">
+        <v>4</v>
+      </c>
+      <c r="D36" s="11">
+        <v>15</v>
+      </c>
+      <c r="E36" s="17">
+        <v>0.34305555555555556</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C37" s="11">
+        <v>4</v>
+      </c>
+      <c r="D37" s="11">
+        <v>15</v>
+      </c>
+      <c r="E37" s="17">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C38" s="11">
+        <v>4</v>
+      </c>
+      <c r="D38" s="11">
+        <v>15</v>
+      </c>
+      <c r="E38" s="17">
+        <v>0.59791666666666665</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C39" s="11">
+        <v>4</v>
+      </c>
+      <c r="D39" s="11">
+        <v>15</v>
+      </c>
+      <c r="E39" s="17">
+        <v>0.62013888888888891</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C40" s="11">
+        <v>4</v>
+      </c>
+      <c r="D40" s="11">
+        <v>15</v>
+      </c>
+      <c r="E40" s="17">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C41" s="11">
+        <v>4</v>
+      </c>
+      <c r="D41" s="11">
+        <v>15</v>
+      </c>
+      <c r="E41" s="17">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C42" s="11">
+        <v>4</v>
+      </c>
+      <c r="D42" s="11">
+        <v>15</v>
+      </c>
+      <c r="E42" s="17">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C43" s="11">
+        <v>4</v>
+      </c>
+      <c r="D43" s="11">
+        <v>15</v>
+      </c>
+      <c r="E43" s="17">
+        <v>0.80972222222222223</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C44" s="11">
+        <v>4</v>
+      </c>
+      <c r="D44" s="11">
+        <v>16</v>
+      </c>
+      <c r="E44" s="17">
+        <v>0.125</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C45" s="11">
+        <v>4</v>
+      </c>
+      <c r="D45" s="11">
+        <v>16</v>
+      </c>
+      <c r="E45" s="17">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C46" s="11">
+        <v>4</v>
+      </c>
+      <c r="D46" s="11">
+        <v>16</v>
+      </c>
+      <c r="E46" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C47" s="11">
+        <v>4</v>
+      </c>
+      <c r="D47" s="11">
+        <v>16</v>
+      </c>
+      <c r="E47" s="17">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C48" s="11">
+        <v>4</v>
+      </c>
+      <c r="D48" s="11">
+        <v>16</v>
+      </c>
+      <c r="E48" s="17">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C49" s="11">
+        <v>4</v>
+      </c>
+      <c r="D49" s="11">
+        <v>16</v>
+      </c>
+      <c r="E49" s="17">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C50" s="11">
+        <v>4</v>
+      </c>
+      <c r="D50" s="11">
+        <v>16</v>
+      </c>
+      <c r="E50" s="17">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C51" s="11">
+        <v>4</v>
+      </c>
+      <c r="D51" s="11">
+        <v>16</v>
+      </c>
+      <c r="E51" s="17">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C52" s="11">
+        <v>4</v>
+      </c>
+      <c r="D52" s="11">
+        <v>17</v>
+      </c>
+      <c r="E52" s="17">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C53" s="11">
+        <v>4</v>
+      </c>
+      <c r="D53" s="11">
+        <v>17</v>
+      </c>
+      <c r="E53" s="17">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C54" s="11">
+        <v>4</v>
+      </c>
+      <c r="D54" s="11">
+        <v>17</v>
+      </c>
+      <c r="E54" s="17">
+        <v>6.5972222222222224E-2</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C55" s="11">
+        <v>4</v>
+      </c>
+      <c r="D55" s="11">
+        <v>17</v>
+      </c>
+      <c r="E55" s="17">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C56" s="11">
+        <v>4</v>
+      </c>
+      <c r="D56" s="11">
+        <v>17</v>
+      </c>
+      <c r="E56" s="17">
+        <v>0.12152777777777778</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C57" s="11">
+        <v>4</v>
+      </c>
+      <c r="D57" s="11">
+        <v>17</v>
+      </c>
+      <c r="E57" s="17">
+        <v>0.13680555555555557</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C58" s="11">
+        <v>4</v>
+      </c>
+      <c r="D58" s="11">
+        <v>17</v>
+      </c>
+      <c r="E58" s="17">
+        <v>0.19097222222222221</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C59" s="11">
+        <v>4</v>
+      </c>
+      <c r="D59" s="11">
+        <v>17</v>
+      </c>
+      <c r="E59" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C60" s="11">
+        <v>4</v>
+      </c>
+      <c r="D60" s="11">
+        <v>17</v>
+      </c>
+      <c r="E60" s="17">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C61" s="11">
+        <v>4</v>
+      </c>
+      <c r="D61" s="11">
+        <v>17</v>
+      </c>
+      <c r="E61" s="17">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C62" s="11">
+        <v>4</v>
+      </c>
+      <c r="D62" s="11">
+        <v>17</v>
+      </c>
+      <c r="E62" s="17">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C63" s="11">
+        <v>4</v>
+      </c>
+      <c r="D63" s="11">
+        <v>17</v>
+      </c>
+      <c r="E63" s="17">
+        <v>0.43541666666666667</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C64" s="11">
+        <v>4</v>
+      </c>
+      <c r="D64" s="11">
+        <v>17</v>
+      </c>
+      <c r="E64" s="17">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C65" s="11">
+        <v>4</v>
+      </c>
+      <c r="D65" s="11">
+        <v>17</v>
+      </c>
+      <c r="E65" s="17">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C66" s="11">
+        <v>4</v>
+      </c>
+      <c r="D66" s="11">
+        <v>17</v>
+      </c>
+      <c r="E66" s="17">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C67" s="11">
+        <v>4</v>
+      </c>
+      <c r="D67" s="11">
+        <v>17</v>
+      </c>
+      <c r="E67" s="17">
+        <v>0.69930555555555551</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C68" s="11">
+        <v>4</v>
+      </c>
+      <c r="D68" s="11">
+        <v>17</v>
+      </c>
+      <c r="E68" s="17">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C69" s="11">
+        <v>4</v>
+      </c>
+      <c r="D69" s="11">
+        <v>18</v>
+      </c>
+      <c r="E69" s="17">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C70" s="11">
+        <v>4</v>
+      </c>
+      <c r="D70" s="11">
+        <v>18</v>
+      </c>
+      <c r="E70" s="17">
+        <v>0.21875</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C71" s="11">
+        <v>4</v>
+      </c>
+      <c r="D71" s="11">
+        <v>18</v>
+      </c>
+      <c r="E71" s="17">
+        <v>0.24930555555555556</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C72" s="11">
+        <v>4</v>
+      </c>
+      <c r="D72" s="11">
+        <v>18</v>
+      </c>
+      <c r="E72" s="17">
+        <v>0.31736111111111109</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C73" s="11">
+        <v>4</v>
+      </c>
+      <c r="D73" s="11">
+        <v>18</v>
+      </c>
+      <c r="E73" s="17">
+        <v>0.41180555555555554</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C74" s="11">
+        <v>4</v>
+      </c>
+      <c r="D74" s="11">
+        <v>18</v>
+      </c>
+      <c r="E74" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C75" s="11">
+        <v>4</v>
+      </c>
+      <c r="D75" s="11">
+        <v>18</v>
+      </c>
+      <c r="E75" s="17">
+        <v>0.5395833333333333</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I75" s="11" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C76" s="11">
+        <v>4</v>
+      </c>
+      <c r="D76" s="11">
+        <v>18</v>
+      </c>
+      <c r="E76" s="17">
+        <v>0.66111111111111109</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C77" s="11">
+        <v>4</v>
+      </c>
+      <c r="D77" s="11">
+        <v>18</v>
+      </c>
+      <c r="E77" s="17">
+        <v>0.68263888888888891</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C78" s="11">
+        <v>4</v>
+      </c>
+      <c r="D78" s="11">
+        <v>18</v>
+      </c>
+      <c r="E78" s="17">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C79" s="11">
+        <v>4</v>
+      </c>
+      <c r="D79" s="11">
+        <v>18</v>
+      </c>
+      <c r="E79" s="17">
+        <v>0.81388888888888888</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C80" s="11">
+        <v>4</v>
+      </c>
+      <c r="D80" s="11">
+        <v>19</v>
+      </c>
+      <c r="E80" s="17">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C81" s="11">
+        <v>4</v>
+      </c>
+      <c r="D81" s="11">
+        <v>19</v>
+      </c>
+      <c r="E81" s="17">
+        <v>0.25138888888888888</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C82" s="11">
+        <v>4</v>
+      </c>
+      <c r="D82" s="11">
+        <v>19</v>
+      </c>
+      <c r="E82" s="17">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C83" s="11">
+        <v>4</v>
+      </c>
+      <c r="D83" s="11">
+        <v>19</v>
+      </c>
+      <c r="E83" s="17">
+        <v>0.33819444444444446</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C84" s="11">
+        <v>4</v>
+      </c>
+      <c r="D84" s="11">
+        <v>19</v>
+      </c>
+      <c r="E84" s="17">
+        <v>0.3527777777777778</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C85" s="11">
+        <v>4</v>
+      </c>
+      <c r="D85" s="11">
+        <v>19</v>
+      </c>
+      <c r="E85" s="17">
+        <v>0.41180555555555554</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C86" s="11">
+        <v>4</v>
+      </c>
+      <c r="D86" s="11">
+        <v>19</v>
+      </c>
+      <c r="E86" s="17">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C87" s="11">
+        <v>4</v>
+      </c>
+      <c r="D87" s="11">
+        <v>19</v>
+      </c>
+      <c r="E87" s="17">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C88" s="11">
+        <v>4</v>
+      </c>
+      <c r="D88" s="11">
+        <v>19</v>
+      </c>
+      <c r="E88" s="17">
+        <v>0.57361111111111107</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C89" s="11">
+        <v>4</v>
+      </c>
+      <c r="D89" s="11">
+        <v>19</v>
+      </c>
+      <c r="E89" s="17">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C90" s="11">
+        <v>4</v>
+      </c>
+      <c r="D90" s="11">
+        <v>20</v>
+      </c>
+      <c r="E90" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C91" s="11">
+        <v>4</v>
+      </c>
+      <c r="D91" s="11">
+        <v>20</v>
+      </c>
+      <c r="E91" s="17">
+        <v>0.28194444444444444</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C92" s="11">
+        <v>4</v>
+      </c>
+      <c r="D92" s="11">
+        <v>20</v>
+      </c>
+      <c r="E92" s="17">
+        <v>0.38680555555555557</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C93" s="11">
+        <v>4</v>
+      </c>
+      <c r="D93" s="11">
+        <v>20</v>
+      </c>
+      <c r="E93" s="17">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C94" s="11">
+        <v>4</v>
+      </c>
+      <c r="D94" s="11">
+        <v>20</v>
+      </c>
+      <c r="E94" s="17">
+        <v>0.46944444444444444</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H94" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="C95" s="11">
+        <v>4</v>
+      </c>
+      <c r="D95" s="11">
+        <v>20</v>
+      </c>
+      <c r="E95" s="17">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H95" s="11" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -23855,31 +26566,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="31" t="s">
+      <c r="D1" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="30" t="s">
         <v>647</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>387</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>662</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>663</v>
       </c>
     </row>
@@ -23910,384 +26621,384 @@
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <v>2021</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="28">
         <v>4</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="28">
         <v>12</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="28"/>
+      <c r="G3" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>2021</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="28">
         <v>4</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="28">
         <v>12</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="28"/>
+      <c r="G4" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <v>2021</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <v>4</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="28">
         <v>12</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>0.18333333333333332</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="28"/>
+      <c r="G5" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28">
+      <c r="A6" s="27">
         <v>2021</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <v>4</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="28">
         <v>12</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>0.22013888888888888</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="28"/>
+      <c r="G6" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>2021</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <v>4</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <v>12</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>0.23541666666666666</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>648</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="28"/>
+      <c r="G7" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28">
+      <c r="A8" s="27">
         <v>2021</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <v>4</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
         <v>12</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="28"/>
+      <c r="G8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <v>2021</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <v>4</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>12</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>0.28541666666666665</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="28"/>
+      <c r="G9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28">
+      <c r="A10" s="27">
         <v>2021</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
         <v>4</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="28">
         <v>12</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>0.37708333333333333</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="27" t="s">
         <v>461</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="28"/>
+      <c r="G10" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28">
+      <c r="A11" s="27">
         <v>2021</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <v>4</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="28">
         <v>12</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>0.39791666666666664</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="28"/>
+      <c r="G11" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
+      <c r="A12" s="27">
         <v>2021</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <v>4</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <v>12</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>0.45347222222222222</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="27" t="s">
         <v>745</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="28" t="s">
+      <c r="G12" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="27" t="s">
         <v>640</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="27" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>2021</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="28">
         <v>4</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="28">
         <v>12</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>0.55208333333333337</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="28"/>
+      <c r="G13" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>2021</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="28">
         <v>4</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="28">
         <v>12</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>0.66388888888888886</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="28"/>
+      <c r="G14" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="28">
+      <c r="A15" s="27">
         <v>2021</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <v>4</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="28">
         <v>12</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>0.70138888888888884</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="28"/>
+      <c r="G15" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9" s="4" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>2021</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="28">
         <v>4</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <v>12</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>0.72569444444444442</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="27" t="s">
         <v>668</v>
       </c>
     </row>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D86946D-4A27-4720-B496-ED97F22D7218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CBBFD5-F991-4A82-A414-72C855A1D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4168" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4169" uniqueCount="1195">
   <si>
     <t>年份</t>
   </si>
@@ -5100,7 +5100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5220,9 +5220,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -15318,7 +15315,7 @@
     <col min="2" max="2" width="5.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28" style="40" customWidth="1"/>
+    <col min="5" max="5" width="28" style="13" customWidth="1"/>
     <col min="6" max="6" width="50.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.21875" style="11" bestFit="1" customWidth="1"/>
@@ -15340,6 +15337,9 @@
       </c>
       <c r="D1" s="11" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>647</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>4</v>

--- a/BaishatunMAZU_Data.xlsx
+++ b/BaishatunMAZU_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\BLACK\MAZU\白沙屯歷年資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CBBFD5-F991-4A82-A414-72C855A1D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAA2CA3-2979-4B70-9E45-A257F4E6410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23992" yWindow="-50" windowWidth="24142" windowHeight="12897" tabRatio="783" activeTab="1" xr2:uid="{DA17B94B-1B8F-4AA7-851A-FB1198B0BA7A}"/>
   </bookViews>
@@ -15315,7 +15315,7 @@
     <col min="2" max="2" width="5.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28" style="13" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="50.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.21875" style="11" bestFit="1" customWidth="1"/>
